--- a/data/spain/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/spain/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:BN1"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,6 +757,3280 @@
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>45522.6875</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23010</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M2" t="n">
+        <v>33</v>
+      </c>
+      <c r="N2" t="n">
+        <v>67</v>
+      </c>
+      <c r="O2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>148</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12444444.44444444</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>78.44444444444444</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>80850000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>26.36842105263158</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>182.8947368421053</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>73.73684210526316</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6868947.368421053</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>76.68421052631579</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>24.52631578947368</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>177.1052631578947</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>2.052631578947369</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>77.89473684210526</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>34988157.89473684</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>83.36842105263158</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>172</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>69</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>168</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>108500000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>hIsKeIld</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45522.60416666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de aza m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>12194</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9642</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>56</v>
+      </c>
+      <c r="N3" t="n">
+        <v>44</v>
+      </c>
+      <c r="O3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>13</v>
+      </c>
+      <c r="T3" t="n">
+        <v>19</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>148</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>22.625</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1884375</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>858333.3333333334</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>nigFFwtS</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45522.60416666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">palencia caballero d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio manuel martinez valero
+  elche </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>31388</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>71</v>
+      </c>
+      <c r="N4" t="n">
+        <v>29</v>
+      </c>
+      <c r="O4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>16</v>
+      </c>
+      <c r="T4" t="n">
+        <v>18</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>148</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1365625</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>70.625</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>179.1333333333333</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>67.93333333333334</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1441666.666666667</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>65.66666666666667</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1277777.777777778</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45522.58333333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>31763</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>66</v>
+      </c>
+      <c r="N5" t="n">
+        <v>34</v>
+      </c>
+      <c r="O5" t="n">
+        <v>11</v>
+      </c>
+      <c r="P5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14</v>
+      </c>
+      <c r="T5" t="n">
+        <v>21</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>148</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>22555555.55555556</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>81.22222222222223</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>6887500</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>23.125</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>17412500</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>81.1875</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>28.06666666666667</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>177.8666666666667</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>73.86666666666666</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4980000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>314</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>329</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>137</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>11550000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0I1yLYH7</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guzman mansilla j  l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>29029</v>
+      </c>
+      <c r="F6" t="n">
+        <v>23319</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>66</v>
+      </c>
+      <c r="N6" t="n">
+        <v>34</v>
+      </c>
+      <c r="O6" t="n">
+        <v>11</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>148</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>179.1111111111111</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2372222.222222222</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>24.18181818181818</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>177.3636363636364</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1788636.363636364</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>177.5833333333333</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1983333.333333333</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>0fJlUxeL</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moreno a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sardinero
+  santander </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>22222</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19697</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>36</v>
+      </c>
+      <c r="N7" t="n">
+        <v>64</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>9</v>
+      </c>
+      <c r="S7" t="n">
+        <v>18</v>
+      </c>
+      <c r="T7" t="n">
+        <v>15</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>148</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>26.47058823529412</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>180.6470588235294</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>66.88235294117646</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1427941.176470588</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>72.64705882352941</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>22.57142857142857</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>184.7619047619048</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>69.0952380952381</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3557142.857142857</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>76.42857142857143</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45521.6875</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F8" t="n">
+        <v>46673</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M8" t="n">
+        <v>36</v>
+      </c>
+      <c r="N8" t="n">
+        <v>64</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>8</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="n">
+        <v>13</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>148</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11602500</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>178.875</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>69.4375</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4559062.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>76.1875</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>21.3125</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>31759375</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>82.125</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>376</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>388</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>397</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>257600000</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19561</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>61</v>
+      </c>
+      <c r="N9" t="n">
+        <v>39</v>
+      </c>
+      <c r="O9" t="n">
+        <v>16</v>
+      </c>
+      <c r="P9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>14</v>
+      </c>
+      <c r="T9" t="n">
+        <v>12</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>148</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>177.875</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>72.3125</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7870312.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>78.1875</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>25.21052631578947</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>183.6315789473684</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>5059210.52631579</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>74.94736842105263</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>145</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>145</v>
+      </c>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tvOEHaBF</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lax franco s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de riazor
+  la coruna </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>34889</v>
+      </c>
+      <c r="F10" t="n">
+        <v>25715</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>66</v>
+      </c>
+      <c r="N10" t="n">
+        <v>34</v>
+      </c>
+      <c r="O10" t="n">
+        <v>17</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>22</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>148</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>177.55</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>69</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2176250</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dQ4KOGIr</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mallo e 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de ipurua
+  eibar </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>8164</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3538</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>37</v>
+      </c>
+      <c r="N11" t="n">
+        <v>63</v>
+      </c>
+      <c r="O11" t="n">
+        <v>9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>17</v>
+      </c>
+      <c r="T11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>148</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>68</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1625000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>24.85714285714286</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>182.7857142857143</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>66.85714285714286</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1801785.714285714</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>72.07142857142857</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vkYg8eY1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesma espinosa m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal da malata
+  ferrol </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>10450</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7541</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>41</v>
+      </c>
+      <c r="N12" t="n">
+        <v>59</v>
+      </c>
+      <c r="O12" t="n">
+        <v>14</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>16</v>
+      </c>
+      <c r="T12" t="n">
+        <v>16</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>148</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1190625</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>27.72727272727273</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>178</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>66.54545454545455</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>959090.9090909091</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>64.16666666666667</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1391666.666666667</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F13" t="n">
+        <v>24843</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M13" t="n">
+        <v>48</v>
+      </c>
+      <c r="N13" t="n">
+        <v>52</v>
+      </c>
+      <c r="O13" t="n">
+        <v>15</v>
+      </c>
+      <c r="P13" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>14</v>
+      </c>
+      <c r="T13" t="n">
+        <v>15</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>148</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>75.11111111111111</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>10622222.22222222</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>79.44444444444444</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>177</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6627272.727272728</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>179</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>10522222.22222222</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>81</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>291</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>17700000</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>294</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>80</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8QP6JLt3</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monescillo d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo mirandilla
+  cadiz </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>20776</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16970</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>62</v>
+      </c>
+      <c r="N14" t="n">
+        <v>38</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>9</v>
+      </c>
+      <c r="S14" t="n">
+        <v>14</v>
+      </c>
+      <c r="T14" t="n">
+        <v>21</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>148</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>175.8888888888889</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1811111.111111111</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>25.5625</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>178.8125</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3395312.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>69.61111111111111</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22477</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>64</v>
+      </c>
+      <c r="N15" t="n">
+        <v>36</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>23</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>148</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>8650000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.277777777777778</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>72.77777777777777</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>9987500</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>24.26315789473684</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>180.6842105263158</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3814473.684210526</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>75.94736842105263</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>151</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>154</v>
+      </c>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>hhbTMfme</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez diaz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5759</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3005</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>32</v>
+      </c>
+      <c r="N16" t="n">
+        <v>68</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>148</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F17" t="n">
+        <v>54084</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M17" t="n">
+        <v>39</v>
+      </c>
+      <c r="N17" t="n">
+        <v>61</v>
+      </c>
+      <c r="O17" t="n">
+        <v>19</v>
+      </c>
+      <c r="P17" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>148</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>17512500</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>81.375</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>185</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>72.76923076923077</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6384615.384615385</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>79.92307692307692</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>24.35714285714286</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>180.9285714285714</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.214285714285714</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>70.71428571428571</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>4835714.285714285</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>79.14285714285714</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>216</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>26650000</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>230</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>358</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>61400000</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>6eQuWbQ8</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45519.64583333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reig s  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo los carmenes
+  granada </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>22524</v>
+      </c>
+      <c r="F18" t="n">
+        <v>13265</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>65</v>
+      </c>
+      <c r="N18" t="n">
+        <v>35</v>
+      </c>
+      <c r="O18" t="n">
+        <v>22</v>
+      </c>
+      <c r="P18" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>10</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="n">
+        <v>11</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>148</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4237500</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="n">
+        <v>25.13636363636364</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>181.6363636363636</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.136363636363636</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>70.86363636363636</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3861363.636363636</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>75.31818181818181</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>180</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>4729545.454545454</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45519.58333333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F19" t="n">
+        <v>47845</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M19" t="n">
+        <v>69</v>
+      </c>
+      <c r="N19" t="n">
+        <v>31</v>
+      </c>
+      <c r="O19" t="n">
+        <v>7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>12</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>148</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>18277777.77777778</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>80.77777777777777</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>26.77777777777778</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>9352777.777777778</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>23.89473684210526</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>182.2105263157895</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.473684210526316</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>76.15789473684211</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>17563157.89473684</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>81.42105263157895</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5260000</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>310</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>82500000</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>330</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>78</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/spain/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:BN1"/>
+  <dimension ref="A1:BN22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,6 +757,3850 @@
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>45523.6875</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21566</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="M2" t="n">
+        <v>44</v>
+      </c>
+      <c r="N2" t="n">
+        <v>56</v>
+      </c>
+      <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ii1Om118</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>148</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>28.22222222222222</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>30055555.55555556</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>83.33333333333333</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11625000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>26.10526315789474</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>180.1052631578947</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.684210526315789</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>79.15789473684211</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>25078947.36842105</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>82.52631578947368</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>233</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>236</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>IZqoAH3k</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45523.64583333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de la fuente ramos o 
+  esp </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo pepico amat
+  elda </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4038</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>46</v>
+      </c>
+      <c r="N3" t="n">
+        <v>54</v>
+      </c>
+      <c r="O3" t="n">
+        <v>15</v>
+      </c>
+      <c r="P3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>11</v>
+      </c>
+      <c r="T3" t="n">
+        <v>17</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>UBD9uzt0</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>148</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>28.11111111111111</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>66.27777777777777</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1244722.222222222</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>69.27777777777777</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>30.14285714285714</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>184.5714285714286</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1642857.142857143</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>72.85714285714286</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45523.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M4" t="n">
+        <v>45</v>
+      </c>
+      <c r="N4" t="n">
+        <v>55</v>
+      </c>
+      <c r="O4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>148</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>178.8888888888889</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>71.44444444444444</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3622222.222222222</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>75.55555555555556</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>76.44444444444444</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>24.4375</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>180.8125</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3392187.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>76.125</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>178.8181818181818</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>69.45454545454545</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3227272.727272727</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>76</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>178</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>142</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>142</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>178</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>74</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45522.6875</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23010</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M5" t="n">
+        <v>35</v>
+      </c>
+      <c r="N5" t="n">
+        <v>65</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>11</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>148</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>12444444.44444444</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>78.44444444444444</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>80850000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>26.36842105263158</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>182.8947368421053</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>73.73684210526316</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6868947.368421053</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>76.68421052631579</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>24.52631578947368</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>177.1052631578947</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.052631578947369</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>77.89473684210526</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>34988157.89473684</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>83.36842105263158</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>172</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>69</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>168</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>108500000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hIsKeIld</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45522.60416666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de aza m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12194</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9642</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>56</v>
+      </c>
+      <c r="N6" t="n">
+        <v>44</v>
+      </c>
+      <c r="O6" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>13</v>
+      </c>
+      <c r="T6" t="n">
+        <v>19</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>148</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>22.625</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1884375</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>858333.3333333334</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>nigFFwtS</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45522.60416666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">palencia caballero d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio manuel martinez valero
+  elche </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>31388</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>71</v>
+      </c>
+      <c r="N7" t="n">
+        <v>29</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16</v>
+      </c>
+      <c r="T7" t="n">
+        <v>18</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>148</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1365625</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>70.625</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>179.1333333333333</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>67.93333333333334</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1441666.666666667</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>65.66666666666667</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1277777.777777778</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45522.58333333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31763</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>66</v>
+      </c>
+      <c r="N8" t="n">
+        <v>34</v>
+      </c>
+      <c r="O8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>14</v>
+      </c>
+      <c r="T8" t="n">
+        <v>21</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>148</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>22555555.55555556</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>81.22222222222223</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>75.125</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>6887500</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>23.125</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>17412500</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>81.1875</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>28.06666666666667</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>177.8666666666667</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>73.86666666666666</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4980000</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>314</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>329</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>137</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>11550000</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0I1yLYH7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guzman mansilla j  l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>29029</v>
+      </c>
+      <c r="F9" t="n">
+        <v>23319</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>66</v>
+      </c>
+      <c r="N9" t="n">
+        <v>34</v>
+      </c>
+      <c r="O9" t="n">
+        <v>11</v>
+      </c>
+      <c r="P9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>148</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>179.1111111111111</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2372222.222222222</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>24.18181818181818</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>177.3636363636364</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1788636.363636364</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>177.5833333333333</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1983333.333333333</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0fJlUxeL</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moreno a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sardinero
+  santander </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>22222</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19697</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>36</v>
+      </c>
+      <c r="N10" t="n">
+        <v>64</v>
+      </c>
+      <c r="O10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>18</v>
+      </c>
+      <c r="T10" t="n">
+        <v>15</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>148</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>26.47058823529412</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>180.6470588235294</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>66.88235294117646</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1427941.176470588</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>72.64705882352941</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>22.57142857142857</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>184.7619047619048</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>69.0952380952381</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3557142.857142857</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>76.42857142857143</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45521.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F11" t="n">
+        <v>46673</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M11" t="n">
+        <v>36</v>
+      </c>
+      <c r="N11" t="n">
+        <v>64</v>
+      </c>
+      <c r="O11" t="n">
+        <v>6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11</v>
+      </c>
+      <c r="T11" t="n">
+        <v>13</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>148</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11602500</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>178.875</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>69.4375</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4559062.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>76.1875</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>21.3125</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>31759375</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>82.125</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>376</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>388</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>397</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>257600000</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F12" t="n">
+        <v>19561</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>61</v>
+      </c>
+      <c r="N12" t="n">
+        <v>39</v>
+      </c>
+      <c r="O12" t="n">
+        <v>16</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>148</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>177.875</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>72.3125</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>7870312.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>78.1875</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>25.21052631578947</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>183.6315789473684</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5059210.52631579</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>74.94736842105263</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>145</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>145</v>
+      </c>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tvOEHaBF</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lax franco s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de riazor
+  la coruna </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>34889</v>
+      </c>
+      <c r="F13" t="n">
+        <v>25715</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>66</v>
+      </c>
+      <c r="N13" t="n">
+        <v>34</v>
+      </c>
+      <c r="O13" t="n">
+        <v>17</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>22</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>148</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>177.55</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>69</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>2176250</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dQ4KOGIr</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mallo e 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de ipurua
+  eibar </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>8164</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3538</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>37</v>
+      </c>
+      <c r="N14" t="n">
+        <v>63</v>
+      </c>
+      <c r="O14" t="n">
+        <v>9</v>
+      </c>
+      <c r="P14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>17</v>
+      </c>
+      <c r="T14" t="n">
+        <v>9</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>148</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>68</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1625000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="n">
+        <v>24.85714285714286</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>182.7857142857143</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>66.85714285714286</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1801785.714285714</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>72.07142857142857</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vkYg8eY1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesma espinosa m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal da malata
+  ferrol </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10450</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7541</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>41</v>
+      </c>
+      <c r="N15" t="n">
+        <v>59</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>16</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>148</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1190625</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="n">
+        <v>27.72727272727273</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>178</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>66.54545454545455</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>959090.9090909091</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>64.16666666666667</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1391666.666666667</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8QP6JLt3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monescillo d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo mirandilla
+  cadiz </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>20776</v>
+      </c>
+      <c r="F16" t="n">
+        <v>16970</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>62</v>
+      </c>
+      <c r="N16" t="n">
+        <v>38</v>
+      </c>
+      <c r="O16" t="n">
+        <v>13</v>
+      </c>
+      <c r="P16" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>9</v>
+      </c>
+      <c r="S16" t="n">
+        <v>14</v>
+      </c>
+      <c r="T16" t="n">
+        <v>21</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>148</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>175.8888888888889</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1811111.111111111</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>25.5625</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>178.8125</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3395312.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>69.61111111111111</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24843</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M17" t="n">
+        <v>48</v>
+      </c>
+      <c r="N17" t="n">
+        <v>52</v>
+      </c>
+      <c r="O17" t="n">
+        <v>15</v>
+      </c>
+      <c r="P17" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>14</v>
+      </c>
+      <c r="T17" t="n">
+        <v>15</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>148</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>75.11111111111111</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>10622222.22222222</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>79.44444444444444</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>177</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6627272.727272728</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>179</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10522222.22222222</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>81</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>291</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>17700000</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>294</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>80</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22477</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M18" t="n">
+        <v>64</v>
+      </c>
+      <c r="N18" t="n">
+        <v>36</v>
+      </c>
+      <c r="O18" t="n">
+        <v>6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>23</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>148</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>8650000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.277777777777778</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>72.77777777777777</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>9987500</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>24.26315789473684</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>180.6842105263158</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3814473.684210526</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>75.94736842105263</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>151</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>154</v>
+      </c>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hhbTMfme</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez diaz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5759</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3005</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>32</v>
+      </c>
+      <c r="N19" t="n">
+        <v>68</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>14</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>148</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F20" t="n">
+        <v>54084</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M20" t="n">
+        <v>39</v>
+      </c>
+      <c r="N20" t="n">
+        <v>61</v>
+      </c>
+      <c r="O20" t="n">
+        <v>19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>11</v>
+      </c>
+      <c r="T20" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>148</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>17512500</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>81.375</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>185</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>72.76923076923077</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>6384615.384615385</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>79.92307692307692</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>24.35714285714286</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>180.9285714285714</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.214285714285714</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>70.71428571428571</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>4835714.285714285</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>79.14285714285714</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>216</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>26650000</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>230</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>358</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>61400000</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>6eQuWbQ8</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45519.64583333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reig s  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo los carmenes
+  granada </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>22524</v>
+      </c>
+      <c r="F21" t="n">
+        <v>13265</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>65</v>
+      </c>
+      <c r="N21" t="n">
+        <v>35</v>
+      </c>
+      <c r="O21" t="n">
+        <v>22</v>
+      </c>
+      <c r="P21" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>10</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="n">
+        <v>11</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>148</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4237500</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="n">
+        <v>25.13636363636364</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>181.6363636363636</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.136363636363636</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>70.86363636363636</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3861363.636363636</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>75.31818181818181</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>180</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4729545.454545454</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45519.58333333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F22" t="n">
+        <v>47845</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M22" t="n">
+        <v>69</v>
+      </c>
+      <c r="N22" t="n">
+        <v>31</v>
+      </c>
+      <c r="O22" t="n">
+        <v>7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="n">
+        <v>12</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>148</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>18277777.77777778</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>80.77777777777777</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>26.77777777777778</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>9352777.777777778</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>23.89473684210526</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>182.2105263157895</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.473684210526316</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>76.15789473684211</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>17563157.89473684</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>81.42105263157895</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>5260000</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>310</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>82500000</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>330</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>78</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/spain/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN22"/>
+  <dimension ref="A1:BN31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,52 +762,48 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>fcYpyo85</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45523.6875</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">barrera r 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadi ciutat de valencia
+  valencia </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23000</v>
+        <v>26354</v>
       </c>
       <c r="F2" t="n">
-        <v>21566</v>
+        <v>14068</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.97</v>
-      </c>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>44</v>
       </c>
@@ -815,38 +811,38 @@
         <v>56</v>
       </c>
       <c r="O2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R2" t="n">
         <v>8</v>
       </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>5</v>
-      </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Ii1Om118</t>
+          <t>fiZxGYJ3</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>84cvAG3H</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>148</v>
       </c>
       <c r="X2" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -856,10 +852,14 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
@@ -867,80 +867,66 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>28.22222222222222</v>
+        <v>28.875</v>
       </c>
       <c r="AJ2" t="n">
-        <v>182.3333333333333</v>
+        <v>182.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.333333333333333</v>
+        <v>1.125</v>
       </c>
       <c r="AL2" t="n">
-        <v>81.33333333333333</v>
+        <v>74.25</v>
       </c>
       <c r="AM2" t="n">
-        <v>30055555.55555556</v>
+        <v>5112500</v>
       </c>
       <c r="AN2" t="n">
-        <v>83.33333333333333</v>
+        <v>75.25</v>
       </c>
       <c r="AO2" t="n">
-        <v>23.5</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AP2" t="n">
-        <v>179.25</v>
+        <v>180.0909090909091</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.416666666666667</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>74.75</v>
+        <v>67.18181818181819</v>
       </c>
       <c r="AS2" t="n">
-        <v>11625000</v>
+        <v>1709090.909090909</v>
       </c>
       <c r="AT2" t="n">
-        <v>80.5</v>
+        <v>72</v>
       </c>
       <c r="AU2" t="n">
-        <v>26.10526315789474</v>
+        <v>26.46153846153846</v>
       </c>
       <c r="AV2" t="n">
-        <v>180.1052631578947</v>
+        <v>179.3076923076923</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.684210526315789</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>79.15789473684211</v>
+        <v>70.15384615384616</v>
       </c>
       <c r="AY2" t="n">
-        <v>25078947.36842105</v>
+        <v>2317307.692307692</v>
       </c>
       <c r="AZ2" t="n">
-        <v>82.52631578947368</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>183</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>233</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>44500000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>236</v>
-      </c>
+        <v>72.53846153846153</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
@@ -952,28 +938,30 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>IZqoAH3k</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45523.64583333334</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">de la fuente ramos o 
+          <t xml:space="preserve">gil manzano j 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo pepico amat
-  elda </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4038</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>55926</v>
+      </c>
+      <c r="F3" t="n">
+        <v>46448</v>
+      </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
@@ -982,55 +970,59 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8WUSyF3F</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.22</v>
+      </c>
       <c r="M3" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="N3" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="O3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="P3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="n">
         <v>11</v>
       </c>
-      <c r="T3" t="n">
-        <v>17</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>hh4xt2Df</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>UBD9uzt0</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>148</v>
       </c>
       <c r="X3" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1040,163 +1032,197 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+      <c r="AI3" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>183.8888888888889</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>77.77777777777777</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>22722222.22222222</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>82</v>
+      </c>
       <c r="AO3" t="n">
-        <v>28.11111111111111</v>
+        <v>20.3</v>
       </c>
       <c r="AP3" t="n">
-        <v>177.5</v>
+        <v>182.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>66.27777777777777</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>1244722.222222222</v>
+        <v>7785000</v>
       </c>
       <c r="AT3" t="n">
-        <v>69.27777777777777</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>30.14285714285714</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="AV3" t="n">
-        <v>184.5714285714286</v>
+        <v>183.1363636363636</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>1.318181818181818</v>
       </c>
       <c r="AX3" t="n">
-        <v>71.42857142857143</v>
+        <v>74</v>
       </c>
       <c r="AY3" t="n">
-        <v>1642857.142857143</v>
+        <v>11668181.81818182</v>
       </c>
       <c r="AZ3" t="n">
-        <v>72.85714285714286</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
+        <v>79.90909090909091</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>331</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>241500000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>353</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>312</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>328</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>QwI4i6hn</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45523.58333333334</v>
+        <v>45528.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">perez m 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>27618</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>29029</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20890</v>
+      </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.26</v>
-      </c>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="N4" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="O4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="P4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
         <v>10</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>15</v>
-      </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>S0PIZoj2</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>hh4xt2Df</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>148</v>
       </c>
       <c r="X4" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1204,219 +1230,171 @@
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>69w4Rb2d</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>4jl02tPF</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>24.88888888888889</v>
+        <v>26.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>178.8888888888889</v>
+        <v>178.7</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>71.44444444444444</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>3622222.222222222</v>
+        <v>2395000</v>
       </c>
       <c r="AH4" t="n">
-        <v>75.55555555555556</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>183.7777777777778</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>72.11111111111111</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>76.44444444444444</v>
-      </c>
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>24.4375</v>
+        <v>25</v>
       </c>
       <c r="AP4" t="n">
-        <v>180.8125</v>
+        <v>178</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.0625</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>69.875</v>
+        <v>69.44444444444444</v>
       </c>
       <c r="AS4" t="n">
-        <v>3392187.5</v>
+        <v>2577777.777777778</v>
       </c>
       <c r="AT4" t="n">
-        <v>76.125</v>
+        <v>74</v>
       </c>
       <c r="AU4" t="n">
-        <v>23.90909090909091</v>
+        <v>28.05882352941176</v>
       </c>
       <c r="AV4" t="n">
-        <v>178.8181818181818</v>
+        <v>178.2941176470588</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>69.45454545454545</v>
+        <v>66.11764705882354</v>
       </c>
       <c r="AY4" t="n">
-        <v>3227272.727272727</v>
+        <v>935588.2352941176</v>
       </c>
       <c r="AZ4" t="n">
-        <v>76</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>178</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>142</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4600000</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>142</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>178</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>74</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>75</v>
-      </c>
+        <v>68.94117647058823</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>fqgCMogC</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.6875</v>
+        <v>45528.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">fuentes molina a 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">estadio municipal da malata
+  ferrol </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26020</v>
+        <v>10450</v>
       </c>
       <c r="F5" t="n">
-        <v>23010</v>
+        <v>7397</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>zcgwCMgS</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.89</v>
-      </c>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="N5" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="O5" t="n">
+        <v>18</v>
+      </c>
+      <c r="P5" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7</v>
+      </c>
+      <c r="S5" t="n">
         <v>12</v>
       </c>
-      <c r="P5" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>11</v>
-      </c>
       <c r="T5" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>61Od00Pr</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>K4dMCgFa</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>148</v>
       </c>
       <c r="X5" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1426,213 +1404,189 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>27.66666666666667</v>
+        <v>26.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>185.1111111111111</v>
+        <v>179.125</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>76.55555555555556</v>
+        <v>66.625</v>
       </c>
       <c r="AG5" t="n">
-        <v>12444444.44444444</v>
+        <v>1190625</v>
       </c>
       <c r="AH5" t="n">
-        <v>78.44444444444444</v>
+        <v>69.875</v>
       </c>
       <c r="AI5" t="n">
-        <v>25.6</v>
+        <v>26.44444444444444</v>
       </c>
       <c r="AJ5" t="n">
-        <v>183.5</v>
+        <v>179.4444444444445</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.3</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AL5" t="n">
-        <v>86.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="AM5" t="n">
-        <v>80850000</v>
+        <v>4133333.333333333</v>
       </c>
       <c r="AN5" t="n">
-        <v>88.7</v>
+        <v>75.11111111111111</v>
       </c>
       <c r="AO5" t="n">
-        <v>26.36842105263158</v>
+        <v>26.78571428571428</v>
       </c>
       <c r="AP5" t="n">
-        <v>182.8947368421053</v>
+        <v>175.8571428571429</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.052631578947368</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>73.73684210526316</v>
+        <v>67.92857142857143</v>
       </c>
       <c r="AS5" t="n">
-        <v>6868947.368421053</v>
+        <v>1678571.428571429</v>
       </c>
       <c r="AT5" t="n">
-        <v>76.68421052631579</v>
+        <v>70.85714285714286</v>
       </c>
       <c r="AU5" t="n">
-        <v>24.52631578947368</v>
+        <v>25.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>177.1052631578947</v>
+        <v>181.1818181818182</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.052631578947369</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="AX5" t="n">
-        <v>77.89473684210526</v>
+        <v>70.68181818181819</v>
       </c>
       <c r="AY5" t="n">
-        <v>34988157.89473684</v>
+        <v>3993181.818181818</v>
       </c>
       <c r="AZ5" t="n">
-        <v>83.36842105263158</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>172</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>69</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>81</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>181</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>168</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>108500000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>175</v>
-      </c>
+        <v>74.45454545454545</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hIsKeIld</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.60416666666</v>
+        <v>45528.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">de aza m 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el plantio
-  burgos </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12194</v>
+        <v>23516</v>
       </c>
       <c r="F6" t="n">
-        <v>9642</v>
+        <v>19900</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>vTxTEFi6</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>IJyXDZ6C</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.35</v>
+      </c>
       <c r="M6" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="N6" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>l6JQtDqc</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>M1vEw5An</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>148</v>
       </c>
       <c r="X6" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1643,7 +1597,7 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
+          <t>YT0e2vMU</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1652,138 +1606,180 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>12444444.44444444</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>78.44444444444444</v>
+      </c>
       <c r="AO6" t="n">
-        <v>22.625</v>
+        <v>24.3125</v>
       </c>
       <c r="AP6" t="n">
-        <v>183.625</v>
+        <v>179.6875</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>1.0625</v>
       </c>
       <c r="AR6" t="n">
-        <v>66.5</v>
+        <v>70.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>1884375</v>
+        <v>6357812.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>73.75</v>
+        <v>76.8125</v>
       </c>
       <c r="AU6" t="n">
-        <v>25.16666666666667</v>
+        <v>27.10526315789474</v>
       </c>
       <c r="AV6" t="n">
-        <v>181</v>
+        <v>181.7368421052632</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AX6" t="n">
-        <v>65</v>
+        <v>73.52631578947368</v>
       </c>
       <c r="AY6" t="n">
-        <v>858333.3333333334</v>
+        <v>5974210.52631579</v>
       </c>
       <c r="AZ6" t="n">
-        <v>69.66666666666667</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+        <v>75.63157894736842</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>28.33333333333333</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>174.3333333333333</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>220</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>11700000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>220</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>172</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>69</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nigFFwtS</t>
+          <t>jPRgZOxI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45522.60416666666</v>
+        <v>45527.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">palencia caballero d 
+          <t xml:space="preserve">galech i 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio manuel martinez valero
-  elche </t>
+          <t xml:space="preserve">estadio el alcoraz
+  huesca </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>31388</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>9100</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6172</v>
+      </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
+          <t>UytPaaEP</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
+          <t>Q51ZzMS6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="N7" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>zT9gi7i9</t>
+          <t>lfrtHtBn</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>lfrtHtBn</t>
+          <t>vHBWuyve</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -1800,73 +1796,57 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
           <t>za7D2lO5</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>179.875</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>67.875</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1365625</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>70.625</v>
-      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>25.8</v>
+        <v>24.91666666666667</v>
       </c>
       <c r="AP7" t="n">
-        <v>179.1333333333333</v>
+        <v>178.75</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>67.93333333333334</v>
+        <v>66.33333333333333</v>
       </c>
       <c r="AS7" t="n">
-        <v>1441666.666666667</v>
+        <v>1304166.666666667</v>
       </c>
       <c r="AT7" t="n">
-        <v>73.2</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="AU7" t="n">
-        <v>24</v>
+        <v>26.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>179.6666666666667</v>
+        <v>180.75</v>
       </c>
       <c r="AW7" t="n">
         <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>65.66666666666667</v>
+        <v>68.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1277777.777777778</v>
+        <v>1515625</v>
       </c>
       <c r="AZ7" t="n">
-        <v>71.33333333333333</v>
+        <v>70.875</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -1886,29 +1866,29 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.58333333334</v>
+        <v>45527.6875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>40000</v>
+        <v>42714</v>
       </c>
       <c r="F8" t="n">
-        <v>31763</v>
+        <v>34004</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -1918,52 +1898,52 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="M8" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N8" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="O8" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
         <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T8" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -1978,204 +1958,196 @@
       <c r="Z8" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>25.88888888888889</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="AD8" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.888888888888889</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AF8" t="n">
-        <v>77.66666666666667</v>
+        <v>75</v>
       </c>
       <c r="AG8" t="n">
-        <v>22555555.55555556</v>
+        <v>11677777.77777778</v>
       </c>
       <c r="AH8" t="n">
-        <v>81.22222222222223</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>28.125</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>178.125</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>75.125</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>6887500</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>76.75</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>23.125</v>
+        <v>27.8</v>
       </c>
       <c r="AP8" t="n">
-        <v>179.25</v>
+        <v>181.0666666666667</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.375</v>
+        <v>1.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>74.5</v>
+        <v>77.06666666666666</v>
       </c>
       <c r="AS8" t="n">
-        <v>17412500</v>
+        <v>12813333.33333333</v>
       </c>
       <c r="AT8" t="n">
-        <v>81.1875</v>
+        <v>80.26666666666667</v>
       </c>
       <c r="AU8" t="n">
-        <v>28.06666666666667</v>
+        <v>28.75</v>
       </c>
       <c r="AV8" t="n">
-        <v>177.8666666666667</v>
+        <v>182.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.133333333333333</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>73.86666666666666</v>
+        <v>77.08333333333333</v>
       </c>
       <c r="AY8" t="n">
-        <v>4980000</v>
+        <v>10491666.66666667</v>
       </c>
       <c r="AZ8" t="n">
-        <v>75.66666666666667</v>
+        <v>79.58333333333333</v>
       </c>
       <c r="BA8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>181.75</v>
+        <v>184</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BE8" t="n">
-        <v>314</v>
+        <v>78</v>
       </c>
       <c r="BF8" t="n">
-        <v>89000000</v>
+        <v>14000000</v>
       </c>
       <c r="BG8" t="n">
-        <v>329</v>
+        <v>78</v>
       </c>
       <c r="BH8" t="n">
-        <v>23.5</v>
+        <v>27</v>
       </c>
       <c r="BI8" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.5</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BK8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL8" t="n">
-        <v>137</v>
+        <v>233</v>
       </c>
       <c r="BM8" t="n">
-        <v>11550000</v>
+        <v>44500000</v>
       </c>
       <c r="BN8" t="n">
-        <v>151</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0I1yLYH7</t>
+          <t>OxQ1X27U</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.5</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">guzman mansilla j  l 
+          <t xml:space="preserve">sanchez a 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el molinon
-  gijon </t>
+          <t xml:space="preserve">estadio el sardinero
+  santander </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29029</v>
+        <v>22222</v>
       </c>
       <c r="F9" t="n">
-        <v>23319</v>
+        <v>19205</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>nVpEwOrl</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>OEsEpExD</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="N9" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="O9" t="n">
+        <v>15</v>
+      </c>
+      <c r="P9" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
         <v>11</v>
       </c>
-      <c r="P9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>5</v>
-      </c>
-      <c r="S9" t="n">
-        <v>15</v>
-      </c>
       <c r="T9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>S0PIZoj2</t>
+          <t>rak12p9n</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>fiZxGYJ3</t>
+          <t>YB3UTO7e</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -2193,68 +2165,68 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="AC9" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>179.1111111111111</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>70.66666666666667</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2372222.222222222</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>73.11111111111111</v>
-      </c>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>180.375</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>68.625</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1675000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>74.125</v>
+      </c>
       <c r="AO9" t="n">
-        <v>24.18181818181818</v>
+        <v>25.35714285714286</v>
       </c>
       <c r="AP9" t="n">
-        <v>177.3636363636364</v>
+        <v>180.2142857142857</v>
       </c>
       <c r="AQ9" t="n">
         <v>1</v>
       </c>
       <c r="AR9" t="n">
-        <v>67.63636363636364</v>
+        <v>67</v>
       </c>
       <c r="AS9" t="n">
-        <v>1788636.363636364</v>
+        <v>1800000</v>
       </c>
       <c r="AT9" t="n">
-        <v>74.27272727272727</v>
+        <v>73.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>23</v>
+        <v>23.11111111111111</v>
       </c>
       <c r="AV9" t="n">
-        <v>177.5833333333333</v>
+        <v>182.5</v>
       </c>
       <c r="AW9" t="n">
         <v>1</v>
       </c>
       <c r="AX9" t="n">
-        <v>67.5</v>
+        <v>66</v>
       </c>
       <c r="AY9" t="n">
-        <v>1983333.333333333</v>
+        <v>1869444.444444444</v>
       </c>
       <c r="AZ9" t="n">
-        <v>73.25</v>
+        <v>73.22222222222223</v>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
@@ -2274,87 +2246,91 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0fJlUxeL</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.5</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">moreno a 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sardinero
-  santander </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22222</v>
+        <v>24791</v>
       </c>
       <c r="F10" t="n">
-        <v>19697</v>
+        <v>23519</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>nVpEwOrl</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>nF2Vy2D0</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.71</v>
+      </c>
       <c r="M10" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="N10" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="O10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
         <v>5</v>
       </c>
       <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
         <v>9</v>
       </c>
-      <c r="S10" t="n">
-        <v>18</v>
-      </c>
       <c r="T10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>rak12p9n</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>x604nX5H</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="W10" t="n">
         <v>148</v>
       </c>
       <c r="X10" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -2362,10 +2338,14 @@
       <c r="Z10" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>EXuxl1xP</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -2374,144 +2354,184 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
+      <c r="AI10" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>72</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>11602500</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>78.5</v>
+      </c>
       <c r="AO10" t="n">
-        <v>26.47058823529412</v>
+        <v>26.9</v>
       </c>
       <c r="AP10" t="n">
-        <v>180.6470588235294</v>
+        <v>180.1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>66.88235294117646</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>1427941.176470588</v>
+        <v>10473750</v>
       </c>
       <c r="AT10" t="n">
-        <v>72.64705882352941</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>22.57142857142857</v>
+        <v>24.88235294117647</v>
       </c>
       <c r="AV10" t="n">
-        <v>184.7619047619048</v>
+        <v>178.7647058823529</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.047619047619048</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="AX10" t="n">
-        <v>69.0952380952381</v>
+        <v>70.70588235294117</v>
       </c>
       <c r="AY10" t="n">
-        <v>3557142.857142857</v>
+        <v>6037941.176470588</v>
       </c>
       <c r="AZ10" t="n">
-        <v>76.42857142857143</v>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
+        <v>75.94117647058823</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>146</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>149</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>376</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>388</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45521.6875</v>
+        <v>45523.6875</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">cuadra g 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49430</v>
+        <v>23000</v>
       </c>
       <c r="F11" t="n">
-        <v>46673</v>
+        <v>21566</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="L11" t="n">
-        <v>2.75</v>
+        <v>0.97</v>
       </c>
       <c r="M11" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="N11" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="O11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" t="n">
         <v>6</v>
       </c>
-      <c r="P11" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>8</v>
-      </c>
-      <c r="S11" t="n">
-        <v>11</v>
-      </c>
       <c r="T11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>Ii1Om118</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="W11" t="n">
@@ -2531,202 +2551,178 @@
           <t>G8FL0ShI</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="AC11" t="n">
-        <v>22.125</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>182.25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>72</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11602500</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>28.22222222222222</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>30055555.55555556</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>83.33333333333333</v>
+      </c>
       <c r="AO11" t="n">
-        <v>23.625</v>
+        <v>23.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>178.875</v>
+        <v>179.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.0625</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="AR11" t="n">
-        <v>69.4375</v>
+        <v>74.75</v>
       </c>
       <c r="AS11" t="n">
-        <v>4559062.5</v>
+        <v>11625000</v>
       </c>
       <c r="AT11" t="n">
-        <v>76.1875</v>
+        <v>80.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>21.3125</v>
+        <v>26.10526315789474</v>
       </c>
       <c r="AV11" t="n">
-        <v>182.25</v>
+        <v>180.1052631578947</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.6875</v>
+        <v>1.684210526315789</v>
       </c>
       <c r="AX11" t="n">
-        <v>73.75</v>
+        <v>79.15789473684211</v>
       </c>
       <c r="AY11" t="n">
-        <v>31759375</v>
+        <v>25078947.36842105</v>
       </c>
       <c r="AZ11" t="n">
-        <v>82.125</v>
+        <v>82.52631578947368</v>
       </c>
       <c r="BA11" t="n">
-        <v>26.4</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>179.4</v>
+        <v>183</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.4</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BD11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BE11" t="n">
-        <v>376</v>
+        <v>233</v>
       </c>
       <c r="BF11" t="n">
-        <v>47000000</v>
+        <v>44500000</v>
       </c>
       <c r="BG11" t="n">
-        <v>388</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>397</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>257600000</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>433</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>IZqoAH3k</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45523.64583333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
+          <t xml:space="preserve">de la fuente ramos o 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio nuevo pepico amat
+  elda </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F12" t="n">
-        <v>19561</v>
-      </c>
+        <v>4038</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>8WUSyF3F</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="N12" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="O12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
         <v>5</v>
       </c>
-      <c r="R12" t="n">
-        <v>4</v>
-      </c>
       <c r="S12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>hh4xt2Df</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>UBD9uzt0</t>
         </is>
       </c>
       <c r="W12" t="n">
         <v>148</v>
       </c>
       <c r="X12" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2734,10 +2730,14 @@
       <c r="Z12" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2753,62 +2753,48 @@
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
-        <v>24.875</v>
+        <v>28.11111111111111</v>
       </c>
       <c r="AP12" t="n">
-        <v>177.875</v>
+        <v>177.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>1</v>
       </c>
       <c r="AR12" t="n">
-        <v>72.3125</v>
+        <v>66.27777777777777</v>
       </c>
       <c r="AS12" t="n">
-        <v>7870312.5</v>
+        <v>1244722.222222222</v>
       </c>
       <c r="AT12" t="n">
-        <v>78.1875</v>
+        <v>69.27777777777777</v>
       </c>
       <c r="AU12" t="n">
-        <v>25.21052631578947</v>
+        <v>30.14285714285714</v>
       </c>
       <c r="AV12" t="n">
-        <v>183.6315789473684</v>
+        <v>184.5714285714286</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.052631578947368</v>
+        <v>1</v>
       </c>
       <c r="AX12" t="n">
-        <v>71.05263157894737</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="AY12" t="n">
-        <v>5059210.52631579</v>
+        <v>1642857.142857143</v>
       </c>
       <c r="AZ12" t="n">
-        <v>74.94736842105263</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>176.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>145</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7600000</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>145</v>
-      </c>
+        <v>72.85714285714286</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr"/>
       <c r="BJ12" t="inlineStr"/>
@@ -2820,87 +2806,89 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tvOEHaBF</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45523.58333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">lax franco s 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de riazor
-  la coruna </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>34889</v>
-      </c>
-      <c r="F13" t="n">
-        <v>25715</v>
-      </c>
+        <v>27618</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Q51ZzMS6</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SzYzw34K</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.26</v>
+      </c>
       <c r="M13" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="N13" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="O13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T13" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>vHBWuyve</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>QmLgLqap</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="W13" t="n">
         <v>148</v>
       </c>
       <c r="X13" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2908,143 +2896,219 @@
       <c r="Z13" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>178.8888888888889</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>71.44444444444444</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3622222.222222222</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>75.55555555555556</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>76.44444444444444</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>24.4375</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>180.8125</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3392187.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>76.125</v>
+      </c>
       <c r="AU13" t="n">
-        <v>25.45</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AV13" t="n">
-        <v>177.55</v>
+        <v>178.8181818181818</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AX13" t="n">
-        <v>69</v>
+        <v>69.45454545454545</v>
       </c>
       <c r="AY13" t="n">
-        <v>2176250</v>
+        <v>3227272.727272727</v>
       </c>
       <c r="AZ13" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
-      <c r="BK13" t="inlineStr"/>
-      <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>178</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>142</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>142</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>178</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>74</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dQ4KOGIr</t>
+          <t>M3h3GWnS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45521.5</v>
+        <v>45522.6875</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">mallo e 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de ipurua
-  eibar </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8164</v>
+        <v>26020</v>
       </c>
       <c r="F14" t="n">
-        <v>3538</v>
+        <v>23010</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OEsEpExD</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>QyHHzdwl</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.89</v>
+      </c>
       <c r="M14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
         <v>4</v>
       </c>
       <c r="S14" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>YB3UTO7e</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>EF6Hrtsn</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="W14" t="n">
         <v>148</v>
       </c>
       <c r="X14" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -3054,150 +3118,204 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
       <c r="AC14" t="n">
-        <v>25.125</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="AD14" t="n">
-        <v>180.75</v>
+        <v>185.1111111111111</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AF14" t="n">
-        <v>68</v>
+        <v>76.55555555555556</v>
       </c>
       <c r="AG14" t="n">
-        <v>1625000</v>
+        <v>12444444.44444444</v>
       </c>
       <c r="AH14" t="n">
-        <v>74.375</v>
-      </c>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
+        <v>78.44444444444444</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>80850000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>88.7</v>
+      </c>
       <c r="AO14" t="n">
-        <v>24.85714285714286</v>
+        <v>26.36842105263158</v>
       </c>
       <c r="AP14" t="n">
-        <v>182.7857142857143</v>
+        <v>182.8947368421053</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AR14" t="n">
-        <v>66.85714285714286</v>
+        <v>73.73684210526316</v>
       </c>
       <c r="AS14" t="n">
-        <v>1801785.714285714</v>
+        <v>6868947.368421053</v>
       </c>
       <c r="AT14" t="n">
-        <v>72.07142857142857</v>
-      </c>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="inlineStr"/>
-      <c r="BJ14" t="inlineStr"/>
-      <c r="BK14" t="inlineStr"/>
-      <c r="BL14" t="inlineStr"/>
-      <c r="BM14" t="inlineStr"/>
-      <c r="BN14" t="inlineStr"/>
+        <v>76.68421052631579</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>24.52631578947368</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>177.1052631578947</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.052631578947369</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>77.89473684210526</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>34988157.89473684</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>83.36842105263158</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>172</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>69</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>168</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>108500000</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>vkYg8eY1</t>
+          <t>nigFFwtS</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45521.5</v>
+        <v>45522.60416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">sesma espinosa m 
+          <t xml:space="preserve">palencia caballero d 
   esp </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal da malata
-  ferrol </t>
+          <t xml:space="preserve">estadio manuel martinez valero
+  elche </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10450</v>
-      </c>
-      <c r="F15" t="n">
-        <v>7541</v>
-      </c>
+        <v>31388</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>zcgwCMgS</t>
+          <t>4jl02tPF</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25tIqYiJ</t>
+          <t>UytPaaEP</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="N15" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="O15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
         <v>16</v>
       </c>
       <c r="T15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>61Od00Pr</t>
+          <t>zT9gi7i9</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>tjXr7SAp</t>
+          <t>lfrtHtBn</t>
         </is>
       </c>
       <c r="W15" t="n">
@@ -3214,69 +3332,73 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>179.125</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>66.625</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1190625</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>69.875</v>
-      </c>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1365625</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>70.625</v>
+      </c>
       <c r="AO15" t="n">
-        <v>27.72727272727273</v>
+        <v>25.8</v>
       </c>
       <c r="AP15" t="n">
-        <v>178</v>
+        <v>179.1333333333333</v>
       </c>
       <c r="AQ15" t="n">
         <v>1</v>
       </c>
       <c r="AR15" t="n">
-        <v>66.54545454545455</v>
+        <v>67.93333333333334</v>
       </c>
       <c r="AS15" t="n">
-        <v>959090.9090909091</v>
+        <v>1441666.666666667</v>
       </c>
       <c r="AT15" t="n">
-        <v>68.63636363636364</v>
+        <v>73.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>21.66666666666667</v>
+        <v>24</v>
       </c>
       <c r="AV15" t="n">
-        <v>181.8333333333333</v>
+        <v>179.6666666666667</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>64.16666666666667</v>
+        <v>65.66666666666667</v>
       </c>
       <c r="AY15" t="n">
-        <v>1391666.666666667</v>
+        <v>1277777.777777778</v>
       </c>
       <c r="AZ15" t="n">
-        <v>73.33333333333333</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr"/>
@@ -3296,80 +3418,80 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>8QP6JLt3</t>
+          <t>hIsKeIld</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45520.6875</v>
+        <v>45522.60416666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">monescillo d 
+          <t xml:space="preserve">de aza m 
   esp </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo mirandilla
-  cadiz </t>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>20776</v>
+        <v>12194</v>
       </c>
       <c r="F16" t="n">
-        <v>16970</v>
+        <v>9642</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>hdWjLJUJ</t>
+          <t>vTxTEFi6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>za7D2lO5</t>
+          <t>IJyXDZ6C</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="N16" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="O16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P16" t="n">
         <v>12</v>
       </c>
       <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
         <v>3</v>
       </c>
-      <c r="R16" t="n">
-        <v>9</v>
-      </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>84cvAG3H</t>
+          <t>l6JQtDqc</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>4WbDi59E</t>
+          <t>M1vEw5An</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -3384,14 +3506,10 @@
       <c r="Z16" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
+      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
+          <t>4jl02tPF</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -3400,59 +3518,47 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="n">
-        <v>23.77777777777778</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>175.8888888888889</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>67.88888888888889</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1811111.111111111</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>73.77777777777777</v>
-      </c>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="n">
-        <v>25.5625</v>
+        <v>22.625</v>
       </c>
       <c r="AP16" t="n">
-        <v>178.8125</v>
+        <v>183.625</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.1875</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
-        <v>70</v>
+        <v>66.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>3395312.5</v>
+        <v>1884375</v>
       </c>
       <c r="AT16" t="n">
-        <v>75.375</v>
+        <v>73.75</v>
       </c>
       <c r="AU16" t="n">
-        <v>26.38888888888889</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="AV16" t="n">
-        <v>180.7777777777778</v>
+        <v>181</v>
       </c>
       <c r="AW16" t="n">
         <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>69.61111111111111</v>
+        <v>65</v>
       </c>
       <c r="AY16" t="n">
-        <v>2075000</v>
+        <v>858333.3333333334</v>
       </c>
       <c r="AZ16" t="n">
-        <v>73.33333333333333</v>
+        <v>69.66666666666667</v>
       </c>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
@@ -3472,63 +3578,63 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>Eax2EqHs</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45520.6875</v>
+        <v>45522.58333333334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>32392</v>
+        <v>40000</v>
       </c>
       <c r="F17" t="n">
-        <v>24843</v>
+        <v>31763</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.86</v>
+        <v>1.55</v>
       </c>
       <c r="L17" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="N17" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="O17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
         <v>5</v>
@@ -3540,16 +3646,16 @@
         <v>14</v>
       </c>
       <c r="T17" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="W17" t="n">
@@ -3564,207 +3670,211 @@
       <c r="Z17" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
+      <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>22555555.55555556</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>81.22222222222223</v>
+      </c>
       <c r="AI17" t="n">
-        <v>25.33333333333333</v>
+        <v>28.125</v>
       </c>
       <c r="AJ17" t="n">
-        <v>185.5555555555555</v>
+        <v>178.125</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.444444444444444</v>
+        <v>1.375</v>
       </c>
       <c r="AL17" t="n">
-        <v>75.11111111111111</v>
+        <v>75.125</v>
       </c>
       <c r="AM17" t="n">
-        <v>10622222.22222222</v>
+        <v>6887500</v>
       </c>
       <c r="AN17" t="n">
-        <v>79.44444444444444</v>
+        <v>76.75</v>
       </c>
       <c r="AO17" t="n">
-        <v>25.27272727272727</v>
+        <v>23.125</v>
       </c>
       <c r="AP17" t="n">
-        <v>177</v>
+        <v>179.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.090909090909091</v>
+        <v>1.375</v>
       </c>
       <c r="AR17" t="n">
-        <v>73.45454545454545</v>
+        <v>74.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>6627272.727272728</v>
+        <v>17412500</v>
       </c>
       <c r="AT17" t="n">
-        <v>75.90909090909091</v>
+        <v>81.1875</v>
       </c>
       <c r="AU17" t="n">
-        <v>27.66666666666667</v>
+        <v>28.06666666666667</v>
       </c>
       <c r="AV17" t="n">
-        <v>179</v>
+        <v>177.8666666666667</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.777777777777778</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="AX17" t="n">
-        <v>75.88888888888889</v>
+        <v>73.86666666666666</v>
       </c>
       <c r="AY17" t="n">
-        <v>10522222.22222222</v>
+        <v>4980000</v>
       </c>
       <c r="AZ17" t="n">
-        <v>81</v>
+        <v>75.66666666666667</v>
       </c>
       <c r="BA17" t="n">
-        <v>26.75</v>
+        <v>25</v>
       </c>
       <c r="BB17" t="n">
-        <v>179.5</v>
+        <v>181.75</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="BD17" t="n">
         <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="BF17" t="n">
-        <v>17700000</v>
+        <v>89000000</v>
       </c>
       <c r="BG17" t="n">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="BH17" t="n">
-        <v>28</v>
+        <v>23.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="BJ17" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL17" t="n">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="BM17" t="n">
-        <v>21000000</v>
+        <v>11550000</v>
       </c>
       <c r="BN17" t="n">
-        <v>80</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>0fJlUxeL</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45520.58333333334</v>
+        <v>45522.5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">moreno a 
   esp </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">estadio el sardinero
+  santander </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>24791</v>
+        <v>22222</v>
       </c>
       <c r="F18" t="n">
-        <v>22477</v>
+        <v>19697</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>nVpEwOrl</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.8</v>
-      </c>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
+        <v>36</v>
+      </c>
+      <c r="N18" t="n">
         <v>64</v>
       </c>
-      <c r="N18" t="n">
-        <v>36</v>
-      </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P18" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T18" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>rak12p9n</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>x604nX5H</t>
         </is>
       </c>
       <c r="W18" t="n">
         <v>148</v>
       </c>
       <c r="X18" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -3772,30 +3882,18 @@
       <c r="Z18" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>179.875</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>75.375</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>8650000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>78.25</v>
-      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
@@ -3803,62 +3901,48 @@
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="n">
-        <v>25.5</v>
+        <v>26.47058823529412</v>
       </c>
       <c r="AP18" t="n">
-        <v>181.5555555555555</v>
+        <v>180.6470588235294</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.277777777777778</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
-        <v>72.77777777777777</v>
+        <v>66.88235294117646</v>
       </c>
       <c r="AS18" t="n">
-        <v>9987500</v>
+        <v>1427941.176470588</v>
       </c>
       <c r="AT18" t="n">
-        <v>76.77777777777777</v>
+        <v>72.64705882352941</v>
       </c>
       <c r="AU18" t="n">
-        <v>24.26315789473684</v>
+        <v>22.57142857142857</v>
       </c>
       <c r="AV18" t="n">
-        <v>180.6842105263158</v>
+        <v>184.7619047619048</v>
       </c>
       <c r="AW18" t="n">
-        <v>1</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AX18" t="n">
-        <v>71.05263157894737</v>
+        <v>69.0952380952381</v>
       </c>
       <c r="AY18" t="n">
-        <v>3814473.684210526</v>
+        <v>3557142.857142857</v>
       </c>
       <c r="AZ18" t="n">
-        <v>75.94736842105263</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>151</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>154</v>
-      </c>
+        <v>76.42857142857143</v>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr"/>
       <c r="BJ18" t="inlineStr"/>
@@ -3870,80 +3954,80 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hhbTMfme</t>
+          <t>0I1yLYH7</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45520.58333333334</v>
+        <v>45522.5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez diaz m 
+          <t xml:space="preserve">guzman mansilla j  l 
   esp </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de anduva
-  miranda de ebro </t>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5759</v>
+        <v>29029</v>
       </c>
       <c r="F19" t="n">
-        <v>3005</v>
+        <v>23319</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>48Z7G1Sf</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>CWuejruc</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="N19" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P19" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>pbHOStFA</t>
+          <t>S0PIZoj2</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>vBENkWfS</t>
+          <t>fiZxGYJ3</t>
         </is>
       </c>
       <c r="W19" t="n">
@@ -3958,36 +4042,72 @@
       <c r="Z19" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>179.1111111111111</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2372222.222222222</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>73.11111111111111</v>
+      </c>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="inlineStr"/>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr"/>
+      <c r="AO19" t="n">
+        <v>24.18181818181818</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>177.3636363636364</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>67.63636363636364</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1788636.363636364</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>177.5833333333333</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1983333.333333333</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>73.25</v>
+      </c>
       <c r="BA19" t="inlineStr"/>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
@@ -4006,84 +4126,84 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>KbKTWiX8</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45519.6875</v>
+        <v>45521.6875</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>60721</v>
+        <v>49430</v>
       </c>
       <c r="F20" t="n">
-        <v>54084</v>
+        <v>46673</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1.44</v>
+        <v>0.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="N20" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="O20" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S20" t="n">
         <v>11</v>
       </c>
       <c r="T20" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="W20" t="n">
@@ -4100,201 +4220,205 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="n">
-        <v>25.625</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>182.75</v>
-      </c>
-      <c r="AK20" t="n">
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL20" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>17512500</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>81.375</v>
-      </c>
+      <c r="AF20" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11602500</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="n">
-        <v>23.07692307692308</v>
+        <v>23.625</v>
       </c>
       <c r="AP20" t="n">
-        <v>185</v>
+        <v>178.875</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.307692307692308</v>
+        <v>1.0625</v>
       </c>
       <c r="AR20" t="n">
-        <v>72.76923076923077</v>
+        <v>69.4375</v>
       </c>
       <c r="AS20" t="n">
-        <v>6384615.384615385</v>
+        <v>4559062.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>79.92307692307692</v>
+        <v>76.1875</v>
       </c>
       <c r="AU20" t="n">
-        <v>24.35714285714286</v>
+        <v>21.3125</v>
       </c>
       <c r="AV20" t="n">
-        <v>180.9285714285714</v>
+        <v>182.25</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.214285714285714</v>
+        <v>1.6875</v>
       </c>
       <c r="AX20" t="n">
-        <v>70.71428571428571</v>
+        <v>73.75</v>
       </c>
       <c r="AY20" t="n">
-        <v>4835714.285714285</v>
+        <v>31759375</v>
       </c>
       <c r="AZ20" t="n">
-        <v>79.14285714285714</v>
+        <v>82.125</v>
       </c>
       <c r="BA20" t="n">
-        <v>27</v>
+        <v>26.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>181.6666666666667</v>
+        <v>179.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
-        <v>216</v>
+        <v>376</v>
       </c>
       <c r="BF20" t="n">
-        <v>26650000</v>
+        <v>47000000</v>
       </c>
       <c r="BG20" t="n">
-        <v>230</v>
+        <v>388</v>
       </c>
       <c r="BH20" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="BI20" t="n">
-        <v>177.6</v>
+        <v>179.6</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="BK20" t="n">
         <v>5</v>
       </c>
       <c r="BL20" t="n">
-        <v>358</v>
+        <v>397</v>
       </c>
       <c r="BM20" t="n">
-        <v>61400000</v>
+        <v>257600000</v>
       </c>
       <c r="BN20" t="n">
-        <v>397</v>
+        <v>433</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>6eQuWbQ8</t>
+          <t>ruUIA1G6</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45519.64583333334</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">reig s  a 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo los carmenes
-  granada </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>22524</v>
+        <v>23516</v>
       </c>
       <c r="F21" t="n">
-        <v>13265</v>
+        <v>19561</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>EXuxl1xP</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>UirAofN6</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
       <c r="M21" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N21" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="O21" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>K4dMCgFa</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>ALneer6b</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="W21" t="n">
         <v>148</v>
       </c>
       <c r="X21" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -4302,34 +4426,18 @@
       <c r="Z21" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
+      <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AC21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>178.125</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>72.625</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>4237500</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>74.375</v>
-      </c>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
@@ -4337,48 +4445,62 @@
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="n">
-        <v>25.13636363636364</v>
+        <v>24.875</v>
       </c>
       <c r="AP21" t="n">
-        <v>181.6363636363636</v>
+        <v>177.875</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.136363636363636</v>
+        <v>1</v>
       </c>
       <c r="AR21" t="n">
-        <v>70.86363636363636</v>
+        <v>72.3125</v>
       </c>
       <c r="AS21" t="n">
-        <v>3861363.636363636</v>
+        <v>7870312.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>75.31818181818181</v>
+        <v>78.1875</v>
       </c>
       <c r="AU21" t="n">
-        <v>25.90909090909091</v>
+        <v>25.21052631578947</v>
       </c>
       <c r="AV21" t="n">
-        <v>180</v>
+        <v>183.6315789473684</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.181818181818182</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AX21" t="n">
-        <v>66.72727272727273</v>
+        <v>71.05263157894737</v>
       </c>
       <c r="AY21" t="n">
-        <v>4729545.454545454</v>
+        <v>5059210.52631579</v>
       </c>
       <c r="AZ21" t="n">
-        <v>70.09090909090909</v>
-      </c>
-      <c r="BA21" t="inlineStr"/>
-      <c r="BB21" t="inlineStr"/>
-      <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="inlineStr"/>
-      <c r="BF21" t="inlineStr"/>
-      <c r="BG21" t="inlineStr"/>
+        <v>74.94736842105263</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>145</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>145</v>
+      </c>
       <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr"/>
       <c r="BJ21" t="inlineStr"/>
@@ -4390,216 +4512,1786 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>tvOEHaBF</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lax franco s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de riazor
+  la coruna </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>34889</v>
+      </c>
+      <c r="F22" t="n">
+        <v>25715</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>66</v>
+      </c>
+      <c r="N22" t="n">
+        <v>34</v>
+      </c>
+      <c r="O22" t="n">
+        <v>17</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>22</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>148</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>177.55</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>69</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>2176250</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>dQ4KOGIr</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mallo e 
+  esp </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de ipurua
+  eibar </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>8164</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3538</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>37</v>
+      </c>
+      <c r="N23" t="n">
+        <v>63</v>
+      </c>
+      <c r="O23" t="n">
+        <v>9</v>
+      </c>
+      <c r="P23" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>17</v>
+      </c>
+      <c r="T23" t="n">
+        <v>9</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>148</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>68</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1625000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="n">
+        <v>24.85714285714286</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>182.7857142857143</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>66.85714285714286</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1801785.714285714</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>72.07142857142857</v>
+      </c>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>vkYg8eY1</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesma espinosa m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal da malata
+  ferrol </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>10450</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7541</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>41</v>
+      </c>
+      <c r="N24" t="n">
+        <v>59</v>
+      </c>
+      <c r="O24" t="n">
+        <v>14</v>
+      </c>
+      <c r="P24" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>16</v>
+      </c>
+      <c r="T24" t="n">
+        <v>16</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>148</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1190625</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="n">
+        <v>27.72727272727273</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>178</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>66.54545454545455</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>959090.9090909091</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>64.16666666666667</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1391666.666666667</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F25" t="n">
+        <v>24843</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M25" t="n">
+        <v>48</v>
+      </c>
+      <c r="N25" t="n">
+        <v>52</v>
+      </c>
+      <c r="O25" t="n">
+        <v>15</v>
+      </c>
+      <c r="P25" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>14</v>
+      </c>
+      <c r="T25" t="n">
+        <v>15</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>148</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>75.11111111111111</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>10622222.22222222</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>79.44444444444444</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>177</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>6627272.727272728</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>179</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>10522222.22222222</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>81</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>291</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>17700000</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>294</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>80</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>8QP6JLt3</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monescillo d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo mirandilla
+  cadiz </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>20776</v>
+      </c>
+      <c r="F26" t="n">
+        <v>16970</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>62</v>
+      </c>
+      <c r="N26" t="n">
+        <v>38</v>
+      </c>
+      <c r="O26" t="n">
+        <v>13</v>
+      </c>
+      <c r="P26" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>9</v>
+      </c>
+      <c r="S26" t="n">
+        <v>14</v>
+      </c>
+      <c r="T26" t="n">
+        <v>21</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>148</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>175.8888888888889</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1811111.111111111</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>25.5625</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>178.8125</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>3395312.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>69.61111111111111</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F27" t="n">
+        <v>22477</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M27" t="n">
+        <v>64</v>
+      </c>
+      <c r="N27" t="n">
+        <v>36</v>
+      </c>
+      <c r="O27" t="n">
+        <v>6</v>
+      </c>
+      <c r="P27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>23</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>148</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>8650000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.277777777777778</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>72.77777777777777</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>9987500</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>24.26315789473684</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>180.6842105263158</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>3814473.684210526</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>75.94736842105263</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>151</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>154</v>
+      </c>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>hhbTMfme</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez diaz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5759</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3005</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>32</v>
+      </c>
+      <c r="N28" t="n">
+        <v>68</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>14</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>148</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F29" t="n">
+        <v>54084</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M29" t="n">
+        <v>39</v>
+      </c>
+      <c r="N29" t="n">
+        <v>61</v>
+      </c>
+      <c r="O29" t="n">
+        <v>19</v>
+      </c>
+      <c r="P29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>11</v>
+      </c>
+      <c r="T29" t="n">
+        <v>7</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>148</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>17512500</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>81.375</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>185</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>72.76923076923077</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>6384615.384615385</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>79.92307692307692</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>24.35714285714286</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>180.9285714285714</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.214285714285714</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>70.71428571428571</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>4835714.285714285</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>79.14285714285714</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>216</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>26650000</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>230</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>358</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>61400000</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>6eQuWbQ8</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45519.64583333334</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reig s  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo los carmenes
+  granada </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>22524</v>
+      </c>
+      <c r="F30" t="n">
+        <v>13265</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>65</v>
+      </c>
+      <c r="N30" t="n">
+        <v>35</v>
+      </c>
+      <c r="O30" t="n">
+        <v>22</v>
+      </c>
+      <c r="P30" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>10</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="n">
+        <v>11</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>148</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>4237500</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="n">
+        <v>25.13636363636364</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>181.6363636363636</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.136363636363636</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>70.86363636363636</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>3861363.636363636</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>75.31818181818181</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>180</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>4729545.454545454</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
           <t>hO0nKEm3</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B31" s="2" t="n">
         <v>45519.58333333334</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio san mames
   bilbao </t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E31" t="n">
         <v>53331</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F31" t="n">
         <v>47845</v>
       </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>IP5zl0cJ</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>dboeiWOt</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="K31" t="n">
         <v>0.72</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L31" t="n">
         <v>1.07</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M31" t="n">
         <v>69</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N31" t="n">
         <v>31</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O31" t="n">
         <v>7</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P31" t="n">
         <v>9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q31" t="n">
         <v>4</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S31" t="n">
         <v>15</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T31" t="n">
         <v>12</v>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>EJmuzs93</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>4AuIPRuq</t>
         </is>
       </c>
-      <c r="W22" t="n">
+      <c r="W31" t="n">
         <v>148</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X31" t="n">
         <v>1481</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Y31" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="Z31" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr">
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr">
         <is>
           <t>Mi0rXQg7</t>
         </is>
       </c>
-      <c r="AC22" t="n">
+      <c r="AC31" t="n">
         <v>25.77777777777778</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AD31" t="n">
         <v>185</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AE31" t="n">
         <v>1.222222222222222</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AF31" t="n">
         <v>77.11111111111111</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AG31" t="n">
         <v>18277777.77777778</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AH31" t="n">
         <v>80.77777777777777</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AI31" t="n">
         <v>26.77777777777778</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AJ31" t="n">
         <v>179.8888888888889</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AK31" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AL31" t="n">
         <v>74.66666666666667</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AM31" t="n">
         <v>9352777.777777778</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AN31" t="n">
         <v>77.33333333333333</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AO31" t="n">
         <v>23.89473684210526</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AP31" t="n">
         <v>182.2105263157895</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AQ31" t="n">
         <v>1.473684210526316</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AR31" t="n">
         <v>76.15789473684211</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AS31" t="n">
         <v>17563157.89473684</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AT31" t="n">
         <v>81.42105263157895</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AU31" t="n">
         <v>23.9</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AV31" t="n">
         <v>179.6</v>
       </c>
-      <c r="AW22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX22" t="n">
+      <c r="AW31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX31" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="AY31" t="n">
         <v>5260000</v>
       </c>
-      <c r="AZ22" t="n">
+      <c r="AZ31" t="n">
         <v>77.3</v>
       </c>
-      <c r="BA22" t="n">
+      <c r="BA31" t="n">
         <v>24.25</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BB31" t="n">
         <v>182.5</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BC31" t="n">
         <v>1.5</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BD31" t="n">
         <v>4</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BE31" t="n">
         <v>310</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BF31" t="n">
         <v>82500000</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BG31" t="n">
         <v>330</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BH31" t="n">
         <v>26</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BI31" t="n">
         <v>182</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BJ31" t="n">
         <v>2</v>
       </c>
-      <c r="BK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL22" t="n">
+      <c r="BK31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL31" t="n">
         <v>78</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BM31" t="n">
         <v>17000000</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BN31" t="n">
         <v>79</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/spain/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN31"/>
+  <dimension ref="A1:BN39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,87 +762,91 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>fcYpyo85</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45529.59375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrera r 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi ciutat de valencia
-  valencia </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>26354</v>
+        <v>19840</v>
       </c>
       <c r="F2" t="n">
-        <v>14068</v>
+        <v>16623</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>hdWjLJUJ</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.37</v>
+      </c>
       <c r="M2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="N2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>16</v>
       </c>
       <c r="T2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>fiZxGYJ3</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>84cvAG3H</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>148</v>
       </c>
       <c r="X2" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -850,11 +854,7 @@
       <c r="Z2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
           <t>h8oAv4Ts</t>
@@ -866,59 +866,47 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>28.875</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>182.25</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>74.25</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>5112500</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>75.25</v>
-      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>23.90909090909091</v>
+        <v>23.53333333333333</v>
       </c>
       <c r="AP2" t="n">
-        <v>180.0909090909091</v>
+        <v>177.9333333333333</v>
       </c>
       <c r="AQ2" t="n">
         <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>67.18181818181819</v>
+        <v>71.46666666666667</v>
       </c>
       <c r="AS2" t="n">
-        <v>1709090.909090909</v>
+        <v>3713333.333333333</v>
       </c>
       <c r="AT2" t="n">
-        <v>72</v>
+        <v>76.53333333333333</v>
       </c>
       <c r="AU2" t="n">
-        <v>26.46153846153846</v>
+        <v>23.85714285714286</v>
       </c>
       <c r="AV2" t="n">
-        <v>179.3076923076923</v>
+        <v>182</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="AX2" t="n">
-        <v>70.15384615384616</v>
+        <v>73.57142857142857</v>
       </c>
       <c r="AY2" t="n">
-        <v>2317307.692307692</v>
+        <v>6514285.714285715</v>
       </c>
       <c r="AZ2" t="n">
-        <v>72.53846153846153</v>
+        <v>79.85714285714286</v>
       </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
@@ -927,102 +915,112 @@
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
+      <c r="BH2" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>285</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>29350000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>307</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>tEvOrxAE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45529.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">orellana m 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio carlos belmonte
+  albacete </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55926</v>
+        <v>17524</v>
       </c>
       <c r="F3" t="n">
-        <v>46448</v>
+        <v>11400</v>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>22</v>
+      </c>
+      <c r="N3" t="n">
+        <v>78</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M3" t="n">
-        <v>63</v>
-      </c>
-      <c r="N3" t="n">
-        <v>37</v>
-      </c>
-      <c r="O3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T3" t="n">
         <v>8</v>
       </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" t="n">
-        <v>8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>11</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>ALneer6b</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>zT9gi7i9</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>148</v>
       </c>
       <c r="X3" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1032,197 +1030,165 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="n">
-        <v>25.11111111111111</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>183.8888888888889</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>77.77777777777777</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>22722222.22222222</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>82</v>
-      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>20.3</v>
+        <v>25.25</v>
       </c>
       <c r="AP3" t="n">
-        <v>182.3</v>
+        <v>180</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.2</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AR3" t="n">
-        <v>67.40000000000001</v>
+        <v>68.75</v>
       </c>
       <c r="AS3" t="n">
-        <v>7785000</v>
+        <v>4843750</v>
       </c>
       <c r="AT3" t="n">
-        <v>77.90000000000001</v>
+        <v>72.08333333333333</v>
       </c>
       <c r="AU3" t="n">
-        <v>24.27272727272727</v>
+        <v>25.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>183.1363636363636</v>
+        <v>180.2666666666667</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.318181818181818</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="AY3" t="n">
-        <v>11668181.81818182</v>
+        <v>1320000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>79.90909090909091</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>179.75</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>331</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>241500000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>353</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>182.25</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>312</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>85000000</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>328</v>
-      </c>
+        <v>73.2</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QwI4i6hn</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">perez m 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el molinon
-  gijon </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29029</v>
+        <v>12454</v>
       </c>
       <c r="F4" t="n">
-        <v>20890</v>
+        <v>10052</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8WUSyF3F</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.76</v>
+      </c>
       <c r="M4" t="n">
+        <v>40</v>
+      </c>
+      <c r="N4" t="n">
         <v>60</v>
       </c>
-      <c r="N4" t="n">
-        <v>40</v>
-      </c>
       <c r="O4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5</v>
+      </c>
+      <c r="S4" t="n">
         <v>11</v>
       </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>10</v>
       </c>
-      <c r="T4" t="n">
-        <v>6</v>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>S0PIZoj2</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>hh4xt2Df</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>148</v>
       </c>
       <c r="X4" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1230,30 +1196,22 @@
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>178.7</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2395000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>73.59999999999999</v>
-      </c>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
@@ -1264,37 +1222,37 @@
         <v>25</v>
       </c>
       <c r="AP4" t="n">
-        <v>178</v>
+        <v>180.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AR4" t="n">
-        <v>69.44444444444444</v>
+        <v>70.55</v>
       </c>
       <c r="AS4" t="n">
-        <v>2577777.777777778</v>
+        <v>4871250</v>
       </c>
       <c r="AT4" t="n">
-        <v>74</v>
+        <v>74.75</v>
       </c>
       <c r="AU4" t="n">
-        <v>28.05882352941176</v>
+        <v>25.14285714285714</v>
       </c>
       <c r="AV4" t="n">
-        <v>178.2941176470588</v>
+        <v>176.4285714285714</v>
       </c>
       <c r="AW4" t="n">
-        <v>1</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AX4" t="n">
-        <v>66.11764705882354</v>
+        <v>74.21428571428571</v>
       </c>
       <c r="AY4" t="n">
-        <v>935588.2352941176</v>
+        <v>7907142.857142857</v>
       </c>
       <c r="AZ4" t="n">
-        <v>68.94117647058823</v>
+        <v>77.42857142857143</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
@@ -1303,98 +1261,116 @@
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
+      <c r="BH4" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>219</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>15400000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>222</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fqgCMogC</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuentes molina a 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal da malata
-  ferrol </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10450</v>
+        <v>83186</v>
       </c>
       <c r="F5" t="n">
-        <v>7397</v>
+        <v>70178</v>
       </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>zcgwCMgS</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>EXuxl1xP</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.77</v>
+      </c>
       <c r="M5" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="N5" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>61Od00Pr</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>K4dMCgFa</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>148</v>
       </c>
       <c r="X5" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1404,161 +1380,185 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>26.25</v>
+        <v>25.11111111111111</v>
       </c>
       <c r="AD5" t="n">
-        <v>179.125</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>3.222222222222222</v>
       </c>
       <c r="AF5" t="n">
-        <v>66.625</v>
+        <v>85.33333333333333</v>
       </c>
       <c r="AG5" t="n">
-        <v>1190625</v>
+        <v>74944444.44444445</v>
       </c>
       <c r="AH5" t="n">
-        <v>69.875</v>
+        <v>89</v>
       </c>
       <c r="AI5" t="n">
-        <v>26.44444444444444</v>
+        <v>25.375</v>
       </c>
       <c r="AJ5" t="n">
-        <v>179.4444444444445</v>
+        <v>180.625</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.111111111111111</v>
+        <v>1.125</v>
       </c>
       <c r="AL5" t="n">
-        <v>73</v>
+        <v>71.625</v>
       </c>
       <c r="AM5" t="n">
-        <v>4133333.333333333</v>
+        <v>4487500</v>
       </c>
       <c r="AN5" t="n">
-        <v>75.11111111111111</v>
+        <v>76.25</v>
       </c>
       <c r="AO5" t="n">
-        <v>26.78571428571428</v>
+        <v>26</v>
       </c>
       <c r="AP5" t="n">
-        <v>175.8571428571429</v>
+        <v>175</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="AR5" t="n">
-        <v>67.92857142857143</v>
+        <v>80.08333333333333</v>
       </c>
       <c r="AS5" t="n">
-        <v>1678571.428571429</v>
+        <v>40756250</v>
       </c>
       <c r="AT5" t="n">
-        <v>70.85714285714286</v>
+        <v>84.41666666666667</v>
       </c>
       <c r="AU5" t="n">
         <v>25.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>181.1818181818182</v>
+        <v>178.5555555555555</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.045454545454545</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AX5" t="n">
-        <v>70.68181818181819</v>
+        <v>70.88888888888889</v>
       </c>
       <c r="AY5" t="n">
-        <v>3993181.818181818</v>
+        <v>3048611.111111111</v>
       </c>
       <c r="AZ5" t="n">
-        <v>74.45454545454545</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+        <v>74.44444444444444</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>411</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>267600000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>423</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>174</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>69</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>QHtUvT8t</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.5</v>
+        <v>45528.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">sanchez lopez r 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio heliodoro rodriguez lopez
+  santa cruz de tenerife </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23516</v>
+        <v>22824</v>
       </c>
       <c r="F6" t="n">
-        <v>19900</v>
+        <v>14308</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>IHv6nz80</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.35</v>
-      </c>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N6" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="O6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
@@ -1567,26 +1567,26 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>UBD9uzt0</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>x604nX5H</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>148</v>
       </c>
       <c r="X6" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1594,10 +1594,14 @@
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
+          <t>EXuxl1xP</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1606,180 +1610,140 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="n">
-        <v>27.66666666666667</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>185.1111111111111</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>76.55555555555556</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>12444444.44444444</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>78.44444444444444</v>
-      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>24.3125</v>
+        <v>28.22222222222222</v>
       </c>
       <c r="AP6" t="n">
-        <v>179.6875</v>
+        <v>183.1111111111111</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.0625</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="n">
-        <v>70.75</v>
+        <v>70.77777777777777</v>
       </c>
       <c r="AS6" t="n">
-        <v>6357812.5</v>
+        <v>1822222.222222222</v>
       </c>
       <c r="AT6" t="n">
-        <v>76.8125</v>
+        <v>72.11111111111111</v>
       </c>
       <c r="AU6" t="n">
-        <v>27.10526315789474</v>
+        <v>22.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>181.7368421052632</v>
+        <v>184.1333333333333</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.052631578947368</v>
+        <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>73.52631578947368</v>
+        <v>69.66666666666667</v>
       </c>
       <c r="AY6" t="n">
-        <v>5974210.52631579</v>
+        <v>3886666.666666667</v>
       </c>
       <c r="AZ6" t="n">
-        <v>75.63157894736842</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>28.33333333333333</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>174.3333333333333</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>220</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>11700000</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>220</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>172</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>69</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>81</v>
-      </c>
+        <v>76.86666666666666</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jPRgZOxI</t>
+          <t>jBnLKPNO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45527.6875</v>
+        <v>45528.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">galech i 
+          <t xml:space="preserve">muresan s 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el alcoraz
-  huesca </t>
+          <t xml:space="preserve">estadio la rosaleda
+  malaga </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9100</v>
+        <v>30044</v>
       </c>
       <c r="F7" t="n">
-        <v>6172</v>
+        <v>26066</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
+          <t>25tIqYiJ</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Q51ZzMS6</t>
+          <t>48Z7G1Sf</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="N7" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="T7" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>lfrtHtBn</t>
+          <t>tjXr7SAp</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>vHBWuyve</t>
+          <t>pbHOStFA</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -1794,59 +1758,71 @@
       <c r="Z7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>za7D2lO5</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
+      <c r="AI7" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>972500</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>71.375</v>
+      </c>
       <c r="AO7" t="n">
-        <v>24.91666666666667</v>
+        <v>21.71428571428572</v>
       </c>
       <c r="AP7" t="n">
-        <v>178.75</v>
+        <v>181.4285714285714</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>66.33333333333333</v>
+        <v>64.14285714285714</v>
       </c>
       <c r="AS7" t="n">
-        <v>1304166.666666667</v>
+        <v>1392857.142857143</v>
       </c>
       <c r="AT7" t="n">
-        <v>70.83333333333333</v>
+        <v>73.28571428571429</v>
       </c>
       <c r="AU7" t="n">
-        <v>26.25</v>
+        <v>20.46153846153846</v>
       </c>
       <c r="AV7" t="n">
-        <v>180.75</v>
+        <v>178.8461538461538</v>
       </c>
       <c r="AW7" t="n">
         <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>68.5</v>
+        <v>64.84615384615384</v>
       </c>
       <c r="AY7" t="n">
-        <v>1515625</v>
+        <v>1555769.230769231</v>
       </c>
       <c r="AZ7" t="n">
-        <v>70.875</v>
+        <v>77.61538461538461</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -1866,84 +1842,84 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45527.6875</v>
+        <v>45528.6875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">rojas j  a 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42714</v>
+        <v>16500</v>
       </c>
       <c r="F8" t="n">
-        <v>34004</v>
+        <v>9529</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1.41</v>
+        <v>0.67</v>
       </c>
       <c r="L8" t="n">
-        <v>1.16</v>
+        <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N8" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>16</v>
       </c>
       <c r="T8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -1960,79 +1936,91 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>24.66666666666667</v>
+        <v>26.55555555555556</v>
       </c>
       <c r="AD8" t="n">
-        <v>186</v>
+        <v>180.4444444444445</v>
       </c>
       <c r="AE8" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>74</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>7963888.888888889</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>77</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>29.77777777777778</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>178.8888888888889</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.444444444444444</v>
       </c>
-      <c r="AF8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11677777.77777778</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>75.77777777777777</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>6888888.888888889</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>76.55555555555556</v>
+      </c>
       <c r="AO8" t="n">
-        <v>27.8</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="AP8" t="n">
-        <v>181.0666666666667</v>
+        <v>179.1666666666667</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
-        <v>77.06666666666666</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="AS8" t="n">
-        <v>12813333.33333333</v>
+        <v>6772916.666666667</v>
       </c>
       <c r="AT8" t="n">
-        <v>80.26666666666667</v>
+        <v>77.41666666666667</v>
       </c>
       <c r="AU8" t="n">
-        <v>28.75</v>
+        <v>28.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>182.5</v>
+        <v>176.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>77.08333333333333</v>
+        <v>75.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>10491666.66666667</v>
+        <v>6730000</v>
       </c>
       <c r="AZ8" t="n">
-        <v>79.58333333333333</v>
+        <v>76</v>
       </c>
       <c r="BA8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB8" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="BC8" t="n">
         <v>2</v>
@@ -2044,117 +2032,121 @@
         <v>78</v>
       </c>
       <c r="BF8" t="n">
-        <v>14000000</v>
+        <v>17000000</v>
       </c>
       <c r="BG8" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BH8" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BI8" t="n">
-        <v>183</v>
+        <v>182.5</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BK8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL8" t="n">
-        <v>233</v>
+        <v>133</v>
       </c>
       <c r="BM8" t="n">
-        <v>44500000</v>
+        <v>4750000</v>
       </c>
       <c r="BN8" t="n">
-        <v>236</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>OxQ1X27U</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45527.58333333334</v>
+        <v>45528.6875</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez a 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sardinero
-  santander </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22222</v>
+        <v>40000</v>
       </c>
       <c r="F9" t="n">
-        <v>19205</v>
+        <v>20900</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>nVpEwOrl</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>OEsEpExD</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.03</v>
+      </c>
       <c r="M9" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="N9" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="O9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>rak12p9n</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>YB3UTO7e</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>148</v>
       </c>
       <c r="X9" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -2162,12 +2154,12 @@
       <c r="Z9" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
@@ -2175,155 +2167,183 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>182.125</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>79.125</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>23025000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>26.17647058823529</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>178.5882352941177</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>70.29411764705883</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2370588.235294118</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>74.05882352941177</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>15505000</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="BA9" t="n">
         <v>26</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>180.375</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>68.625</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1675000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>74.125</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>25.35714285714286</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>180.2142857142857</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>67</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>23.11111111111111</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>66</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1869444.444444444</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>73.22222222222223</v>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
+      <c r="BB9" t="n">
+        <v>178</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>74</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>178.25</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>305</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>53500000</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>327</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45527.58333333334</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">gil manzano j 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>24791</v>
+        <v>55926</v>
       </c>
       <c r="F10" t="n">
-        <v>23519</v>
+        <v>46448</v>
       </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M10" t="n">
+        <v>63</v>
+      </c>
+      <c r="N10" t="n">
+        <v>37</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="M10" t="n">
-        <v>49</v>
-      </c>
-      <c r="N10" t="n">
-        <v>51</v>
-      </c>
-      <c r="O10" t="n">
-        <v>7</v>
-      </c>
-      <c r="P10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>5</v>
-      </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
         <v>11</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="W10" t="n">
@@ -2340,14 +2360,10 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
@@ -2355,151 +2371,147 @@
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>22.125</v>
+        <v>25.11111111111111</v>
       </c>
       <c r="AJ10" t="n">
+        <v>183.8888888888889</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>77.77777777777777</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>22722222.22222222</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>82</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>7785000</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>183.1363636363636</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.318181818181818</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>74</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>11668181.81818182</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>79.90909090909091</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>331</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>241500000</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>353</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BI10" t="n">
         <v>182.25</v>
       </c>
-      <c r="AK10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>72</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>11602500</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>180.1</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="BJ10" t="n">
         <v>1.5</v>
       </c>
-      <c r="AR10" t="n">
-        <v>74.34999999999999</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>10473750</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>24.88235294117647</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>178.7647058823529</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.058823529411765</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>70.70588235294117</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>6037941.176470588</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>75.94117647058823</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>178.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>146</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>6900000</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>149</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>179.4</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BK10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL10" t="n">
-        <v>376</v>
+        <v>312</v>
       </c>
       <c r="BM10" t="n">
-        <v>47000000</v>
+        <v>85000000</v>
       </c>
       <c r="BN10" t="n">
-        <v>388</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>fcYpyo85</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45523.6875</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">barrera r 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadi ciutat de valencia
+  valencia </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23000</v>
+        <v>26354</v>
       </c>
       <c r="F11" t="n">
-        <v>21566</v>
+        <v>14068</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.97</v>
-      </c>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>44</v>
       </c>
@@ -2507,38 +2519,38 @@
         <v>56</v>
       </c>
       <c r="O11" t="n">
+        <v>17</v>
+      </c>
+      <c r="P11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6</v>
+      </c>
+      <c r="R11" t="n">
         <v>8</v>
       </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>5</v>
-      </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Ii1Om118</t>
+          <t>fiZxGYJ3</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>84cvAG3H</t>
         </is>
       </c>
       <c r="W11" t="n">
         <v>148</v>
       </c>
       <c r="X11" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -2548,10 +2560,14 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
@@ -2559,80 +2575,66 @@
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>28.22222222222222</v>
+        <v>28.875</v>
       </c>
       <c r="AJ11" t="n">
-        <v>182.3333333333333</v>
+        <v>182.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.333333333333333</v>
+        <v>1.125</v>
       </c>
       <c r="AL11" t="n">
-        <v>81.33333333333333</v>
+        <v>74.25</v>
       </c>
       <c r="AM11" t="n">
-        <v>30055555.55555556</v>
+        <v>5112500</v>
       </c>
       <c r="AN11" t="n">
-        <v>83.33333333333333</v>
+        <v>75.25</v>
       </c>
       <c r="AO11" t="n">
-        <v>23.5</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AP11" t="n">
-        <v>179.25</v>
+        <v>180.0909090909091</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.416666666666667</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
-        <v>74.75</v>
+        <v>67.18181818181819</v>
       </c>
       <c r="AS11" t="n">
-        <v>11625000</v>
+        <v>1709090.909090909</v>
       </c>
       <c r="AT11" t="n">
-        <v>80.5</v>
+        <v>72</v>
       </c>
       <c r="AU11" t="n">
-        <v>26.10526315789474</v>
+        <v>26.46153846153846</v>
       </c>
       <c r="AV11" t="n">
-        <v>180.1052631578947</v>
+        <v>179.3076923076923</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.684210526315789</v>
+        <v>1</v>
       </c>
       <c r="AX11" t="n">
-        <v>79.15789473684211</v>
+        <v>70.15384615384616</v>
       </c>
       <c r="AY11" t="n">
-        <v>25078947.36842105</v>
+        <v>2317307.692307692</v>
       </c>
       <c r="AZ11" t="n">
-        <v>82.52631578947368</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>183</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>233</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>44500000</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>236</v>
-      </c>
+        <v>72.53846153846153</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr"/>
       <c r="BJ11" t="inlineStr"/>
@@ -2644,78 +2646,80 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>IZqoAH3k</t>
+          <t>QwI4i6hn</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45523.64583333334</v>
+        <v>45528.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">de la fuente ramos o 
+          <t xml:space="preserve">perez m 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo pepico amat
-  elda </t>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4038</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>29029</v>
+      </c>
+      <c r="F12" t="n">
+        <v>20890</v>
+      </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>8WUSyF3F</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>IHv6nz80</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="N12" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="O12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q12" t="n">
         <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>hh4xt2Df</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>UBD9uzt0</t>
         </is>
       </c>
       <c r="W12" t="n">
@@ -2730,22 +2734,30 @@
       <c r="Z12" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>4jl02tPF</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>178.7</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2395000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>73.59999999999999</v>
+      </c>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
@@ -2753,40 +2765,40 @@
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
-        <v>28.11111111111111</v>
+        <v>25</v>
       </c>
       <c r="AP12" t="n">
-        <v>177.5</v>
+        <v>178</v>
       </c>
       <c r="AQ12" t="n">
         <v>1</v>
       </c>
       <c r="AR12" t="n">
-        <v>66.27777777777777</v>
+        <v>69.44444444444444</v>
       </c>
       <c r="AS12" t="n">
-        <v>1244722.222222222</v>
+        <v>2577777.777777778</v>
       </c>
       <c r="AT12" t="n">
-        <v>69.27777777777777</v>
+        <v>74</v>
       </c>
       <c r="AU12" t="n">
-        <v>30.14285714285714</v>
+        <v>28.05882352941176</v>
       </c>
       <c r="AV12" t="n">
-        <v>184.5714285714286</v>
+        <v>178.2941176470588</v>
       </c>
       <c r="AW12" t="n">
         <v>1</v>
       </c>
       <c r="AX12" t="n">
-        <v>71.42857142857143</v>
+        <v>66.11764705882354</v>
       </c>
       <c r="AY12" t="n">
-        <v>1642857.142857143</v>
+        <v>935588.2352941176</v>
       </c>
       <c r="AZ12" t="n">
-        <v>72.85714285714286</v>
+        <v>68.94117647058823</v>
       </c>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
@@ -2806,89 +2818,87 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>fqgCMogC</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45523.58333333334</v>
+        <v>45528.5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">fuentes molina a 
   esp </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio municipal da malata
+  ferrol </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>27618</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>10450</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7397</v>
+      </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>zcgwCMgS</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.26</v>
-      </c>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N13" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O13" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
         <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>61Od00Pr</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>K4dMCgFa</t>
         </is>
       </c>
       <c r="W13" t="n">
         <v>148</v>
       </c>
       <c r="X13" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2898,210 +2908,182 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="AC13" t="n">
-        <v>24.88888888888889</v>
+        <v>26.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>178.8888888888889</v>
+        <v>179.125</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>71.44444444444444</v>
+        <v>66.625</v>
       </c>
       <c r="AG13" t="n">
-        <v>3622222.222222222</v>
+        <v>1190625</v>
       </c>
       <c r="AH13" t="n">
-        <v>75.55555555555556</v>
+        <v>69.875</v>
       </c>
       <c r="AI13" t="n">
-        <v>25.66666666666667</v>
+        <v>26.44444444444444</v>
       </c>
       <c r="AJ13" t="n">
-        <v>183.7777777777778</v>
+        <v>179.4444444444445</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AL13" t="n">
-        <v>72.11111111111111</v>
+        <v>73</v>
       </c>
       <c r="AM13" t="n">
-        <v>4500000</v>
+        <v>4133333.333333333</v>
       </c>
       <c r="AN13" t="n">
-        <v>76.44444444444444</v>
+        <v>75.11111111111111</v>
       </c>
       <c r="AO13" t="n">
-        <v>24.4375</v>
+        <v>26.78571428571428</v>
       </c>
       <c r="AP13" t="n">
-        <v>180.8125</v>
+        <v>175.8571428571429</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.0625</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
-        <v>69.875</v>
+        <v>67.92857142857143</v>
       </c>
       <c r="AS13" t="n">
-        <v>3392187.5</v>
+        <v>1678571.428571429</v>
       </c>
       <c r="AT13" t="n">
-        <v>76.125</v>
+        <v>70.85714285714286</v>
       </c>
       <c r="AU13" t="n">
-        <v>23.90909090909091</v>
+        <v>25.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>178.8181818181818</v>
+        <v>181.1818181818182</v>
       </c>
       <c r="AW13" t="n">
-        <v>1</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="AX13" t="n">
-        <v>69.45454545454545</v>
+        <v>70.68181818181819</v>
       </c>
       <c r="AY13" t="n">
-        <v>3227272.727272727</v>
+        <v>3993181.818181818</v>
       </c>
       <c r="AZ13" t="n">
-        <v>76</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>178</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>142</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>4600000</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>142</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>26</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>178</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>74</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>75</v>
-      </c>
+        <v>74.45454545454545</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45522.6875</v>
+        <v>45528.5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26020</v>
+        <v>23516</v>
       </c>
       <c r="F14" t="n">
-        <v>23010</v>
+        <v>19900</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>4jDQxrbf</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
       <c r="K14" t="n">
-        <v>0.84</v>
+        <v>1.52</v>
       </c>
       <c r="L14" t="n">
-        <v>0.89</v>
+        <v>0.35</v>
       </c>
       <c r="M14" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="N14" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="O14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q14" t="n">
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="W14" t="n">
@@ -3116,213 +3098,203 @@
       <c r="Z14" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>YT0e2vMU</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="AC14" t="n">
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="n">
         <v>27.66666666666667</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AJ14" t="n">
         <v>185.1111111111111</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AK14" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AL14" t="n">
         <v>76.55555555555556</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AM14" t="n">
         <v>12444444.44444444</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AN14" t="n">
         <v>78.44444444444444</v>
       </c>
-      <c r="AI14" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>80850000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>88.7</v>
-      </c>
       <c r="AO14" t="n">
-        <v>26.36842105263158</v>
+        <v>24.3125</v>
       </c>
       <c r="AP14" t="n">
-        <v>182.8947368421053</v>
+        <v>179.6875</v>
       </c>
       <c r="AQ14" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6357812.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>76.8125</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>27.10526315789474</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>181.7368421052632</v>
+      </c>
+      <c r="AW14" t="n">
         <v>1.052631578947368</v>
       </c>
-      <c r="AR14" t="n">
-        <v>73.73684210526316</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>6868947.368421053</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>76.68421052631579</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>24.52631578947368</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>177.1052631578947</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.052631578947369</v>
-      </c>
       <c r="AX14" t="n">
-        <v>77.89473684210526</v>
+        <v>73.52631578947368</v>
       </c>
       <c r="AY14" t="n">
-        <v>34988157.89473684</v>
+        <v>5974210.52631579</v>
       </c>
       <c r="AZ14" t="n">
-        <v>83.36842105263158</v>
+        <v>75.63157894736842</v>
       </c>
       <c r="BA14" t="n">
+        <v>28.33333333333333</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>174.3333333333333</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>220</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>11700000</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>220</v>
+      </c>
+      <c r="BH14" t="n">
         <v>21</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BI14" t="n">
         <v>172</v>
       </c>
-      <c r="BC14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE14" t="n">
+      <c r="BJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL14" t="n">
         <v>69</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BM14" t="n">
         <v>3400000</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BN14" t="n">
         <v>81</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>181</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>168</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>108500000</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>nigFFwtS</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45522.60416666666</v>
+        <v>45527.6875</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">palencia caballero d 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio manuel martinez valero
-  elche </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>31388</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>42714</v>
+      </c>
+      <c r="F15" t="n">
+        <v>34004</v>
+      </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.16</v>
+      </c>
       <c r="M15" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="O15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S15" t="n">
         <v>16</v>
       </c>
       <c r="T15" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>zT9gi7i9</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>lfrtHtBn</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="W15" t="n">
         <v>148</v>
       </c>
       <c r="X15" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -3332,166 +3304,194 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>G8FL0ShI</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>za7D2lO5</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="n">
+      <c r="AC15" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>186</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11677777.77777778</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>181.0666666666667</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>77.06666666666666</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>12813333.33333333</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>80.26666666666667</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>77.08333333333333</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10491666.66666667</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>79.58333333333333</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>184</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>78</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH15" t="n">
         <v>27</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>179.875</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>67.875</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1365625</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>70.625</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>179.1333333333333</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>67.93333333333334</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1441666.666666667</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>179.6666666666667</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>65.66666666666667</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1277777.777777778</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>71.33333333333333</v>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
-      <c r="BK15" t="inlineStr"/>
-      <c r="BL15" t="inlineStr"/>
-      <c r="BM15" t="inlineStr"/>
-      <c r="BN15" t="inlineStr"/>
+      <c r="BI15" t="n">
+        <v>183</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>233</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>236</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hIsKeIld</t>
+          <t>jPRgZOxI</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45522.60416666666</v>
+        <v>45527.6875</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">de aza m 
+          <t xml:space="preserve">galech i 
   esp </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el plantio
-  burgos </t>
+          <t xml:space="preserve">estadio el alcoraz
+  huesca </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12194</v>
+        <v>9100</v>
       </c>
       <c r="F16" t="n">
-        <v>9642</v>
+        <v>6172</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>vTxTEFi6</t>
+          <t>UytPaaEP</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>IJyXDZ6C</t>
+          <t>Q51ZzMS6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="N16" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="O16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
         <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>l6JQtDqc</t>
+          <t>lfrtHtBn</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>M1vEw5An</t>
+          <t>vHBWuyve</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -3506,12 +3506,12 @@
       <c r="Z16" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>4jl02tPF</t>
-        </is>
-      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
@@ -3525,40 +3525,40 @@
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="n">
-        <v>22.625</v>
+        <v>24.91666666666667</v>
       </c>
       <c r="AP16" t="n">
-        <v>183.625</v>
+        <v>178.75</v>
       </c>
       <c r="AQ16" t="n">
         <v>1</v>
       </c>
       <c r="AR16" t="n">
-        <v>66.5</v>
+        <v>66.33333333333333</v>
       </c>
       <c r="AS16" t="n">
-        <v>1884375</v>
+        <v>1304166.666666667</v>
       </c>
       <c r="AT16" t="n">
-        <v>73.75</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="AU16" t="n">
-        <v>25.16666666666667</v>
+        <v>26.25</v>
       </c>
       <c r="AV16" t="n">
-        <v>181</v>
+        <v>180.75</v>
       </c>
       <c r="AW16" t="n">
         <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>65</v>
+        <v>68.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>858333.3333333334</v>
+        <v>1515625</v>
       </c>
       <c r="AZ16" t="n">
-        <v>69.66666666666667</v>
+        <v>70.875</v>
       </c>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
@@ -3578,91 +3578,87 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>OxQ1X27U</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45522.58333333334</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">sanchez a 
   esp </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">estadio el sardinero
+  santander </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>40000</v>
+        <v>22222</v>
       </c>
       <c r="F17" t="n">
-        <v>31763</v>
+        <v>19205</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>nVpEwOrl</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.5</v>
-      </c>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="N17" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="O17" t="n">
+        <v>15</v>
+      </c>
+      <c r="P17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
         <v>11</v>
       </c>
-      <c r="P17" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>5</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>14</v>
       </c>
-      <c r="T17" t="n">
-        <v>21</v>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>rak12p9n</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>YB3UTO7e</t>
         </is>
       </c>
       <c r="W17" t="n">
         <v>148</v>
       </c>
       <c r="X17" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -3673,208 +3669,172 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="AC17" t="n">
-        <v>25.88888888888889</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>182</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.888888888888889</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>77.66666666666667</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>22555555.55555556</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>81.22222222222223</v>
-      </c>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>28.125</v>
+        <v>26</v>
       </c>
       <c r="AJ17" t="n">
-        <v>178.125</v>
+        <v>180.375</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.375</v>
+        <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>75.125</v>
+        <v>68.625</v>
       </c>
       <c r="AM17" t="n">
-        <v>6887500</v>
+        <v>1675000</v>
       </c>
       <c r="AN17" t="n">
-        <v>76.75</v>
+        <v>74.125</v>
       </c>
       <c r="AO17" t="n">
-        <v>23.125</v>
+        <v>25.35714285714286</v>
       </c>
       <c r="AP17" t="n">
-        <v>179.25</v>
+        <v>180.2142857142857</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.375</v>
+        <v>1</v>
       </c>
       <c r="AR17" t="n">
-        <v>74.5</v>
+        <v>67</v>
       </c>
       <c r="AS17" t="n">
-        <v>17412500</v>
+        <v>1800000</v>
       </c>
       <c r="AT17" t="n">
-        <v>81.1875</v>
+        <v>73.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>28.06666666666667</v>
+        <v>23.11111111111111</v>
       </c>
       <c r="AV17" t="n">
-        <v>177.8666666666667</v>
+        <v>182.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.133333333333333</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>73.86666666666666</v>
+        <v>66</v>
       </c>
       <c r="AY17" t="n">
-        <v>4980000</v>
+        <v>1869444.444444444</v>
       </c>
       <c r="AZ17" t="n">
-        <v>75.66666666666667</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>181.75</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>314</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>89000000</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>329</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>181</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>137</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>11550000</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>151</v>
-      </c>
+        <v>73.22222222222223</v>
+      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>0fJlUxeL</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45522.5</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">moreno a 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sardinero
-  santander </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>22222</v>
+        <v>24791</v>
       </c>
       <c r="F18" t="n">
-        <v>19697</v>
+        <v>23519</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>nVpEwOrl</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>nF2Vy2D0</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.71</v>
+      </c>
       <c r="M18" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="N18" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="O18" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P18" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q18" t="n">
         <v>5</v>
       </c>
       <c r="R18" t="n">
+        <v>5</v>
+      </c>
+      <c r="S18" t="n">
         <v>9</v>
       </c>
-      <c r="S18" t="n">
-        <v>18</v>
-      </c>
       <c r="T18" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>rak12p9n</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>x604nX5H</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="W18" t="n">
         <v>148</v>
       </c>
       <c r="X18" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -3882,10 +3842,14 @@
       <c r="Z18" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>EXuxl1xP</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3894,147 +3858,191 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>72</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>11602500</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>78.5</v>
+      </c>
       <c r="AO18" t="n">
-        <v>26.47058823529412</v>
+        <v>26.9</v>
       </c>
       <c r="AP18" t="n">
-        <v>180.6470588235294</v>
+        <v>180.1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>66.88235294117646</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>1427941.176470588</v>
+        <v>10473750</v>
       </c>
       <c r="AT18" t="n">
-        <v>72.64705882352941</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>22.57142857142857</v>
+        <v>24.88235294117647</v>
       </c>
       <c r="AV18" t="n">
-        <v>184.7619047619048</v>
+        <v>178.7647058823529</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.047619047619048</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="AX18" t="n">
-        <v>69.0952380952381</v>
+        <v>70.70588235294117</v>
       </c>
       <c r="AY18" t="n">
-        <v>3557142.857142857</v>
+        <v>6037941.176470588</v>
       </c>
       <c r="AZ18" t="n">
-        <v>76.42857142857143</v>
-      </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="inlineStr"/>
-      <c r="BM18" t="inlineStr"/>
-      <c r="BN18" t="inlineStr"/>
+        <v>75.94117647058823</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>146</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>149</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>376</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>388</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>0I1yLYH7</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45522.5</v>
+        <v>45523.6875</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">guzman mansilla j  l 
+          <t xml:space="preserve">cuadra g 
   esp </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el molinon
-  gijon </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>29029</v>
+        <v>23000</v>
       </c>
       <c r="F19" t="n">
-        <v>23319</v>
+        <v>21566</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.97</v>
+      </c>
       <c r="M19" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="N19" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="O19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>S0PIZoj2</t>
+          <t>Ii1Om118</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>fiZxGYJ3</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="W19" t="n">
         <v>148</v>
       </c>
       <c r="X19" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -4042,79 +4050,93 @@
       <c r="Z19" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="AC19" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>179.1111111111111</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>70.66666666666667</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2372222.222222222</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>73.11111111111111</v>
-      </c>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="n">
+        <v>28.22222222222222</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>81.33333333333333</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>30055555.55555556</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>83.33333333333333</v>
+      </c>
       <c r="AO19" t="n">
-        <v>24.18181818181818</v>
+        <v>23.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>177.3636363636364</v>
+        <v>179.25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="AR19" t="n">
-        <v>67.63636363636364</v>
+        <v>74.75</v>
       </c>
       <c r="AS19" t="n">
-        <v>1788636.363636364</v>
+        <v>11625000</v>
       </c>
       <c r="AT19" t="n">
-        <v>74.27272727272727</v>
+        <v>80.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>23</v>
+        <v>26.10526315789474</v>
       </c>
       <c r="AV19" t="n">
-        <v>177.5833333333333</v>
+        <v>180.1052631578947</v>
       </c>
       <c r="AW19" t="n">
-        <v>1</v>
+        <v>1.684210526315789</v>
       </c>
       <c r="AX19" t="n">
-        <v>67.5</v>
+        <v>79.15789473684211</v>
       </c>
       <c r="AY19" t="n">
-        <v>1983333.333333333</v>
+        <v>25078947.36842105</v>
       </c>
       <c r="AZ19" t="n">
-        <v>73.25</v>
-      </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
+        <v>82.52631578947368</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>233</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>236</v>
+      </c>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr"/>
       <c r="BJ19" t="inlineStr"/>
@@ -4126,91 +4148,85 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>IZqoAH3k</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45521.6875</v>
+        <v>45523.64583333334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">de la fuente ramos o 
   esp </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio nuevo pepico amat
+  elda </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>49430</v>
-      </c>
-      <c r="F20" t="n">
-        <v>46673</v>
-      </c>
+        <v>4038</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>8WUSyF3F</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2.75</v>
-      </c>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="N20" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="P20" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S20" t="n">
         <v>11</v>
       </c>
       <c r="T20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>hh4xt2Df</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>UBD9uzt0</t>
         </is>
       </c>
       <c r="W20" t="n">
         <v>148</v>
       </c>
       <c r="X20" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -4220,32 +4236,20 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>4jl02tPF</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="AC20" t="n">
-        <v>22.125</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>182.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>72</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>11602500</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>78.5</v>
-      </c>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
@@ -4253,165 +4257,135 @@
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="n">
-        <v>23.625</v>
+        <v>28.11111111111111</v>
       </c>
       <c r="AP20" t="n">
-        <v>178.875</v>
+        <v>177.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.0625</v>
+        <v>1</v>
       </c>
       <c r="AR20" t="n">
-        <v>69.4375</v>
+        <v>66.27777777777777</v>
       </c>
       <c r="AS20" t="n">
-        <v>4559062.5</v>
+        <v>1244722.222222222</v>
       </c>
       <c r="AT20" t="n">
-        <v>76.1875</v>
+        <v>69.27777777777777</v>
       </c>
       <c r="AU20" t="n">
-        <v>21.3125</v>
+        <v>30.14285714285714</v>
       </c>
       <c r="AV20" t="n">
-        <v>182.25</v>
+        <v>184.5714285714286</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.6875</v>
+        <v>1</v>
       </c>
       <c r="AX20" t="n">
-        <v>73.75</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="AY20" t="n">
-        <v>31759375</v>
+        <v>1642857.142857143</v>
       </c>
       <c r="AZ20" t="n">
-        <v>82.125</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>179.4</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>376</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>47000000</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>388</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>397</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>257600000</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>433</v>
-      </c>
+        <v>72.85714285714286</v>
+      </c>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45523.58333333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F21" t="n">
-        <v>19561</v>
-      </c>
+        <v>27618</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1.61</v>
+        <v>0.57</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0.26</v>
       </c>
       <c r="M21" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="N21" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="O21" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
         <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="W21" t="n">
@@ -4426,65 +4400,93 @@
       <c r="Z21" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>178.8888888888889</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>71.44444444444444</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3622222.222222222</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>75.55555555555556</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>76.44444444444444</v>
+      </c>
       <c r="AO21" t="n">
-        <v>24.875</v>
+        <v>24.4375</v>
       </c>
       <c r="AP21" t="n">
-        <v>177.875</v>
+        <v>180.8125</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1</v>
+        <v>1.0625</v>
       </c>
       <c r="AR21" t="n">
-        <v>72.3125</v>
+        <v>69.875</v>
       </c>
       <c r="AS21" t="n">
-        <v>7870312.5</v>
+        <v>3392187.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>78.1875</v>
+        <v>76.125</v>
       </c>
       <c r="AU21" t="n">
-        <v>25.21052631578947</v>
+        <v>23.90909090909091</v>
       </c>
       <c r="AV21" t="n">
-        <v>183.6315789473684</v>
+        <v>178.8181818181818</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.052631578947368</v>
+        <v>1</v>
       </c>
       <c r="AX21" t="n">
-        <v>71.05263157894737</v>
+        <v>69.45454545454545</v>
       </c>
       <c r="AY21" t="n">
-        <v>5059210.52631579</v>
+        <v>3227272.727272727</v>
       </c>
       <c r="AZ21" t="n">
-        <v>74.94736842105263</v>
+        <v>76</v>
       </c>
       <c r="BA21" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>176.5</v>
+        <v>178</v>
       </c>
       <c r="BC21" t="n">
         <v>1</v>
@@ -4493,106 +4495,124 @@
         <v>2</v>
       </c>
       <c r="BE21" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="BF21" t="n">
-        <v>7600000</v>
+        <v>4600000</v>
       </c>
       <c r="BG21" t="n">
-        <v>145</v>
-      </c>
-      <c r="BH21" t="inlineStr"/>
-      <c r="BI21" t="inlineStr"/>
-      <c r="BJ21" t="inlineStr"/>
-      <c r="BK21" t="inlineStr"/>
-      <c r="BL21" t="inlineStr"/>
-      <c r="BM21" t="inlineStr"/>
-      <c r="BN21" t="inlineStr"/>
+        <v>142</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>178</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>74</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tvOEHaBF</t>
+          <t>M3h3GWnS</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45522.6875</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">lax franco s 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de riazor
-  la coruna </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>34889</v>
+        <v>26020</v>
       </c>
       <c r="F22" t="n">
-        <v>25715</v>
+        <v>23010</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Q51ZzMS6</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SzYzw34K</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.89</v>
+      </c>
       <c r="M22" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="N22" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="O22" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
         <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T22" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>vHBWuyve</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>QmLgLqap</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="W22" t="n">
         <v>148</v>
       </c>
       <c r="X22" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -4600,136 +4620,208 @@
       <c r="Z22" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>76.55555555555556</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>12444444.44444444</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>78.44444444444444</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>80850000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>26.36842105263158</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>182.8947368421053</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>73.73684210526316</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>6868947.368421053</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>76.68421052631579</v>
+      </c>
       <c r="AU22" t="n">
-        <v>25.45</v>
+        <v>24.52631578947368</v>
       </c>
       <c r="AV22" t="n">
-        <v>177.55</v>
+        <v>177.1052631578947</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.3</v>
+        <v>2.052631578947369</v>
       </c>
       <c r="AX22" t="n">
+        <v>77.89473684210526</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>34988157.89473684</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>83.36842105263158</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>172</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE22" t="n">
         <v>69</v>
       </c>
-      <c r="AY22" t="n">
-        <v>2176250</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="BA22" t="inlineStr"/>
-      <c r="BB22" t="inlineStr"/>
-      <c r="BC22" t="inlineStr"/>
-      <c r="BD22" t="inlineStr"/>
-      <c r="BE22" t="inlineStr"/>
-      <c r="BF22" t="inlineStr"/>
-      <c r="BG22" t="inlineStr"/>
-      <c r="BH22" t="inlineStr"/>
-      <c r="BI22" t="inlineStr"/>
-      <c r="BJ22" t="inlineStr"/>
-      <c r="BK22" t="inlineStr"/>
-      <c r="BL22" t="inlineStr"/>
-      <c r="BM22" t="inlineStr"/>
-      <c r="BN22" t="inlineStr"/>
+      <c r="BF22" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>168</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>108500000</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>dQ4KOGIr</t>
+          <t>hIsKeIld</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45521.5</v>
+        <v>45522.60416666666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">mallo e 
+          <t xml:space="preserve">de aza m 
   esp </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de ipurua
-  eibar </t>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8164</v>
+        <v>12194</v>
       </c>
       <c r="F23" t="n">
-        <v>3538</v>
+        <v>9642</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>OEsEpExD</t>
+          <t>vTxTEFi6</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>QyHHzdwl</t>
+          <t>IJyXDZ6C</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="N23" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="O23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="n">
+        <v>6</v>
+      </c>
+      <c r="R23" t="n">
         <v>3</v>
       </c>
-      <c r="R23" t="n">
-        <v>4</v>
-      </c>
       <c r="S23" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>YB3UTO7e</t>
+          <t>l6JQtDqc</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>EF6Hrtsn</t>
+          <t>M1vEw5An</t>
         </is>
       </c>
       <c r="W23" t="n">
@@ -4744,30 +4836,18 @@
       <c r="Z23" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="n">
-        <v>25.125</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>180.75</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>68</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1625000</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>74.375</v>
-      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
@@ -4775,29 +4855,41 @@
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="n">
-        <v>24.85714285714286</v>
+        <v>22.625</v>
       </c>
       <c r="AP23" t="n">
-        <v>182.7857142857143</v>
+        <v>183.625</v>
       </c>
       <c r="AQ23" t="n">
         <v>1</v>
       </c>
       <c r="AR23" t="n">
-        <v>66.85714285714286</v>
+        <v>66.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>1801785.714285714</v>
+        <v>1884375</v>
       </c>
       <c r="AT23" t="n">
-        <v>72.07142857142857</v>
-      </c>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr"/>
+        <v>73.75</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>858333.3333333334</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>69.66666666666667</v>
+      </c>
       <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr"/>
@@ -4816,80 +4908,78 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>vkYg8eY1</t>
+          <t>nigFFwtS</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45521.5</v>
+        <v>45522.60416666666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">sesma espinosa m 
+          <t xml:space="preserve">palencia caballero d 
   esp </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal da malata
-  ferrol </t>
+          <t xml:space="preserve">estadio manuel martinez valero
+  elche </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10450</v>
-      </c>
-      <c r="F24" t="n">
-        <v>7541</v>
-      </c>
+        <v>31388</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>zcgwCMgS</t>
+          <t>4jl02tPF</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>25tIqYiJ</t>
+          <t>UytPaaEP</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="N24" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="O24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S24" t="n">
         <v>16</v>
       </c>
       <c r="T24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>61Od00Pr</t>
+          <t>zT9gi7i9</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>tjXr7SAp</t>
+          <t>lfrtHtBn</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -4906,69 +4996,73 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>179.125</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>66.625</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1190625</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>69.875</v>
-      </c>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1365625</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>70.625</v>
+      </c>
       <c r="AO24" t="n">
-        <v>27.72727272727273</v>
+        <v>25.8</v>
       </c>
       <c r="AP24" t="n">
-        <v>178</v>
+        <v>179.1333333333333</v>
       </c>
       <c r="AQ24" t="n">
         <v>1</v>
       </c>
       <c r="AR24" t="n">
-        <v>66.54545454545455</v>
+        <v>67.93333333333334</v>
       </c>
       <c r="AS24" t="n">
-        <v>959090.9090909091</v>
+        <v>1441666.666666667</v>
       </c>
       <c r="AT24" t="n">
-        <v>68.63636363636364</v>
+        <v>73.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>21.66666666666667</v>
+        <v>24</v>
       </c>
       <c r="AV24" t="n">
-        <v>181.8333333333333</v>
+        <v>179.6666666666667</v>
       </c>
       <c r="AW24" t="n">
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>64.16666666666667</v>
+        <v>65.66666666666667</v>
       </c>
       <c r="AY24" t="n">
-        <v>1391666.666666667</v>
+        <v>1277777.777777778</v>
       </c>
       <c r="AZ24" t="n">
-        <v>73.33333333333333</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="inlineStr"/>
@@ -4988,63 +5082,63 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>Eax2EqHs</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45520.6875</v>
+        <v>45522.58333333334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>32392</v>
+        <v>40000</v>
       </c>
       <c r="F25" t="n">
-        <v>24843</v>
+        <v>31763</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.86</v>
+        <v>1.55</v>
       </c>
       <c r="L25" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="N25" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="O25" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P25" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Q25" t="n">
         <v>5</v>
@@ -5056,16 +5150,16 @@
         <v>14</v>
       </c>
       <c r="T25" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -5080,196 +5174,204 @@
       <c r="Z25" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
+      <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>22555555.55555556</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>81.22222222222223</v>
+      </c>
       <c r="AI25" t="n">
-        <v>25.33333333333333</v>
+        <v>28.125</v>
       </c>
       <c r="AJ25" t="n">
-        <v>185.5555555555555</v>
+        <v>178.125</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.444444444444444</v>
+        <v>1.375</v>
       </c>
       <c r="AL25" t="n">
-        <v>75.11111111111111</v>
+        <v>75.125</v>
       </c>
       <c r="AM25" t="n">
-        <v>10622222.22222222</v>
+        <v>6887500</v>
       </c>
       <c r="AN25" t="n">
-        <v>79.44444444444444</v>
+        <v>76.75</v>
       </c>
       <c r="AO25" t="n">
-        <v>25.27272727272727</v>
+        <v>23.125</v>
       </c>
       <c r="AP25" t="n">
-        <v>177</v>
+        <v>179.25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.090909090909091</v>
+        <v>1.375</v>
       </c>
       <c r="AR25" t="n">
-        <v>73.45454545454545</v>
+        <v>74.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>6627272.727272728</v>
+        <v>17412500</v>
       </c>
       <c r="AT25" t="n">
-        <v>75.90909090909091</v>
+        <v>81.1875</v>
       </c>
       <c r="AU25" t="n">
-        <v>27.66666666666667</v>
+        <v>28.06666666666667</v>
       </c>
       <c r="AV25" t="n">
-        <v>179</v>
+        <v>177.8666666666667</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.777777777777778</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="AX25" t="n">
-        <v>75.88888888888889</v>
+        <v>73.86666666666666</v>
       </c>
       <c r="AY25" t="n">
-        <v>10522222.22222222</v>
+        <v>4980000</v>
       </c>
       <c r="AZ25" t="n">
-        <v>81</v>
+        <v>75.66666666666667</v>
       </c>
       <c r="BA25" t="n">
-        <v>26.75</v>
+        <v>25</v>
       </c>
       <c r="BB25" t="n">
-        <v>179.5</v>
+        <v>181.75</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="BD25" t="n">
         <v>4</v>
       </c>
       <c r="BE25" t="n">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="BF25" t="n">
-        <v>17700000</v>
+        <v>89000000</v>
       </c>
       <c r="BG25" t="n">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="BH25" t="n">
-        <v>28</v>
+        <v>23.5</v>
       </c>
       <c r="BI25" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="BJ25" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL25" t="n">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="BM25" t="n">
-        <v>21000000</v>
+        <v>11550000</v>
       </c>
       <c r="BN25" t="n">
-        <v>80</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>8QP6JLt3</t>
+          <t>0fJlUxeL</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45520.6875</v>
+        <v>45522.5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">monescillo d 
+          <t xml:space="preserve">moreno a 
   esp </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo mirandilla
-  cadiz </t>
+          <t xml:space="preserve">estadio el sardinero
+  santander </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>20776</v>
+        <v>22222</v>
       </c>
       <c r="F26" t="n">
-        <v>16970</v>
+        <v>19697</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>hdWjLJUJ</t>
+          <t>nVpEwOrl</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>za7D2lO5</t>
+          <t>nF2Vy2D0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="N26" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="O26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
         <v>9</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="T26" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>84cvAG3H</t>
+          <t>rak12p9n</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>4WbDi59E</t>
+          <t>x604nX5H</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -5284,14 +5386,10 @@
       <c r="Z26" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
+      <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
+          <t>EXuxl1xP</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -5300,59 +5398,47 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="n">
-        <v>23.77777777777778</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>175.8888888888889</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>67.88888888888889</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1811111.111111111</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>73.77777777777777</v>
-      </c>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="n">
-        <v>25.5625</v>
+        <v>26.47058823529412</v>
       </c>
       <c r="AP26" t="n">
-        <v>178.8125</v>
+        <v>180.6470588235294</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.1875</v>
+        <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>70</v>
+        <v>66.88235294117646</v>
       </c>
       <c r="AS26" t="n">
-        <v>3395312.5</v>
+        <v>1427941.176470588</v>
       </c>
       <c r="AT26" t="n">
-        <v>75.375</v>
+        <v>72.64705882352941</v>
       </c>
       <c r="AU26" t="n">
-        <v>26.38888888888889</v>
+        <v>22.57142857142857</v>
       </c>
       <c r="AV26" t="n">
-        <v>180.7777777777778</v>
+        <v>184.7619047619048</v>
       </c>
       <c r="AW26" t="n">
-        <v>1</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AX26" t="n">
-        <v>69.61111111111111</v>
+        <v>69.0952380952381</v>
       </c>
       <c r="AY26" t="n">
-        <v>2075000</v>
+        <v>3557142.857142857</v>
       </c>
       <c r="AZ26" t="n">
-        <v>73.33333333333333</v>
+        <v>76.42857142857143</v>
       </c>
       <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="inlineStr"/>
@@ -5372,91 +5458,87 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>0I1yLYH7</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45520.58333333334</v>
+        <v>45522.5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">guzman mansilla j  l 
   esp </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>24791</v>
+        <v>29029</v>
       </c>
       <c r="F27" t="n">
-        <v>22477</v>
+        <v>23319</v>
       </c>
       <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
         <v>2</v>
       </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.8</v>
-      </c>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O27" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T27" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>S0PIZoj2</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>fiZxGYJ3</t>
         </is>
       </c>
       <c r="W27" t="n">
         <v>148</v>
       </c>
       <c r="X27" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -5464,29 +5546,29 @@
       <c r="Z27" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
       <c r="AC27" t="n">
-        <v>26.75</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="AD27" t="n">
-        <v>179.875</v>
+        <v>179.1111111111111</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>75.375</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="AG27" t="n">
-        <v>8650000</v>
+        <v>2372222.222222222</v>
       </c>
       <c r="AH27" t="n">
-        <v>78.25</v>
+        <v>73.11111111111111</v>
       </c>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
@@ -5495,62 +5577,48 @@
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="n">
-        <v>25.5</v>
+        <v>24.18181818181818</v>
       </c>
       <c r="AP27" t="n">
-        <v>181.5555555555555</v>
+        <v>177.3636363636364</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.277777777777778</v>
+        <v>1</v>
       </c>
       <c r="AR27" t="n">
-        <v>72.77777777777777</v>
+        <v>67.63636363636364</v>
       </c>
       <c r="AS27" t="n">
-        <v>9987500</v>
+        <v>1788636.363636364</v>
       </c>
       <c r="AT27" t="n">
-        <v>76.77777777777777</v>
+        <v>74.27272727272727</v>
       </c>
       <c r="AU27" t="n">
-        <v>24.26315789473684</v>
+        <v>23</v>
       </c>
       <c r="AV27" t="n">
-        <v>180.6842105263158</v>
+        <v>177.5833333333333</v>
       </c>
       <c r="AW27" t="n">
         <v>1</v>
       </c>
       <c r="AX27" t="n">
-        <v>71.05263157894737</v>
+        <v>67.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>3814473.684210526</v>
+        <v>1983333.333333333</v>
       </c>
       <c r="AZ27" t="n">
-        <v>75.94736842105263</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>151</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>154</v>
-      </c>
+        <v>73.25</v>
+      </c>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
       <c r="BH27" t="inlineStr"/>
       <c r="BI27" t="inlineStr"/>
       <c r="BJ27" t="inlineStr"/>
@@ -5562,87 +5630,91 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hhbTMfme</t>
+          <t>KbKTWiX8</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45520.58333333334</v>
+        <v>45521.6875</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez diaz m 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de anduva
-  miranda de ebro </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5759</v>
+        <v>49430</v>
       </c>
       <c r="F28" t="n">
-        <v>3005</v>
+        <v>46673</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>48Z7G1Sf</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CWuejruc</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2.75</v>
+      </c>
       <c r="M28" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N28" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P28" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>pbHOStFA</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>vBENkWfS</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="W28" t="n">
         <v>148</v>
       </c>
       <c r="X28" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -5652,137 +5724,201 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11602500</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>78.5</v>
+      </c>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr"/>
-      <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AU28" t="inlineStr"/>
-      <c r="AV28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr"/>
-      <c r="AX28" t="inlineStr"/>
-      <c r="AY28" t="inlineStr"/>
-      <c r="AZ28" t="inlineStr"/>
-      <c r="BA28" t="inlineStr"/>
-      <c r="BB28" t="inlineStr"/>
-      <c r="BC28" t="inlineStr"/>
-      <c r="BD28" t="inlineStr"/>
-      <c r="BE28" t="inlineStr"/>
-      <c r="BF28" t="inlineStr"/>
-      <c r="BG28" t="inlineStr"/>
-      <c r="BH28" t="inlineStr"/>
-      <c r="BI28" t="inlineStr"/>
-      <c r="BJ28" t="inlineStr"/>
-      <c r="BK28" t="inlineStr"/>
-      <c r="BL28" t="inlineStr"/>
-      <c r="BM28" t="inlineStr"/>
-      <c r="BN28" t="inlineStr"/>
+      <c r="AO28" t="n">
+        <v>23.625</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>178.875</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>69.4375</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4559062.5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>76.1875</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>21.3125</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>31759375</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>82.125</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>376</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>388</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>397</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>257600000</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>433</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>tvOEHaBF</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45519.6875</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">lax franco s 
   esp </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">estadio municipal de riazor
+  la coruna </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>60721</v>
+        <v>34889</v>
       </c>
       <c r="F29" t="n">
-        <v>54084</v>
+        <v>25715</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>Q51ZzMS6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.41</v>
-      </c>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="N29" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="O29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P29" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="n">
+        <v>7</v>
+      </c>
+      <c r="R29" t="n">
         <v>4</v>
       </c>
-      <c r="R29" t="n">
-        <v>2</v>
-      </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T29" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>vHBWuyve</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>QmLgLqap</t>
         </is>
       </c>
       <c r="W29" t="n">
         <v>148</v>
       </c>
       <c r="X29" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -5790,203 +5926,147 @@
       <c r="Z29" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="n">
-        <v>25.625</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>182.75</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>17512500</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>81.375</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>23.07692307692308</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>185</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.307692307692308</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>72.76923076923077</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>6384615.384615385</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>79.92307692307692</v>
-      </c>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
       <c r="AU29" t="n">
-        <v>24.35714285714286</v>
+        <v>25.45</v>
       </c>
       <c r="AV29" t="n">
-        <v>180.9285714285714</v>
+        <v>177.55</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.214285714285714</v>
+        <v>1.3</v>
       </c>
       <c r="AX29" t="n">
-        <v>70.71428571428571</v>
+        <v>69</v>
       </c>
       <c r="AY29" t="n">
-        <v>4835714.285714285</v>
+        <v>2176250</v>
       </c>
       <c r="AZ29" t="n">
-        <v>79.14285714285714</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>181.6666666666667</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>216</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>26650000</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>230</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="BI29" t="n">
-        <v>177.6</v>
-      </c>
-      <c r="BJ29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BK29" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>358</v>
-      </c>
-      <c r="BM29" t="n">
-        <v>61400000</v>
-      </c>
-      <c r="BN29" t="n">
-        <v>397</v>
-      </c>
+        <v>75.5</v>
+      </c>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>6eQuWbQ8</t>
+          <t>ruUIA1G6</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45519.64583333334</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">reig s  a 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo los carmenes
-  granada </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>22524</v>
+        <v>23516</v>
       </c>
       <c r="F30" t="n">
-        <v>13265</v>
+        <v>19561</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EXuxl1xP</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>UirAofN6</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
       <c r="M30" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N30" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="O30" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>K4dMCgFa</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>ALneer6b</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="W30" t="n">
         <v>148</v>
       </c>
       <c r="X30" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -5994,34 +6074,18 @@
       <c r="Z30" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
+      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AC30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>178.125</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>72.625</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>4237500</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>74.375</v>
-      </c>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
@@ -6029,48 +6093,62 @@
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="n">
-        <v>25.13636363636364</v>
+        <v>24.875</v>
       </c>
       <c r="AP30" t="n">
-        <v>181.6363636363636</v>
+        <v>177.875</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.136363636363636</v>
+        <v>1</v>
       </c>
       <c r="AR30" t="n">
-        <v>70.86363636363636</v>
+        <v>72.3125</v>
       </c>
       <c r="AS30" t="n">
-        <v>3861363.636363636</v>
+        <v>7870312.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>75.31818181818181</v>
+        <v>78.1875</v>
       </c>
       <c r="AU30" t="n">
-        <v>25.90909090909091</v>
+        <v>25.21052631578947</v>
       </c>
       <c r="AV30" t="n">
-        <v>180</v>
+        <v>183.6315789473684</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.181818181818182</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AX30" t="n">
-        <v>66.72727272727273</v>
+        <v>71.05263157894737</v>
       </c>
       <c r="AY30" t="n">
-        <v>4729545.454545454</v>
+        <v>5059210.52631579</v>
       </c>
       <c r="AZ30" t="n">
-        <v>70.09090909090909</v>
-      </c>
-      <c r="BA30" t="inlineStr"/>
-      <c r="BB30" t="inlineStr"/>
-      <c r="BC30" t="inlineStr"/>
-      <c r="BD30" t="inlineStr"/>
-      <c r="BE30" t="inlineStr"/>
-      <c r="BF30" t="inlineStr"/>
-      <c r="BG30" t="inlineStr"/>
+        <v>74.94736842105263</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>145</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>145</v>
+      </c>
       <c r="BH30" t="inlineStr"/>
       <c r="BI30" t="inlineStr"/>
       <c r="BJ30" t="inlineStr"/>
@@ -6082,216 +6160,1642 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
+          <t>vkYg8eY1</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesma espinosa m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal da malata
+  ferrol </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>10450</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7541</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>41</v>
+      </c>
+      <c r="N31" t="n">
+        <v>59</v>
+      </c>
+      <c r="O31" t="n">
+        <v>14</v>
+      </c>
+      <c r="P31" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>16</v>
+      </c>
+      <c r="T31" t="n">
+        <v>16</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>148</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1190625</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="n">
+        <v>27.72727272727273</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>178</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>66.54545454545455</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>959090.9090909091</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>64.16666666666667</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1391666.666666667</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>dQ4KOGIr</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mallo e 
+  esp </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de ipurua
+  eibar </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>8164</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3538</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>37</v>
+      </c>
+      <c r="N32" t="n">
+        <v>63</v>
+      </c>
+      <c r="O32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>17</v>
+      </c>
+      <c r="T32" t="n">
+        <v>9</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>148</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>68</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1625000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="n">
+        <v>24.85714285714286</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>182.7857142857143</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>66.85714285714286</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1801785.714285714</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>72.07142857142857</v>
+      </c>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>8QP6JLt3</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monescillo d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo mirandilla
+  cadiz </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>20776</v>
+      </c>
+      <c r="F33" t="n">
+        <v>16970</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>62</v>
+      </c>
+      <c r="N33" t="n">
+        <v>38</v>
+      </c>
+      <c r="O33" t="n">
+        <v>13</v>
+      </c>
+      <c r="P33" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>9</v>
+      </c>
+      <c r="S33" t="n">
+        <v>14</v>
+      </c>
+      <c r="T33" t="n">
+        <v>21</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>148</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>175.8888888888889</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1811111.111111111</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>25.5625</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>178.8125</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>3395312.5</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>26.38888888888889</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>69.61111111111111</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>2075000</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45520.6875</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F34" t="n">
+        <v>24843</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M34" t="n">
+        <v>48</v>
+      </c>
+      <c r="N34" t="n">
+        <v>52</v>
+      </c>
+      <c r="O34" t="n">
+        <v>15</v>
+      </c>
+      <c r="P34" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>14</v>
+      </c>
+      <c r="T34" t="n">
+        <v>15</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>148</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>75.11111111111111</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>10622222.22222222</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>79.44444444444444</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>177</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>6627272.727272728</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>179</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>10522222.22222222</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>81</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>291</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>17700000</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>294</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>80</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>hhbTMfme</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez diaz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5759</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3005</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>32</v>
+      </c>
+      <c r="N35" t="n">
+        <v>68</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P35" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6</v>
+      </c>
+      <c r="T35" t="n">
+        <v>14</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>148</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45520.58333333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22477</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M36" t="n">
+        <v>64</v>
+      </c>
+      <c r="N36" t="n">
+        <v>36</v>
+      </c>
+      <c r="O36" t="n">
+        <v>6</v>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8</v>
+      </c>
+      <c r="T36" t="n">
+        <v>23</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>148</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>8650000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.277777777777778</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>72.77777777777777</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>9987500</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>76.77777777777777</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>24.26315789473684</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>180.6842105263158</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>71.05263157894737</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>3814473.684210526</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>75.94736842105263</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>151</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>154</v>
+      </c>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45519.6875</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F37" t="n">
+        <v>54084</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M37" t="n">
+        <v>39</v>
+      </c>
+      <c r="N37" t="n">
+        <v>61</v>
+      </c>
+      <c r="O37" t="n">
+        <v>19</v>
+      </c>
+      <c r="P37" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>11</v>
+      </c>
+      <c r="T37" t="n">
+        <v>7</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>148</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>17512500</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>81.375</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>185</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>72.76923076923077</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>6384615.384615385</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>79.92307692307692</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>24.35714285714286</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>180.9285714285714</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.214285714285714</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>70.71428571428571</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>4835714.285714285</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>79.14285714285714</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>216</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>26650000</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>230</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>358</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>61400000</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>6eQuWbQ8</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45519.64583333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reig s  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo los carmenes
+  granada </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>22524</v>
+      </c>
+      <c r="F38" t="n">
+        <v>13265</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>65</v>
+      </c>
+      <c r="N38" t="n">
+        <v>35</v>
+      </c>
+      <c r="O38" t="n">
+        <v>22</v>
+      </c>
+      <c r="P38" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>10</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="n">
+        <v>11</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>148</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>178.125</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>4237500</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="n">
+        <v>25.13636363636364</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>181.6363636363636</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.136363636363636</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>70.86363636363636</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>3861363.636363636</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>75.31818181818181</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>25.90909090909091</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>180</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>4729545.454545454</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
           <t>hO0nKEm3</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B39" s="2" t="n">
         <v>45519.58333333334</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio san mames
   bilbao </t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E39" t="n">
         <v>53331</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F39" t="n">
         <v>47845</v>
       </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>IP5zl0cJ</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>dboeiWOt</t>
         </is>
       </c>
-      <c r="K31" t="n">
+      <c r="K39" t="n">
         <v>0.72</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L39" t="n">
         <v>1.07</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M39" t="n">
         <v>69</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N39" t="n">
         <v>31</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O39" t="n">
         <v>7</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P39" t="n">
         <v>9</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q39" t="n">
         <v>4</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R39" t="n">
         <v>2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S39" t="n">
         <v>15</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T39" t="n">
         <v>12</v>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>EJmuzs93</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>4AuIPRuq</t>
         </is>
       </c>
-      <c r="W31" t="n">
+      <c r="W39" t="n">
         <v>148</v>
       </c>
-      <c r="X31" t="n">
+      <c r="X39" t="n">
         <v>1481</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Y39" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="Z39" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr">
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr">
         <is>
           <t>Mi0rXQg7</t>
         </is>
       </c>
-      <c r="AC31" t="n">
+      <c r="AC39" t="n">
         <v>25.77777777777778</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AD39" t="n">
         <v>185</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AE39" t="n">
         <v>1.222222222222222</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AF39" t="n">
         <v>77.11111111111111</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AG39" t="n">
         <v>18277777.77777778</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AH39" t="n">
         <v>80.77777777777777</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AI39" t="n">
         <v>26.77777777777778</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AJ39" t="n">
         <v>179.8888888888889</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AK39" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AL39" t="n">
         <v>74.66666666666667</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AM39" t="n">
         <v>9352777.777777778</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AN39" t="n">
         <v>77.33333333333333</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AO39" t="n">
         <v>23.89473684210526</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AP39" t="n">
         <v>182.2105263157895</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AQ39" t="n">
         <v>1.473684210526316</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AR39" t="n">
         <v>76.15789473684211</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AS39" t="n">
         <v>17563157.89473684</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AT39" t="n">
         <v>81.42105263157895</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AU39" t="n">
         <v>23.9</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AV39" t="n">
         <v>179.6</v>
       </c>
-      <c r="AW31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX31" t="n">
+      <c r="AW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX39" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="AY39" t="n">
         <v>5260000</v>
       </c>
-      <c r="AZ31" t="n">
+      <c r="AZ39" t="n">
         <v>77.3</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BA39" t="n">
         <v>24.25</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BB39" t="n">
         <v>182.5</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BC39" t="n">
         <v>1.5</v>
       </c>
-      <c r="BD31" t="n">
+      <c r="BD39" t="n">
         <v>4</v>
       </c>
-      <c r="BE31" t="n">
+      <c r="BE39" t="n">
         <v>310</v>
       </c>
-      <c r="BF31" t="n">
+      <c r="BF39" t="n">
         <v>82500000</v>
       </c>
-      <c r="BG31" t="n">
+      <c r="BG39" t="n">
         <v>330</v>
       </c>
-      <c r="BH31" t="n">
+      <c r="BH39" t="n">
         <v>26</v>
       </c>
-      <c r="BI31" t="n">
+      <c r="BI39" t="n">
         <v>182</v>
       </c>
-      <c r="BJ31" t="n">
+      <c r="BJ39" t="n">
         <v>2</v>
       </c>
-      <c r="BK31" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL31" t="n">
+      <c r="BK39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL39" t="n">
         <v>78</v>
       </c>
-      <c r="BM31" t="n">
+      <c r="BM39" t="n">
         <v>17000000</v>
       </c>
-      <c r="BN31" t="n">
+      <c r="BN39" t="n">
         <v>79</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
+++ b/data/spain/p6_deployment/data_preparation/construct_data/df_matches_to_construct_historic_values.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN91"/>
+  <dimension ref="A1:BN84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3748,7 +3748,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>CjIFsr1e</t>
+          <t>Q14lVXc5</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3756,83 +3756,79 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
+          <t xml:space="preserve">palencia caballero d 
   esp </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">rcde stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadi ciutat de valencia
+  valencia </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>40000</v>
+        <v>26354</v>
       </c>
       <c r="F18" t="n">
-        <v>24238</v>
+        <v>14904</v>
       </c>
       <c r="G18" t="n">
         <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.84</v>
-      </c>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="N18" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="O18" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="P18" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>fiZxGYJ3</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>hh4xt2Df</t>
         </is>
       </c>
       <c r="W18" t="n">
         <v>148</v>
       </c>
       <c r="X18" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -3842,105 +3838,93 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>919375</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>70.375</v>
+      </c>
       <c r="AO18" t="n">
-        <v>25.90909090909091</v>
+        <v>22.58333333333333</v>
       </c>
       <c r="AP18" t="n">
-        <v>182.5909090909091</v>
+        <v>177.75</v>
       </c>
       <c r="AQ18" t="n">
         <v>1</v>
       </c>
       <c r="AR18" t="n">
-        <v>71.59090909090909</v>
+        <v>66.16666666666667</v>
       </c>
       <c r="AS18" t="n">
-        <v>3431818.181818182</v>
+        <v>1704166.666666667</v>
       </c>
       <c r="AT18" t="n">
-        <v>75.18181818181819</v>
+        <v>73.66666666666667</v>
       </c>
       <c r="AU18" t="n">
-        <v>24.25</v>
+        <v>27.05882352941176</v>
       </c>
       <c r="AV18" t="n">
-        <v>181.6</v>
+        <v>181.2352941176471</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="AX18" t="n">
-        <v>72.3</v>
+        <v>68.17647058823529</v>
       </c>
       <c r="AY18" t="n">
-        <v>5365000</v>
+        <v>2327941.176470588</v>
       </c>
       <c r="AZ18" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>178</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>74</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>75</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>182</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>69</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>80</v>
-      </c>
+        <v>71.35294117647059</v>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Q14lVXc5</t>
+          <t>CjIFsr1e</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3948,79 +3932,83 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">palencia caballero d 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi ciutat de valencia
-  valencia </t>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>26354</v>
+        <v>40000</v>
       </c>
       <c r="F19" t="n">
-        <v>14904</v>
+        <v>24238</v>
       </c>
       <c r="G19" t="n">
         <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8WUSyF3F</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.84</v>
+      </c>
       <c r="M19" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="N19" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="O19" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
         <v>6</v>
       </c>
-      <c r="R19" t="n">
-        <v>3</v>
-      </c>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="T19" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>fiZxGYJ3</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>hh4xt2Df</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="W19" t="n">
         <v>148</v>
       </c>
       <c r="X19" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -4030,88 +4018,100 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>4jl02tPF</t>
-        </is>
-      </c>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>181.25</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>919375</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>70.375</v>
-      </c>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="n">
-        <v>22.58333333333333</v>
+        <v>25.90909090909091</v>
       </c>
       <c r="AP19" t="n">
-        <v>177.75</v>
+        <v>182.5909090909091</v>
       </c>
       <c r="AQ19" t="n">
         <v>1</v>
       </c>
       <c r="AR19" t="n">
-        <v>66.16666666666667</v>
+        <v>71.59090909090909</v>
       </c>
       <c r="AS19" t="n">
-        <v>1704166.666666667</v>
+        <v>3431818.181818182</v>
       </c>
       <c r="AT19" t="n">
-        <v>73.66666666666667</v>
+        <v>75.18181818181819</v>
       </c>
       <c r="AU19" t="n">
-        <v>27.05882352941176</v>
+        <v>24.25</v>
       </c>
       <c r="AV19" t="n">
-        <v>181.2352941176471</v>
+        <v>181.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AX19" t="n">
-        <v>68.17647058823529</v>
+        <v>72.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>2327941.176470588</v>
+        <v>5365000</v>
       </c>
       <c r="AZ19" t="n">
-        <v>71.35294117647059</v>
-      </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
-      <c r="BI19" t="inlineStr"/>
-      <c r="BJ19" t="inlineStr"/>
-      <c r="BK19" t="inlineStr"/>
-      <c r="BL19" t="inlineStr"/>
-      <c r="BM19" t="inlineStr"/>
-      <c r="BN19" t="inlineStr"/>
+        <v>77.2</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>178</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>74</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>69</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -4688,7 +4688,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>G8Q9dhzq</t>
+          <t>MR4h79l1</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -4696,72 +4696,72 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">muresan s 
+          <t xml:space="preserve">sesma espinosa m 
   esp </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio carlos belmonte
-  albacete </t>
+          <t xml:space="preserve">estadio municipal de castalia
+  castellon de la plana </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17524</v>
+        <v>15500</v>
       </c>
       <c r="F23" t="n">
-        <v>10433</v>
+        <v>13218</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>UirAofN6</t>
+          <t>QyHHzdwl</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>OEsEpExD</t>
+          <t>hdWjLJUJ</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="N23" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>ALneer6b</t>
+          <t>EF6Hrtsn</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>YB3UTO7e</t>
+          <t>84cvAG3H</t>
         </is>
       </c>
       <c r="W23" t="n">
@@ -4776,14 +4776,10 @@
       <c r="Z23" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
+      <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -4792,47 +4788,47 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="n">
-        <v>25.14285714285714</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>179.6428571428571</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>65.42857142857143</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1155357.142857143</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>69.42857142857143</v>
-      </c>
+      <c r="AI23" t="n">
+        <v>28.77777777777778</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>4688888.888888889</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
       <c r="AU23" t="n">
-        <v>22.70588235294118</v>
+        <v>25.53846153846154</v>
       </c>
       <c r="AV23" t="n">
-        <v>182.8823529411765</v>
+        <v>179.7692307692308</v>
       </c>
       <c r="AW23" t="n">
-        <v>1</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="AX23" t="n">
-        <v>64.70588235294117</v>
+        <v>68.69230769230769</v>
       </c>
       <c r="AY23" t="n">
-        <v>1602941.176470588</v>
+        <v>3344230.769230769</v>
       </c>
       <c r="AZ23" t="n">
-        <v>72.76470588235294</v>
+        <v>73.92307692307692</v>
       </c>
       <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="inlineStr"/>
@@ -4852,7 +4848,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>MR4h79l1</t>
+          <t>G8Q9dhzq</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -4860,72 +4856,72 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">sesma espinosa m 
+          <t xml:space="preserve">muresan s 
   esp </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de castalia
-  castellon de la plana </t>
+          <t xml:space="preserve">estadio carlos belmonte
+  albacete </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>15500</v>
+        <v>17524</v>
       </c>
       <c r="F24" t="n">
-        <v>13218</v>
+        <v>10433</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>QyHHzdwl</t>
+          <t>UirAofN6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>hdWjLJUJ</t>
+          <t>OEsEpExD</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="N24" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="O24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P24" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
         <v>9</v>
       </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
       <c r="T24" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>EF6Hrtsn</t>
+          <t>ALneer6b</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>84cvAG3H</t>
+          <t>YB3UTO7e</t>
         </is>
       </c>
       <c r="W24" t="n">
@@ -4940,10 +4936,14 @@
       <c r="Z24" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -4952,47 +4952,47 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="n">
-        <v>28.77777777777778</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>180.6666666666667</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>73.66666666666667</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>4688888.888888889</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>74.55555555555556</v>
-      </c>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="n">
+        <v>25.14285714285714</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>179.6428571428571</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>65.42857142857143</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1155357.142857143</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>69.42857142857143</v>
+      </c>
       <c r="AU24" t="n">
-        <v>25.53846153846154</v>
+        <v>22.70588235294118</v>
       </c>
       <c r="AV24" t="n">
-        <v>179.7692307692308</v>
+        <v>182.8823529411765</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.076923076923077</v>
+        <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>68.69230769230769</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="AY24" t="n">
-        <v>3344230.769230769</v>
+        <v>1602941.176470588</v>
       </c>
       <c r="AZ24" t="n">
-        <v>73.92307692307692</v>
+        <v>72.76470588235294</v>
       </c>
       <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="inlineStr"/>
@@ -5012,7 +5012,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>6g3LEidR</t>
+          <t>CGXpDaxK</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -5020,72 +5020,72 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">muniz munoz c 
+          <t xml:space="preserve">barrera r 
   esp </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo pepico amat
-  elda </t>
+          <t xml:space="preserve">la romareda
+  zaragoza </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4038</v>
+        <v>33608</v>
       </c>
       <c r="F25" t="n">
-        <v>4957</v>
+        <v>21024</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8WUSyF3F</t>
+          <t>za7D2lO5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>nF2Vy2D0</t>
+          <t>4jl02tPF</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N25" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="O25" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="P25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q25" t="n">
+        <v>9</v>
+      </c>
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" t="n">
-        <v>2</v>
-      </c>
       <c r="S25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>hh4xt2Df</t>
+          <t>4WbDi59E</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>x604nX5H</t>
+          <t>zT9gi7i9</t>
         </is>
       </c>
       <c r="W25" t="n">
@@ -5102,85 +5102,85 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
+          <t>UytPaaEP</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>EXuxl1xP</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>29.25</v>
+        <v>23.55555555555556</v>
       </c>
       <c r="AD25" t="n">
-        <v>181.25</v>
+        <v>176</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>67.5</v>
+        <v>67.55555555555556</v>
       </c>
       <c r="AG25" t="n">
-        <v>919375</v>
+        <v>1777777.777777778</v>
       </c>
       <c r="AH25" t="n">
-        <v>70.375</v>
+        <v>73.77777777777777</v>
       </c>
       <c r="AI25" t="n">
-        <v>24.44444444444444</v>
+        <v>26.875</v>
       </c>
       <c r="AJ25" t="n">
-        <v>184</v>
+        <v>180.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.555555555555556</v>
+        <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>72.88888888888889</v>
+        <v>70.75</v>
       </c>
       <c r="AM25" t="n">
-        <v>7350000</v>
+        <v>2278125</v>
       </c>
       <c r="AN25" t="n">
-        <v>78.44444444444444</v>
+        <v>74.375</v>
       </c>
       <c r="AO25" t="n">
-        <v>26.70588235294118</v>
+        <v>24.46666666666667</v>
       </c>
       <c r="AP25" t="n">
-        <v>181.2352941176471</v>
+        <v>180.5333333333333</v>
       </c>
       <c r="AQ25" t="n">
         <v>1</v>
       </c>
       <c r="AR25" t="n">
-        <v>68.23529411764706</v>
+        <v>69.86666666666666</v>
       </c>
       <c r="AS25" t="n">
-        <v>2364705.882352941</v>
+        <v>2440000</v>
       </c>
       <c r="AT25" t="n">
-        <v>71.41176470588235</v>
+        <v>75.73333333333333</v>
       </c>
       <c r="AU25" t="n">
-        <v>22</v>
+        <v>26.27777777777778</v>
       </c>
       <c r="AV25" t="n">
-        <v>183.125</v>
+        <v>183.7222222222222</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.125</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AX25" t="n">
-        <v>68.1875</v>
+        <v>68.33333333333333</v>
       </c>
       <c r="AY25" t="n">
-        <v>3607812.5</v>
+        <v>1659722.222222222</v>
       </c>
       <c r="AZ25" t="n">
-        <v>77.25</v>
+        <v>72</v>
       </c>
       <c r="BA25" t="inlineStr"/>
       <c r="BB25" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CGXpDaxK</t>
+          <t>6g3LEidR</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -5208,72 +5208,72 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrera r 
+          <t xml:space="preserve">muniz munoz c 
   esp </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">la romareda
-  zaragoza </t>
+          <t xml:space="preserve">estadio nuevo pepico amat
+  elda </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>33608</v>
+        <v>4038</v>
       </c>
       <c r="F26" t="n">
-        <v>21024</v>
+        <v>4957</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>za7D2lO5</t>
+          <t>8WUSyF3F</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
+          <t>nF2Vy2D0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N26" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="O26" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="P26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q26" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T26" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>4WbDi59E</t>
+          <t>hh4xt2Df</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>zT9gi7i9</t>
+          <t>x604nX5H</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -5290,85 +5290,85 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
+          <t>4jl02tPF</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>EXuxl1xP</t>
         </is>
       </c>
       <c r="AC26" t="n">
-        <v>23.55555555555556</v>
+        <v>29.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>176</v>
+        <v>181.25</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>67.55555555555556</v>
+        <v>67.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1777777.777777778</v>
+        <v>919375</v>
       </c>
       <c r="AH26" t="n">
-        <v>73.77777777777777</v>
+        <v>70.375</v>
       </c>
       <c r="AI26" t="n">
-        <v>26.875</v>
+        <v>24.44444444444444</v>
       </c>
       <c r="AJ26" t="n">
-        <v>180.5</v>
+        <v>184</v>
       </c>
       <c r="AK26" t="n">
-        <v>1</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="AL26" t="n">
-        <v>70.75</v>
+        <v>72.88888888888889</v>
       </c>
       <c r="AM26" t="n">
-        <v>2278125</v>
+        <v>7350000</v>
       </c>
       <c r="AN26" t="n">
-        <v>74.375</v>
+        <v>78.44444444444444</v>
       </c>
       <c r="AO26" t="n">
-        <v>24.46666666666667</v>
+        <v>26.70588235294118</v>
       </c>
       <c r="AP26" t="n">
-        <v>180.5333333333333</v>
+        <v>181.2352941176471</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>69.86666666666666</v>
+        <v>68.23529411764706</v>
       </c>
       <c r="AS26" t="n">
-        <v>2440000</v>
+        <v>2364705.882352941</v>
       </c>
       <c r="AT26" t="n">
-        <v>75.73333333333333</v>
+        <v>71.41176470588235</v>
       </c>
       <c r="AU26" t="n">
-        <v>26.27777777777778</v>
+        <v>22</v>
       </c>
       <c r="AV26" t="n">
-        <v>183.7222222222222</v>
+        <v>183.125</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.166666666666667</v>
+        <v>1.125</v>
       </c>
       <c r="AX26" t="n">
-        <v>68.33333333333333</v>
+        <v>68.1875</v>
       </c>
       <c r="AY26" t="n">
-        <v>1659722.222222222</v>
+        <v>3607812.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>72</v>
+        <v>77.25</v>
       </c>
       <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="inlineStr"/>
@@ -5884,7 +5884,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2Pli9VJl</t>
+          <t>raOG7w0s</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -5892,72 +5892,72 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez a 
+          <t xml:space="preserve">orellana m 
   esp </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el alcoraz
-  huesca </t>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9100</v>
+        <v>29029</v>
       </c>
       <c r="F30" t="n">
-        <v>6024</v>
+        <v>25706</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>vTxTEFi6</t>
+          <t>SzYzw34K</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="N30" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="O30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P30" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>lfrtHtBn</t>
+          <t>S0PIZoj2</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>l6JQtDqc</t>
+          <t>QmLgLqap</t>
         </is>
       </c>
       <c r="W30" t="n">
@@ -5972,18 +5972,26 @@
       <c r="Z30" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>za7D2lO5</t>
-        </is>
-      </c>
+      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>180.2222222222222</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2622222.222222222</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>73.55555555555556</v>
+      </c>
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
@@ -5991,40 +5999,40 @@
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="n">
-        <v>24.93333333333333</v>
+        <v>23.73333333333333</v>
       </c>
       <c r="AP30" t="n">
-        <v>180</v>
+        <v>179.3333333333333</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
       </c>
       <c r="AR30" t="n">
-        <v>66.53333333333333</v>
+        <v>69.33333333333333</v>
       </c>
       <c r="AS30" t="n">
-        <v>1313333.333333333</v>
+        <v>2780000</v>
       </c>
       <c r="AT30" t="n">
-        <v>70.8</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="AU30" t="n">
-        <v>24.45454545454545</v>
+        <v>24.55</v>
       </c>
       <c r="AV30" t="n">
-        <v>183.2727272727273</v>
+        <v>179.6</v>
       </c>
       <c r="AW30" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AX30" t="n">
-        <v>69.18181818181819</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="AY30" t="n">
-        <v>2265909.090909091</v>
+        <v>2301250</v>
       </c>
       <c r="AZ30" t="n">
-        <v>72.90909090909091</v>
+        <v>75.55</v>
       </c>
       <c r="BA30" t="inlineStr"/>
       <c r="BB30" t="inlineStr"/>
@@ -6044,7 +6052,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>raOG7w0s</t>
+          <t>2Pli9VJl</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -6052,72 +6060,72 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">orellana m 
+          <t xml:space="preserve">sanchez a 
   esp </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el molinon
-  gijon </t>
+          <t xml:space="preserve">estadio el alcoraz
+  huesca </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>29029</v>
+        <v>9100</v>
       </c>
       <c r="F31" t="n">
-        <v>25706</v>
+        <v>6024</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>UytPaaEP</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SzYzw34K</t>
+          <t>vTxTEFi6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="N31" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="O31" t="n">
+        <v>12</v>
+      </c>
+      <c r="P31" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7</v>
+      </c>
+      <c r="S31" t="n">
         <v>10</v>
       </c>
-      <c r="P31" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>8</v>
-      </c>
-      <c r="R31" t="n">
-        <v>3</v>
-      </c>
-      <c r="S31" t="n">
-        <v>22</v>
-      </c>
       <c r="T31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>S0PIZoj2</t>
+          <t>lfrtHtBn</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>QmLgLqap</t>
+          <t>l6JQtDqc</t>
         </is>
       </c>
       <c r="W31" t="n">
@@ -6132,26 +6140,18 @@
       <c r="Z31" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
       <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="n">
-        <v>27</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>180.2222222222222</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>71.11111111111111</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2622222.222222222</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>73.55555555555556</v>
-      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
@@ -6159,40 +6159,40 @@
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="n">
-        <v>23.73333333333333</v>
+        <v>24.93333333333333</v>
       </c>
       <c r="AP31" t="n">
-        <v>179.3333333333333</v>
+        <v>180</v>
       </c>
       <c r="AQ31" t="n">
         <v>1</v>
       </c>
       <c r="AR31" t="n">
-        <v>69.33333333333333</v>
+        <v>66.53333333333333</v>
       </c>
       <c r="AS31" t="n">
-        <v>2780000</v>
+        <v>1313333.333333333</v>
       </c>
       <c r="AT31" t="n">
-        <v>75.33333333333333</v>
+        <v>70.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>24.55</v>
+        <v>24.45454545454545</v>
       </c>
       <c r="AV31" t="n">
-        <v>179.6</v>
+        <v>183.2727272727273</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AX31" t="n">
-        <v>68.65000000000001</v>
+        <v>69.18181818181819</v>
       </c>
       <c r="AY31" t="n">
-        <v>2301250</v>
+        <v>2265909.090909091</v>
       </c>
       <c r="AZ31" t="n">
-        <v>75.55</v>
+        <v>72.90909090909091</v>
       </c>
       <c r="BA31" t="inlineStr"/>
       <c r="BB31" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>Gnw301yH</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -7486,83 +7486,79 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">reig s  a 
   esp </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>42714</v>
+        <v>5759</v>
       </c>
       <c r="F39" t="n">
-        <v>35735</v>
+        <v>4747</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>48Z7G1Sf</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.8</v>
-      </c>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N39" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="O39" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P39" t="n">
         <v>11</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T39" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>pbHOStFA</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>4WbDi59E</t>
         </is>
       </c>
       <c r="W39" t="n">
         <v>148</v>
       </c>
       <c r="X39" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -7572,133 +7568,105 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>UytPaaEP</t>
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>23.22222222222222</v>
+        <v>23.375</v>
       </c>
       <c r="AD39" t="n">
-        <v>185.3333333333333</v>
+        <v>179.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.111111111111111</v>
+        <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>73.55555555555556</v>
+        <v>64.75</v>
       </c>
       <c r="AG39" t="n">
-        <v>8644444.444444444</v>
+        <v>1053750</v>
       </c>
       <c r="AH39" t="n">
-        <v>80.33333333333333</v>
+        <v>73.25</v>
       </c>
       <c r="AI39" t="n">
-        <v>25.2</v>
+        <v>23.375</v>
       </c>
       <c r="AJ39" t="n">
-        <v>182.9</v>
+        <v>176.75</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AL39" t="n">
-        <v>77.3</v>
+        <v>67.375</v>
       </c>
       <c r="AM39" t="n">
-        <v>18290000</v>
+        <v>1787500</v>
       </c>
       <c r="AN39" t="n">
-        <v>81.59999999999999</v>
+        <v>74.25</v>
       </c>
       <c r="AO39" t="n">
-        <v>25.66666666666667</v>
+        <v>21</v>
       </c>
       <c r="AP39" t="n">
-        <v>179.3333333333333</v>
+        <v>177.6666666666667</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.611111111111111</v>
+        <v>1</v>
       </c>
       <c r="AR39" t="n">
-        <v>73.88888888888889</v>
+        <v>65.41666666666667</v>
       </c>
       <c r="AS39" t="n">
-        <v>8183333.333333333</v>
+        <v>1658333.333333333</v>
       </c>
       <c r="AT39" t="n">
-        <v>79.77777777777777</v>
+        <v>76.83333333333333</v>
       </c>
       <c r="AU39" t="n">
-        <v>23.5</v>
+        <v>23.85714285714286</v>
       </c>
       <c r="AV39" t="n">
-        <v>179.55</v>
+        <v>179.8571428571429</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AX39" t="n">
-        <v>75.55</v>
+        <v>69.85714285714286</v>
       </c>
       <c r="AY39" t="n">
-        <v>14125000</v>
+        <v>2560714.285714286</v>
       </c>
       <c r="AZ39" t="n">
-        <v>81</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>160</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>160</v>
-      </c>
-      <c r="BH39" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BI39" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="BJ39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK39" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>126</v>
-      </c>
-      <c r="BM39" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="BN39" t="n">
-        <v>156</v>
-      </c>
+        <v>76.14285714285714</v>
+      </c>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Gnw301yH</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -7706,79 +7674,83 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">reig s  a 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de anduva
-  miranda de ebro </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5759</v>
+        <v>42714</v>
       </c>
       <c r="F40" t="n">
-        <v>4747</v>
+        <v>35735</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>48Z7G1Sf</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>za7D2lO5</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.8</v>
+      </c>
       <c r="M40" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N40" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="O40" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P40" t="n">
         <v>11</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T40" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>pbHOStFA</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>4WbDi59E</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="W40" t="n">
         <v>148</v>
       </c>
       <c r="X40" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -7788,105 +7760,133 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>23.375</v>
+        <v>23.22222222222222</v>
       </c>
       <c r="AD40" t="n">
-        <v>179.5</v>
+        <v>185.3333333333333</v>
       </c>
       <c r="AE40" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AF40" t="n">
-        <v>64.75</v>
+        <v>73.55555555555556</v>
       </c>
       <c r="AG40" t="n">
-        <v>1053750</v>
+        <v>8644444.444444444</v>
       </c>
       <c r="AH40" t="n">
-        <v>73.25</v>
+        <v>80.33333333333333</v>
       </c>
       <c r="AI40" t="n">
-        <v>23.375</v>
+        <v>25.2</v>
       </c>
       <c r="AJ40" t="n">
-        <v>176.75</v>
+        <v>182.9</v>
       </c>
       <c r="AK40" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AL40" t="n">
-        <v>67.375</v>
+        <v>77.3</v>
       </c>
       <c r="AM40" t="n">
-        <v>1787500</v>
+        <v>18290000</v>
       </c>
       <c r="AN40" t="n">
-        <v>74.25</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AO40" t="n">
-        <v>21</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="AP40" t="n">
-        <v>177.6666666666667</v>
+        <v>179.3333333333333</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1</v>
+        <v>1.611111111111111</v>
       </c>
       <c r="AR40" t="n">
-        <v>65.41666666666667</v>
+        <v>73.88888888888889</v>
       </c>
       <c r="AS40" t="n">
-        <v>1658333.333333333</v>
+        <v>8183333.333333333</v>
       </c>
       <c r="AT40" t="n">
-        <v>76.83333333333333</v>
+        <v>79.77777777777777</v>
       </c>
       <c r="AU40" t="n">
-        <v>23.85714285714286</v>
+        <v>23.5</v>
       </c>
       <c r="AV40" t="n">
-        <v>179.8571428571429</v>
+        <v>179.55</v>
       </c>
       <c r="AW40" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AX40" t="n">
-        <v>69.85714285714286</v>
+        <v>75.55</v>
       </c>
       <c r="AY40" t="n">
-        <v>2560714.285714286</v>
+        <v>14125000</v>
       </c>
       <c r="AZ40" t="n">
-        <v>76.14285714285714</v>
-      </c>
-      <c r="BA40" t="inlineStr"/>
-      <c r="BB40" t="inlineStr"/>
-      <c r="BC40" t="inlineStr"/>
-      <c r="BD40" t="inlineStr"/>
-      <c r="BE40" t="inlineStr"/>
-      <c r="BF40" t="inlineStr"/>
-      <c r="BG40" t="inlineStr"/>
-      <c r="BH40" t="inlineStr"/>
-      <c r="BI40" t="inlineStr"/>
-      <c r="BJ40" t="inlineStr"/>
-      <c r="BK40" t="inlineStr"/>
-      <c r="BL40" t="inlineStr"/>
-      <c r="BM40" t="inlineStr"/>
-      <c r="BN40" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>160</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>42000000</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>160</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>126</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>fJ9LmOiB</t>
+          <t>K0g0ttpo</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -7894,72 +7894,72 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">moreno a 
+          <t xml:space="preserve">monescillo d 
   esp </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el plantio
-  burgos </t>
+          <t xml:space="preserve">estadio municipal de riazor
+  la coruna </t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12194</v>
+        <v>34889</v>
       </c>
       <c r="F41" t="n">
-        <v>9105</v>
+        <v>26452</v>
       </c>
       <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="n">
-        <v>2</v>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>vTxTEFi6</t>
+          <t>Q51ZzMS6</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>QyHHzdwl</t>
+          <t>zcgwCMgS</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="N41" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="O41" t="n">
+        <v>15</v>
+      </c>
+      <c r="P41" t="n">
         <v>10</v>
       </c>
-      <c r="P41" t="n">
-        <v>13</v>
-      </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T41" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>l6JQtDqc</t>
+          <t>vHBWuyve</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>EF6Hrtsn</t>
+          <t>61Od00Pr</t>
         </is>
       </c>
       <c r="W41" t="n">
@@ -7975,43 +7975,71 @@
         <v>20242025</v>
       </c>
       <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
+      <c r="AI41" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1190625</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>69.875</v>
+      </c>
       <c r="AO41" t="n">
-        <v>24.72727272727273</v>
+        <v>24.85714285714286</v>
       </c>
       <c r="AP41" t="n">
-        <v>182.9090909090909</v>
+        <v>181.4285714285714</v>
       </c>
       <c r="AQ41" t="n">
         <v>1</v>
       </c>
       <c r="AR41" t="n">
-        <v>68.63636363636364</v>
+        <v>68.14285714285714</v>
       </c>
       <c r="AS41" t="n">
-        <v>2265909.090909091</v>
+        <v>1641071.428571429</v>
       </c>
       <c r="AT41" t="n">
-        <v>73.54545454545455</v>
-      </c>
-      <c r="AU41" t="inlineStr"/>
-      <c r="AV41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr"/>
-      <c r="AX41" t="inlineStr"/>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr"/>
+        <v>72.85714285714286</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>26.23529411764706</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>177.5294117647059</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>66.52941176470588</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1226470.588235294</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>69.94117647058823</v>
+      </c>
       <c r="BA41" t="inlineStr"/>
       <c r="BB41" t="inlineStr"/>
       <c r="BC41" t="inlineStr"/>
@@ -8030,7 +8058,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -8038,76 +8066,76 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera j 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>23516</v>
+        <v>19840</v>
       </c>
       <c r="F42" t="n">
-        <v>19908</v>
+        <v>16386</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="L42" t="n">
-        <v>1.68</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="N42" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="O42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P42" t="n">
         <v>12</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S42" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="W42" t="n">
@@ -8125,128 +8153,90 @@
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="AC42" t="n">
-        <v>25.625</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>75.875</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>11400000</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>75.25</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>10962500</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>79.625</v>
-      </c>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="n">
-        <v>25.88235294117647</v>
+        <v>22.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>175.8823529411765</v>
+        <v>178.1666666666667</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.058823529411765</v>
+        <v>1</v>
       </c>
       <c r="AR42" t="n">
-        <v>73.47058823529412</v>
+        <v>70.72222222222223</v>
       </c>
       <c r="AS42" t="n">
-        <v>7888235.294117647</v>
+        <v>3688888.888888889</v>
       </c>
       <c r="AT42" t="n">
-        <v>77.82352941176471</v>
+        <v>77.83333333333333</v>
       </c>
       <c r="AU42" t="n">
-        <v>26.13333333333333</v>
+        <v>23.72222222222222</v>
       </c>
       <c r="AV42" t="n">
-        <v>179.2666666666667</v>
+        <v>178</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.266666666666667</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AX42" t="n">
-        <v>72.66666666666667</v>
+        <v>73.11111111111111</v>
       </c>
       <c r="AY42" t="n">
-        <v>6920000</v>
+        <v>8713888.888888888</v>
       </c>
       <c r="AZ42" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>179</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD42" t="n">
+        <v>78.27777777777777</v>
+      </c>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="n">
+        <v>27</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK42" t="n">
         <v>2</v>
       </c>
-      <c r="BE42" t="n">
-        <v>138</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="BG42" t="n">
+      <c r="BL42" t="n">
         <v>150</v>
       </c>
-      <c r="BH42" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="BI42" t="n">
-        <v>178</v>
-      </c>
-      <c r="BJ42" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK42" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL42" t="n">
-        <v>293</v>
-      </c>
       <c r="BM42" t="n">
-        <v>17000000</v>
+        <v>13800000</v>
       </c>
       <c r="BN42" t="n">
-        <v>299</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -8254,76 +8244,76 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>19840</v>
+        <v>23516</v>
       </c>
       <c r="F43" t="n">
-        <v>16386</v>
+        <v>19908</v>
       </c>
       <c r="G43" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" t="n">
         <v>2</v>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="L43" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="M43" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="N43" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="O43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P43" t="n">
         <v>12</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="W43" t="n">
@@ -8341,90 +8331,128 @@
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="inlineStr"/>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AC43" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>11400000</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>10962500</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>79.625</v>
+      </c>
       <c r="AO43" t="n">
-        <v>22.5</v>
+        <v>25.88235294117647</v>
       </c>
       <c r="AP43" t="n">
-        <v>178.1666666666667</v>
+        <v>175.8823529411765</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="AR43" t="n">
-        <v>70.72222222222223</v>
+        <v>73.47058823529412</v>
       </c>
       <c r="AS43" t="n">
-        <v>3688888.888888889</v>
+        <v>7888235.294117647</v>
       </c>
       <c r="AT43" t="n">
-        <v>77.83333333333333</v>
+        <v>77.82352941176471</v>
       </c>
       <c r="AU43" t="n">
-        <v>23.72222222222222</v>
+        <v>26.13333333333333</v>
       </c>
       <c r="AV43" t="n">
+        <v>179.2666666666667</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>6920000</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>179</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>138</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>150</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BI43" t="n">
         <v>178</v>
       </c>
-      <c r="AW43" t="n">
-        <v>1.055555555555556</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>73.11111111111111</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>8713888.888888888</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>78.27777777777777</v>
-      </c>
-      <c r="BA43" t="inlineStr"/>
-      <c r="BB43" t="inlineStr"/>
-      <c r="BC43" t="inlineStr"/>
-      <c r="BD43" t="inlineStr"/>
-      <c r="BE43" t="inlineStr"/>
-      <c r="BF43" t="inlineStr"/>
-      <c r="BG43" t="inlineStr"/>
-      <c r="BH43" t="n">
-        <v>27</v>
-      </c>
-      <c r="BI43" t="n">
-        <v>179.5</v>
-      </c>
       <c r="BJ43" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BK43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BL43" t="n">
-        <v>150</v>
+        <v>293</v>
       </c>
       <c r="BM43" t="n">
-        <v>13800000</v>
+        <v>17000000</v>
       </c>
       <c r="BN43" t="n">
-        <v>150</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>K0g0ttpo</t>
+          <t>fJ9LmOiB</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -8432,72 +8460,72 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">monescillo d 
+          <t xml:space="preserve">moreno a 
   esp </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de riazor
-  la coruna </t>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>34889</v>
+        <v>12194</v>
       </c>
       <c r="F44" t="n">
-        <v>26452</v>
+        <v>9105</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Q51ZzMS6</t>
+          <t>vTxTEFi6</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>zcgwCMgS</t>
+          <t>QyHHzdwl</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="N44" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="O44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S44" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>vHBWuyve</t>
+          <t>l6JQtDqc</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>61Od00Pr</t>
+          <t>EF6Hrtsn</t>
         </is>
       </c>
       <c r="W44" t="n">
@@ -8513,71 +8541,43 @@
         <v>20242025</v>
       </c>
       <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>179.125</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>66.625</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1190625</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>69.875</v>
-      </c>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="n">
-        <v>24.85714285714286</v>
+        <v>24.72727272727273</v>
       </c>
       <c r="AP44" t="n">
-        <v>181.4285714285714</v>
+        <v>182.9090909090909</v>
       </c>
       <c r="AQ44" t="n">
         <v>1</v>
       </c>
       <c r="AR44" t="n">
-        <v>68.14285714285714</v>
+        <v>68.63636363636364</v>
       </c>
       <c r="AS44" t="n">
-        <v>1641071.428571429</v>
+        <v>2265909.090909091</v>
       </c>
       <c r="AT44" t="n">
-        <v>72.85714285714286</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>26.23529411764706</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>177.5294117647059</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>66.52941176470588</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>1226470.588235294</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>69.94117647058823</v>
-      </c>
+        <v>73.54545454545455</v>
+      </c>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="inlineStr"/>
       <c r="BB44" t="inlineStr"/>
       <c r="BC44" t="inlineStr"/>
@@ -8928,7 +8928,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -8936,76 +8936,76 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>49430</v>
+        <v>12454</v>
       </c>
       <c r="F47" t="n">
-        <v>43857</v>
+        <v>10482</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1.28</v>
+        <v>0.37</v>
       </c>
       <c r="L47" t="n">
-        <v>0.45</v>
+        <v>1.16</v>
       </c>
       <c r="M47" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="N47" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O47" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T47" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="W47" t="n">
@@ -9022,121 +9022,119 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>YT0e2vMU</t>
         </is>
       </c>
       <c r="AC47" t="n">
-        <v>22.88888888888889</v>
+        <v>26.22222222222222</v>
       </c>
       <c r="AD47" t="n">
-        <v>180.4444444444445</v>
+        <v>182.5555555555555</v>
       </c>
       <c r="AE47" t="n">
         <v>1.111111111111111</v>
       </c>
       <c r="AF47" t="n">
-        <v>71.66666666666667</v>
+        <v>72.55555555555556</v>
       </c>
       <c r="AG47" t="n">
-        <v>10091111.11111111</v>
+        <v>4811111.111111111</v>
       </c>
       <c r="AH47" t="n">
-        <v>77.66666666666667</v>
-      </c>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr"/>
+        <v>75.33333333333333</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>75.33333333333333</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>9444444.444444444</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>78.11111111111111</v>
+      </c>
       <c r="AO47" t="n">
-        <v>25.23529411764706</v>
+        <v>25.09523809523809</v>
       </c>
       <c r="AP47" t="n">
-        <v>181.0588235294118</v>
+        <v>179.3333333333333</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.176470588235294</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AR47" t="n">
-        <v>72.94117647058823</v>
+        <v>71</v>
       </c>
       <c r="AS47" t="n">
-        <v>6145588.235294118</v>
+        <v>4248809.523809524</v>
       </c>
       <c r="AT47" t="n">
-        <v>77.05882352941177</v>
+        <v>74.80952380952381</v>
       </c>
       <c r="AU47" t="n">
-        <v>23</v>
+        <v>26.7037037037037</v>
       </c>
       <c r="AV47" t="n">
-        <v>176.6153846153846</v>
+        <v>181.4444444444445</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.307692307692308</v>
+        <v>1.148148148148148</v>
       </c>
       <c r="AX47" t="n">
-        <v>73</v>
+        <v>74.74074074074075</v>
       </c>
       <c r="AY47" t="n">
-        <v>7907692.307692308</v>
+        <v>9111481.481481481</v>
       </c>
       <c r="AZ47" t="n">
-        <v>79.69230769230769</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>181.25</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>303</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>43700000</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>315</v>
-      </c>
+        <v>77.44444444444444</v>
+      </c>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="inlineStr"/>
       <c r="BH47" t="n">
-        <v>28.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="BI47" t="n">
-        <v>182.5</v>
+        <v>172.5</v>
       </c>
       <c r="BJ47" t="n">
-        <v>1.833333333333333</v>
+        <v>1</v>
       </c>
       <c r="BK47" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BL47" t="n">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="BM47" t="n">
-        <v>96000000</v>
+        <v>6200000</v>
       </c>
       <c r="BN47" t="n">
-        <v>474</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -9144,76 +9142,76 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">gil manzano j 
   esp </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12454</v>
+        <v>49430</v>
       </c>
       <c r="F48" t="n">
-        <v>10482</v>
+        <v>43857</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.37</v>
+        <v>1.28</v>
       </c>
       <c r="L48" t="n">
-        <v>1.16</v>
+        <v>0.45</v>
       </c>
       <c r="M48" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="N48" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="P48" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R48" t="n">
         <v>3</v>
       </c>
       <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="n">
         <v>11</v>
       </c>
-      <c r="T48" t="n">
-        <v>17</v>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="W48" t="n">
@@ -9230,113 +9228,115 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="AC48" t="n">
-        <v>26.22222222222222</v>
+        <v>22.88888888888889</v>
       </c>
       <c r="AD48" t="n">
-        <v>182.5555555555555</v>
+        <v>180.4444444444445</v>
       </c>
       <c r="AE48" t="n">
         <v>1.111111111111111</v>
       </c>
       <c r="AF48" t="n">
-        <v>72.55555555555556</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="AG48" t="n">
-        <v>4811111.111111111</v>
+        <v>10091111.11111111</v>
       </c>
       <c r="AH48" t="n">
-        <v>75.33333333333333</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>182.3333333333333</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>75.33333333333333</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>9444444.444444444</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>78.11111111111111</v>
-      </c>
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
       <c r="AO48" t="n">
-        <v>25.09523809523809</v>
+        <v>25.23529411764706</v>
       </c>
       <c r="AP48" t="n">
-        <v>179.3333333333333</v>
+        <v>181.0588235294118</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.047619047619048</v>
+        <v>1.176470588235294</v>
       </c>
       <c r="AR48" t="n">
-        <v>71</v>
+        <v>72.94117647058823</v>
       </c>
       <c r="AS48" t="n">
-        <v>4248809.523809524</v>
+        <v>6145588.235294118</v>
       </c>
       <c r="AT48" t="n">
-        <v>74.80952380952381</v>
+        <v>77.05882352941177</v>
       </c>
       <c r="AU48" t="n">
-        <v>26.7037037037037</v>
+        <v>23</v>
       </c>
       <c r="AV48" t="n">
-        <v>181.4444444444445</v>
+        <v>176.6153846153846</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.148148148148148</v>
+        <v>1.307692307692308</v>
       </c>
       <c r="AX48" t="n">
-        <v>74.74074074074075</v>
+        <v>73</v>
       </c>
       <c r="AY48" t="n">
-        <v>9111481.481481481</v>
+        <v>7907692.307692308</v>
       </c>
       <c r="AZ48" t="n">
-        <v>77.44444444444444</v>
-      </c>
-      <c r="BA48" t="inlineStr"/>
-      <c r="BB48" t="inlineStr"/>
-      <c r="BC48" t="inlineStr"/>
-      <c r="BD48" t="inlineStr"/>
-      <c r="BE48" t="inlineStr"/>
-      <c r="BF48" t="inlineStr"/>
-      <c r="BG48" t="inlineStr"/>
+        <v>79.69230769230769</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>303</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>43700000</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>315</v>
+      </c>
       <c r="BH48" t="n">
-        <v>22</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="BI48" t="n">
-        <v>172.5</v>
+        <v>182.5</v>
       </c>
       <c r="BJ48" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="BK48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BL48" t="n">
-        <v>140</v>
+        <v>470</v>
       </c>
       <c r="BM48" t="n">
-        <v>6200000</v>
+        <v>96000000</v>
       </c>
       <c r="BN48" t="n">
-        <v>158</v>
+        <v>474</v>
       </c>
     </row>
     <row r="49">
@@ -12154,7 +12154,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>nXUxw7wg</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -12162,79 +12162,83 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">muniz munoz c 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo arcangel
-  cordoba </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>21822</v>
+        <v>23000</v>
       </c>
       <c r="F63" t="n">
-        <v>14415</v>
+        <v>19651</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CWuejruc</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>vTxTEFi6</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3.18</v>
+      </c>
       <c r="M63" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="N63" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O63" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="P63" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R63" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S63" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T63" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>vBENkWfS</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>l6JQtDqc</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="W63" t="n">
         <v>148</v>
       </c>
       <c r="X63" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y63" t="n">
         <v>0</v>
@@ -12242,75 +12246,123 @@
       <c r="Z63" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
       <c r="AC63" t="inlineStr"/>
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr"/>
-      <c r="AJ63" t="inlineStr"/>
-      <c r="AK63" t="inlineStr"/>
-      <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="inlineStr"/>
-      <c r="AN63" t="inlineStr"/>
+      <c r="AI63" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>7233333.333333333</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>75.88888888888889</v>
+      </c>
       <c r="AO63" t="n">
-        <v>23.2</v>
+        <v>24.88888888888889</v>
       </c>
       <c r="AP63" t="n">
-        <v>184.4</v>
+        <v>183.7777777777778</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR63" t="n">
-        <v>64.59999999999999</v>
+        <v>74.77777777777777</v>
       </c>
       <c r="AS63" t="n">
-        <v>1220000</v>
+        <v>10720833.33333333</v>
       </c>
       <c r="AT63" t="n">
-        <v>73.40000000000001</v>
+        <v>79.55555555555556</v>
       </c>
       <c r="AU63" t="n">
-        <v>23.16666666666667</v>
+        <v>26.29411764705882</v>
       </c>
       <c r="AV63" t="n">
-        <v>183.5833333333333</v>
+        <v>178.1176470588235</v>
       </c>
       <c r="AW63" t="n">
-        <v>1</v>
+        <v>1.529411764705882</v>
       </c>
       <c r="AX63" t="n">
-        <v>67.33333333333333</v>
+        <v>74.64705882352941</v>
       </c>
       <c r="AY63" t="n">
-        <v>2147916.666666667</v>
+        <v>10416176.47058824</v>
       </c>
       <c r="AZ63" t="n">
-        <v>74.16666666666667</v>
-      </c>
-      <c r="BA63" t="inlineStr"/>
-      <c r="BB63" t="inlineStr"/>
-      <c r="BC63" t="inlineStr"/>
-      <c r="BD63" t="inlineStr"/>
-      <c r="BE63" t="inlineStr"/>
-      <c r="BF63" t="inlineStr"/>
-      <c r="BG63" t="inlineStr"/>
-      <c r="BH63" t="inlineStr"/>
-      <c r="BI63" t="inlineStr"/>
-      <c r="BJ63" t="inlineStr"/>
-      <c r="BK63" t="inlineStr"/>
-      <c r="BL63" t="inlineStr"/>
-      <c r="BM63" t="inlineStr"/>
-      <c r="BN63" t="inlineStr"/>
+        <v>79.35294117647059</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>233</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>236</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI63" t="n">
+        <v>179</v>
+      </c>
+      <c r="BJ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>146</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>nXUxw7wg</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -12318,83 +12370,79 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">muniz munoz c 
   esp </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadio nuevo arcangel
+  cordoba </t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>23000</v>
+        <v>21822</v>
       </c>
       <c r="F64" t="n">
-        <v>19651</v>
+        <v>14415</v>
       </c>
       <c r="G64" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="n">
+        <v>54</v>
+      </c>
+      <c r="N64" t="n">
+        <v>46</v>
+      </c>
+      <c r="O64" t="n">
+        <v>11</v>
+      </c>
+      <c r="P64" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q64" t="n">
         <v>4</v>
       </c>
-      <c r="H64" t="n">
-        <v>3</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="K64" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="L64" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="M64" t="n">
-        <v>45</v>
-      </c>
-      <c r="N64" t="n">
-        <v>55</v>
-      </c>
-      <c r="O64" t="n">
-        <v>24</v>
-      </c>
-      <c r="P64" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>9</v>
-      </c>
       <c r="R64" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T64" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>vBENkWfS</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>l6JQtDqc</t>
         </is>
       </c>
       <c r="W64" t="n">
         <v>148</v>
       </c>
       <c r="X64" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y64" t="n">
         <v>0</v>
@@ -12402,118 +12450,70 @@
       <c r="Z64" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr"/>
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="n">
-        <v>26.22222222222222</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>180.7777777777778</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>72.88888888888889</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>7233333.333333333</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>75.88888888888889</v>
-      </c>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
       <c r="AO64" t="n">
-        <v>24.88888888888889</v>
+        <v>23.2</v>
       </c>
       <c r="AP64" t="n">
-        <v>183.7777777777778</v>
+        <v>184.4</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR64" t="n">
-        <v>74.77777777777777</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AS64" t="n">
-        <v>10720833.33333333</v>
+        <v>1220000</v>
       </c>
       <c r="AT64" t="n">
-        <v>79.55555555555556</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AU64" t="n">
-        <v>26.29411764705882</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="AV64" t="n">
-        <v>178.1176470588235</v>
+        <v>183.5833333333333</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.529411764705882</v>
+        <v>1</v>
       </c>
       <c r="AX64" t="n">
-        <v>74.64705882352941</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="AY64" t="n">
-        <v>10416176.47058824</v>
+        <v>2147916.666666667</v>
       </c>
       <c r="AZ64" t="n">
-        <v>79.35294117647059</v>
-      </c>
-      <c r="BA64" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB64" t="n">
-        <v>181.6666666666667</v>
-      </c>
-      <c r="BC64" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="BD64" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE64" t="n">
-        <v>233</v>
-      </c>
-      <c r="BF64" t="n">
-        <v>44500000</v>
-      </c>
-      <c r="BG64" t="n">
-        <v>236</v>
-      </c>
-      <c r="BH64" t="n">
-        <v>26</v>
-      </c>
-      <c r="BI64" t="n">
-        <v>179</v>
-      </c>
-      <c r="BJ64" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL64" t="n">
-        <v>146</v>
-      </c>
-      <c r="BM64" t="n">
-        <v>6900000</v>
-      </c>
-      <c r="BN64" t="n">
-        <v>149</v>
-      </c>
+        <v>74.16666666666667</v>
+      </c>
+      <c r="BA64" t="inlineStr"/>
+      <c r="BB64" t="inlineStr"/>
+      <c r="BC64" t="inlineStr"/>
+      <c r="BD64" t="inlineStr"/>
+      <c r="BE64" t="inlineStr"/>
+      <c r="BF64" t="inlineStr"/>
+      <c r="BG64" t="inlineStr"/>
+      <c r="BH64" t="inlineStr"/>
+      <c r="BI64" t="inlineStr"/>
+      <c r="BJ64" t="inlineStr"/>
+      <c r="BK64" t="inlineStr"/>
+      <c r="BL64" t="inlineStr"/>
+      <c r="BM64" t="inlineStr"/>
+      <c r="BN64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -13834,7 +13834,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>jBnLKPNO</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -13842,83 +13842,79 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">muresan s 
   esp </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio la rosaleda
+  malaga </t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>16500</v>
+        <v>30044</v>
       </c>
       <c r="F72" t="n">
-        <v>9529</v>
+        <v>26066</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>25tIqYiJ</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="K72" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0.25</v>
-      </c>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="N72" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="O72" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P72" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q72" t="n">
         <v>3</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S72" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="T72" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>tjXr7SAp</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>pbHOStFA</t>
         </is>
       </c>
       <c r="W72" t="n">
         <v>148</v>
       </c>
       <c r="X72" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y72" t="n">
         <v>0</v>
@@ -13926,135 +13922,91 @@
       <c r="Z72" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
+      <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="AC72" t="n">
-        <v>26.55555555555556</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>180.7777777777778</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>74</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>7963888.888888889</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>77</v>
-      </c>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>29.77777777777778</v>
+        <v>25.375</v>
       </c>
       <c r="AJ72" t="n">
-        <v>177.7777777777778</v>
+        <v>180.625</v>
       </c>
       <c r="AK72" t="n">
-        <v>1.444444444444444</v>
+        <v>1</v>
       </c>
       <c r="AL72" t="n">
-        <v>75.77777777777777</v>
+        <v>65.625</v>
       </c>
       <c r="AM72" t="n">
-        <v>6888888.888888889</v>
+        <v>972500</v>
       </c>
       <c r="AN72" t="n">
-        <v>76.55555555555556</v>
+        <v>71.625</v>
       </c>
       <c r="AO72" t="n">
-        <v>23.83333333333333</v>
+        <v>21.71428571428572</v>
       </c>
       <c r="AP72" t="n">
-        <v>179.1666666666667</v>
+        <v>181.4285714285714</v>
       </c>
       <c r="AQ72" t="n">
         <v>1</v>
       </c>
       <c r="AR72" t="n">
-        <v>71.66666666666667</v>
+        <v>64.14285714285714</v>
       </c>
       <c r="AS72" t="n">
-        <v>6772916.666666667</v>
+        <v>1392857.142857143</v>
       </c>
       <c r="AT72" t="n">
-        <v>77.41666666666667</v>
+        <v>73.28571428571429</v>
       </c>
       <c r="AU72" t="n">
-        <v>27.46153846153846</v>
+        <v>20.46153846153846</v>
       </c>
       <c r="AV72" t="n">
-        <v>176.2307692307692</v>
+        <v>178.8461538461538</v>
       </c>
       <c r="AW72" t="n">
-        <v>1.230769230769231</v>
+        <v>1</v>
       </c>
       <c r="AX72" t="n">
-        <v>74.07692307692308</v>
+        <v>64.84615384615384</v>
       </c>
       <c r="AY72" t="n">
-        <v>5376923.076923077</v>
+        <v>1555769.230769231</v>
       </c>
       <c r="AZ72" t="n">
-        <v>75.92307692307692</v>
-      </c>
-      <c r="BA72" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB72" t="n">
-        <v>181</v>
-      </c>
-      <c r="BC72" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD72" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE72" t="n">
-        <v>78</v>
-      </c>
-      <c r="BF72" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="BG72" t="n">
-        <v>79</v>
-      </c>
-      <c r="BH72" t="n">
-        <v>22</v>
-      </c>
-      <c r="BI72" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="BJ72" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK72" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL72" t="n">
-        <v>133</v>
-      </c>
-      <c r="BM72" t="n">
-        <v>4750000</v>
-      </c>
-      <c r="BN72" t="n">
-        <v>152</v>
-      </c>
+        <v>77.76923076923077</v>
+      </c>
+      <c r="BA72" t="inlineStr"/>
+      <c r="BB72" t="inlineStr"/>
+      <c r="BC72" t="inlineStr"/>
+      <c r="BD72" t="inlineStr"/>
+      <c r="BE72" t="inlineStr"/>
+      <c r="BF72" t="inlineStr"/>
+      <c r="BG72" t="inlineStr"/>
+      <c r="BH72" t="inlineStr"/>
+      <c r="BI72" t="inlineStr"/>
+      <c r="BJ72" t="inlineStr"/>
+      <c r="BK72" t="inlineStr"/>
+      <c r="BL72" t="inlineStr"/>
+      <c r="BM72" t="inlineStr"/>
+      <c r="BN72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>QHtUvT8t</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -14062,21 +14014,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">sanchez lopez r 
   esp </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio heliodoro rodriguez lopez
+  santa cruz de tenerife </t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>40000</v>
+        <v>22824</v>
       </c>
       <c r="F73" t="n">
-        <v>20900</v>
+        <v>14308</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -14086,59 +14038,55 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>IHv6nz80</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L73" t="n">
-        <v>1.03</v>
-      </c>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="N73" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="O73" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P73" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="Q73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S73" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T73" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>UBD9uzt0</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>x604nX5H</t>
         </is>
       </c>
       <c r="W73" t="n">
         <v>148</v>
       </c>
       <c r="X73" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y73" t="n">
         <v>0</v>
@@ -14148,117 +14096,81 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr"/>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
       <c r="AC73" t="inlineStr"/>
       <c r="AD73" t="inlineStr"/>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
-      <c r="AI73" t="n">
-        <v>26.11111111111111</v>
-      </c>
-      <c r="AJ73" t="n">
-        <v>180.8888888888889</v>
-      </c>
-      <c r="AK73" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AL73" t="n">
-        <v>78.77777777777777</v>
-      </c>
-      <c r="AM73" t="n">
-        <v>22244444.44444444</v>
-      </c>
-      <c r="AN73" t="n">
-        <v>81.88888888888889</v>
-      </c>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
       <c r="AO73" t="n">
-        <v>26.11111111111111</v>
+        <v>28.22222222222222</v>
       </c>
       <c r="AP73" t="n">
-        <v>178.9444444444445</v>
+        <v>183.1111111111111</v>
       </c>
       <c r="AQ73" t="n">
         <v>1</v>
       </c>
       <c r="AR73" t="n">
-        <v>70.33333333333333</v>
+        <v>70.77777777777777</v>
       </c>
       <c r="AS73" t="n">
-        <v>2377777.777777778</v>
+        <v>1822222.222222222</v>
       </c>
       <c r="AT73" t="n">
-        <v>74.05555555555556</v>
+        <v>72.11111111111111</v>
       </c>
       <c r="AU73" t="n">
-        <v>23.35</v>
+        <v>22.4</v>
       </c>
       <c r="AV73" t="n">
-        <v>180.25</v>
+        <v>184.0666666666667</v>
       </c>
       <c r="AW73" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="AX73" t="n">
-        <v>73.15000000000001</v>
+        <v>69.66666666666667</v>
       </c>
       <c r="AY73" t="n">
-        <v>15855000</v>
+        <v>3886666.666666667</v>
       </c>
       <c r="AZ73" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="BA73" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB73" t="n">
-        <v>178</v>
-      </c>
-      <c r="BC73" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD73" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE73" t="n">
-        <v>74</v>
-      </c>
-      <c r="BF73" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="BG73" t="n">
-        <v>75</v>
-      </c>
-      <c r="BH73" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="BI73" t="n">
-        <v>178.5</v>
-      </c>
-      <c r="BJ73" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK73" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL73" t="n">
-        <v>305</v>
-      </c>
-      <c r="BM73" t="n">
-        <v>53500000</v>
-      </c>
-      <c r="BN73" t="n">
-        <v>327</v>
-      </c>
+        <v>76.86666666666666</v>
+      </c>
+      <c r="BA73" t="inlineStr"/>
+      <c r="BB73" t="inlineStr"/>
+      <c r="BC73" t="inlineStr"/>
+      <c r="BD73" t="inlineStr"/>
+      <c r="BE73" t="inlineStr"/>
+      <c r="BF73" t="inlineStr"/>
+      <c r="BG73" t="inlineStr"/>
+      <c r="BH73" t="inlineStr"/>
+      <c r="BI73" t="inlineStr"/>
+      <c r="BJ73" t="inlineStr"/>
+      <c r="BK73" t="inlineStr"/>
+      <c r="BL73" t="inlineStr"/>
+      <c r="BM73" t="inlineStr"/>
+      <c r="BN73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>jBnLKPNO</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -14266,79 +14178,83 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">muresan s 
+          <t xml:space="preserve">rojas j  a 
   esp </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio la rosaleda
-  malaga </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>30044</v>
+        <v>16500</v>
       </c>
       <c r="F74" t="n">
-        <v>26066</v>
+        <v>9529</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>25tIqYiJ</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>48Z7G1Sf</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.25</v>
+      </c>
       <c r="M74" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="N74" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="O74" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P74" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S74" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="T74" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>tjXr7SAp</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>pbHOStFA</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="W74" t="n">
         <v>148</v>
       </c>
       <c r="X74" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y74" t="n">
         <v>0</v>
@@ -14346,91 +14262,135 @@
       <c r="Z74" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr"/>
-      <c r="AD74" t="inlineStr"/>
-      <c r="AE74" t="inlineStr"/>
-      <c r="AF74" t="inlineStr"/>
-      <c r="AG74" t="inlineStr"/>
-      <c r="AH74" t="inlineStr"/>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC74" t="n">
+        <v>26.55555555555556</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>74</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>7963888.888888889</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>77</v>
+      </c>
       <c r="AI74" t="n">
-        <v>25.375</v>
+        <v>29.77777777777778</v>
       </c>
       <c r="AJ74" t="n">
-        <v>180.625</v>
+        <v>177.7777777777778</v>
       </c>
       <c r="AK74" t="n">
-        <v>1</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AL74" t="n">
-        <v>65.625</v>
+        <v>75.77777777777777</v>
       </c>
       <c r="AM74" t="n">
-        <v>972500</v>
+        <v>6888888.888888889</v>
       </c>
       <c r="AN74" t="n">
-        <v>71.625</v>
+        <v>76.55555555555556</v>
       </c>
       <c r="AO74" t="n">
-        <v>21.71428571428572</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="AP74" t="n">
-        <v>181.4285714285714</v>
+        <v>179.1666666666667</v>
       </c>
       <c r="AQ74" t="n">
         <v>1</v>
       </c>
       <c r="AR74" t="n">
-        <v>64.14285714285714</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="AS74" t="n">
-        <v>1392857.142857143</v>
+        <v>6772916.666666667</v>
       </c>
       <c r="AT74" t="n">
-        <v>73.28571428571429</v>
+        <v>77.41666666666667</v>
       </c>
       <c r="AU74" t="n">
-        <v>20.46153846153846</v>
+        <v>27.46153846153846</v>
       </c>
       <c r="AV74" t="n">
-        <v>178.8461538461538</v>
+        <v>176.2307692307692</v>
       </c>
       <c r="AW74" t="n">
-        <v>1</v>
+        <v>1.230769230769231</v>
       </c>
       <c r="AX74" t="n">
-        <v>64.84615384615384</v>
+        <v>74.07692307692308</v>
       </c>
       <c r="AY74" t="n">
-        <v>1555769.230769231</v>
+        <v>5376923.076923077</v>
       </c>
       <c r="AZ74" t="n">
-        <v>77.76923076923077</v>
-      </c>
-      <c r="BA74" t="inlineStr"/>
-      <c r="BB74" t="inlineStr"/>
-      <c r="BC74" t="inlineStr"/>
-      <c r="BD74" t="inlineStr"/>
-      <c r="BE74" t="inlineStr"/>
-      <c r="BF74" t="inlineStr"/>
-      <c r="BG74" t="inlineStr"/>
-      <c r="BH74" t="inlineStr"/>
-      <c r="BI74" t="inlineStr"/>
-      <c r="BJ74" t="inlineStr"/>
-      <c r="BK74" t="inlineStr"/>
-      <c r="BL74" t="inlineStr"/>
-      <c r="BM74" t="inlineStr"/>
-      <c r="BN74" t="inlineStr"/>
+        <v>75.92307692307692</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>181</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>78</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="BG74" t="n">
+        <v>79</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>22</v>
+      </c>
+      <c r="BI74" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BJ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL74" t="n">
+        <v>133</v>
+      </c>
+      <c r="BM74" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>QHtUvT8t</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
@@ -14438,21 +14398,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez lopez r 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio heliodoro rodriguez lopez
-  santa cruz de tenerife </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>22824</v>
+        <v>40000</v>
       </c>
       <c r="F75" t="n">
-        <v>14308</v>
+        <v>20900</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -14462,55 +14422,59 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>nF2Vy2D0</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.03</v>
+      </c>
       <c r="M75" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="N75" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="O75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P75" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Q75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T75" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>UBD9uzt0</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>x604nX5H</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="W75" t="n">
         <v>148</v>
       </c>
       <c r="X75" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y75" t="n">
         <v>0</v>
@@ -14520,76 +14484,112 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>EXuxl1xP</t>
-        </is>
-      </c>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr"/>
       <c r="AD75" t="inlineStr"/>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="inlineStr"/>
-      <c r="AJ75" t="inlineStr"/>
-      <c r="AK75" t="inlineStr"/>
-      <c r="AL75" t="inlineStr"/>
-      <c r="AM75" t="inlineStr"/>
-      <c r="AN75" t="inlineStr"/>
+      <c r="AI75" t="n">
+        <v>26.11111111111111</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>180.8888888888889</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>78.77777777777777</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>22244444.44444444</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>81.88888888888889</v>
+      </c>
       <c r="AO75" t="n">
-        <v>28.22222222222222</v>
+        <v>26.11111111111111</v>
       </c>
       <c r="AP75" t="n">
-        <v>183.1111111111111</v>
+        <v>178.9444444444445</v>
       </c>
       <c r="AQ75" t="n">
         <v>1</v>
       </c>
       <c r="AR75" t="n">
-        <v>70.77777777777777</v>
+        <v>70.33333333333333</v>
       </c>
       <c r="AS75" t="n">
-        <v>1822222.222222222</v>
+        <v>2377777.777777778</v>
       </c>
       <c r="AT75" t="n">
-        <v>72.11111111111111</v>
+        <v>74.05555555555556</v>
       </c>
       <c r="AU75" t="n">
-        <v>22.4</v>
+        <v>23.35</v>
       </c>
       <c r="AV75" t="n">
-        <v>184.0666666666667</v>
+        <v>180.25</v>
       </c>
       <c r="AW75" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AX75" t="n">
-        <v>69.66666666666667</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="AY75" t="n">
-        <v>3886666.666666667</v>
+        <v>15855000</v>
       </c>
       <c r="AZ75" t="n">
-        <v>76.86666666666666</v>
-      </c>
-      <c r="BA75" t="inlineStr"/>
-      <c r="BB75" t="inlineStr"/>
-      <c r="BC75" t="inlineStr"/>
-      <c r="BD75" t="inlineStr"/>
-      <c r="BE75" t="inlineStr"/>
-      <c r="BF75" t="inlineStr"/>
-      <c r="BG75" t="inlineStr"/>
-      <c r="BH75" t="inlineStr"/>
-      <c r="BI75" t="inlineStr"/>
-      <c r="BJ75" t="inlineStr"/>
-      <c r="BK75" t="inlineStr"/>
-      <c r="BL75" t="inlineStr"/>
-      <c r="BM75" t="inlineStr"/>
-      <c r="BN75" t="inlineStr"/>
+        <v>79.8</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>178</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>74</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="BJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>305</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>53500000</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>327</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -14974,7 +14974,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>fqgCMogC</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -14982,83 +14982,79 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">fuentes molina a 
   esp </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio municipal da malata
+  ferrol </t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>23516</v>
+        <v>10450</v>
       </c>
       <c r="F78" t="n">
-        <v>19900</v>
+        <v>7397</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>zcgwCMgS</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="K78" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0.35</v>
-      </c>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N78" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O78" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P78" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T78" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>61Od00Pr</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>K4dMCgFa</t>
         </is>
       </c>
       <c r="W78" t="n">
         <v>148</v>
       </c>
       <c r="X78" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y78" t="n">
         <v>0</v>
@@ -15066,114 +15062,102 @@
       <c r="Z78" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr"/>
-      <c r="AD78" t="inlineStr"/>
-      <c r="AE78" t="inlineStr"/>
-      <c r="AF78" t="inlineStr"/>
-      <c r="AG78" t="inlineStr"/>
-      <c r="AH78" t="inlineStr"/>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC78" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>1190625</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>69.875</v>
+      </c>
       <c r="AI78" t="n">
-        <v>27.7</v>
+        <v>26.7</v>
       </c>
       <c r="AJ78" t="n">
-        <v>183.8</v>
+        <v>180</v>
       </c>
       <c r="AK78" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AL78" t="n">
-        <v>76.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="AM78" t="n">
-        <v>11750000</v>
+        <v>3720000</v>
       </c>
       <c r="AN78" t="n">
-        <v>78.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AO78" t="n">
-        <v>24.3125</v>
+        <v>26.78571428571428</v>
       </c>
       <c r="AP78" t="n">
-        <v>179.6875</v>
+        <v>175.8571428571429</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.0625</v>
+        <v>1</v>
       </c>
       <c r="AR78" t="n">
-        <v>70.75</v>
+        <v>67.92857142857143</v>
       </c>
       <c r="AS78" t="n">
-        <v>6357812.5</v>
+        <v>1678571.428571429</v>
       </c>
       <c r="AT78" t="n">
-        <v>76.8125</v>
+        <v>70.85714285714286</v>
       </c>
       <c r="AU78" t="n">
-        <v>27.15</v>
+        <v>25.5</v>
       </c>
       <c r="AV78" t="n">
-        <v>181.3</v>
+        <v>181.6818181818182</v>
       </c>
       <c r="AW78" t="n">
-        <v>1.1</v>
+        <v>1.045454545454545</v>
       </c>
       <c r="AX78" t="n">
-        <v>73.59999999999999</v>
+        <v>70.68181818181819</v>
       </c>
       <c r="AY78" t="n">
-        <v>5950500</v>
+        <v>3993181.818181818</v>
       </c>
       <c r="AZ78" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="BA78" t="n">
-        <v>28.33333333333333</v>
-      </c>
-      <c r="BB78" t="n">
-        <v>174.3333333333333</v>
-      </c>
-      <c r="BC78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD78" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE78" t="n">
-        <v>220</v>
-      </c>
-      <c r="BF78" t="n">
-        <v>11700000</v>
-      </c>
-      <c r="BG78" t="n">
-        <v>220</v>
-      </c>
-      <c r="BH78" t="n">
-        <v>22</v>
-      </c>
-      <c r="BI78" t="n">
-        <v>172.5</v>
-      </c>
-      <c r="BJ78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK78" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL78" t="n">
-        <v>140</v>
-      </c>
-      <c r="BM78" t="n">
-        <v>6200000</v>
-      </c>
-      <c r="BN78" t="n">
-        <v>158</v>
-      </c>
+        <v>74.45454545454545</v>
+      </c>
+      <c r="BA78" t="inlineStr"/>
+      <c r="BB78" t="inlineStr"/>
+      <c r="BC78" t="inlineStr"/>
+      <c r="BD78" t="inlineStr"/>
+      <c r="BE78" t="inlineStr"/>
+      <c r="BF78" t="inlineStr"/>
+      <c r="BG78" t="inlineStr"/>
+      <c r="BH78" t="inlineStr"/>
+      <c r="BI78" t="inlineStr"/>
+      <c r="BJ78" t="inlineStr"/>
+      <c r="BK78" t="inlineStr"/>
+      <c r="BL78" t="inlineStr"/>
+      <c r="BM78" t="inlineStr"/>
+      <c r="BN78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -15350,7 +15334,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>fqgCMogC</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -15358,79 +15342,83 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuentes molina a 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal da malata
-  ferrol </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>10450</v>
+        <v>23516</v>
       </c>
       <c r="F80" t="n">
-        <v>7397</v>
+        <v>19900</v>
       </c>
       <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
         <v>0</v>
       </c>
-      <c r="H80" t="n">
-        <v>1</v>
-      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>zcgwCMgS</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>EXuxl1xP</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.35</v>
+      </c>
       <c r="M80" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N80" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O80" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P80" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R80" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S80" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T80" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>61Od00Pr</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>K4dMCgFa</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="W80" t="n">
         <v>148</v>
       </c>
       <c r="X80" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y80" t="n">
         <v>0</v>
@@ -15438,102 +15426,114 @@
       <c r="Z80" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
+      <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="AC80" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>179.125</v>
-      </c>
-      <c r="AE80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF80" t="n">
-        <v>66.625</v>
-      </c>
-      <c r="AG80" t="n">
-        <v>1190625</v>
-      </c>
-      <c r="AH80" t="n">
-        <v>69.875</v>
-      </c>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>26.7</v>
+        <v>27.7</v>
       </c>
       <c r="AJ80" t="n">
-        <v>180</v>
+        <v>183.8</v>
       </c>
       <c r="AK80" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>11750000</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>24.3125</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>179.6875</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>6357812.5</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>76.8125</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="AW80" t="n">
         <v>1.1</v>
       </c>
-      <c r="AL80" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="AM80" t="n">
-        <v>3720000</v>
-      </c>
-      <c r="AN80" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="AO80" t="n">
-        <v>26.78571428571428</v>
-      </c>
-      <c r="AP80" t="n">
-        <v>175.8571428571429</v>
-      </c>
-      <c r="AQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR80" t="n">
-        <v>67.92857142857143</v>
-      </c>
-      <c r="AS80" t="n">
-        <v>1678571.428571429</v>
-      </c>
-      <c r="AT80" t="n">
-        <v>70.85714285714286</v>
-      </c>
-      <c r="AU80" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AV80" t="n">
-        <v>181.6818181818182</v>
-      </c>
-      <c r="AW80" t="n">
-        <v>1.045454545454545</v>
-      </c>
       <c r="AX80" t="n">
-        <v>70.68181818181819</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AY80" t="n">
-        <v>3993181.818181818</v>
+        <v>5950500</v>
       </c>
       <c r="AZ80" t="n">
-        <v>74.45454545454545</v>
-      </c>
-      <c r="BA80" t="inlineStr"/>
-      <c r="BB80" t="inlineStr"/>
-      <c r="BC80" t="inlineStr"/>
-      <c r="BD80" t="inlineStr"/>
-      <c r="BE80" t="inlineStr"/>
-      <c r="BF80" t="inlineStr"/>
-      <c r="BG80" t="inlineStr"/>
-      <c r="BH80" t="inlineStr"/>
-      <c r="BI80" t="inlineStr"/>
-      <c r="BJ80" t="inlineStr"/>
-      <c r="BK80" t="inlineStr"/>
-      <c r="BL80" t="inlineStr"/>
-      <c r="BM80" t="inlineStr"/>
-      <c r="BN80" t="inlineStr"/>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>28.33333333333333</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>174.3333333333333</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>220</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>11700000</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>220</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>22</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>140</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -16295,1364 +16295,6 @@
       <c r="BM84" t="inlineStr"/>
       <c r="BN84" t="inlineStr"/>
     </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr">
-        <is>
-          <t>E1Xs9lu2</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="n">
-        <v>45523.6875</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cuadra g 
-  esp </t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F85" t="n">
-        <v>21566</v>
-      </c>
-      <c r="G85" t="n">
-        <v>2</v>
-      </c>
-      <c r="H85" t="n">
-        <v>2</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="M85" t="n">
-        <v>45</v>
-      </c>
-      <c r="N85" t="n">
-        <v>55</v>
-      </c>
-      <c r="O85" t="n">
-        <v>9</v>
-      </c>
-      <c r="P85" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>3</v>
-      </c>
-      <c r="R85" t="n">
-        <v>5</v>
-      </c>
-      <c r="S85" t="n">
-        <v>7</v>
-      </c>
-      <c r="T85" t="n">
-        <v>12</v>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Ii1Om118</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>AZ18LjKN</t>
-        </is>
-      </c>
-      <c r="W85" t="n">
-        <v>148</v>
-      </c>
-      <c r="X85" t="n">
-        <v>1481</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr"/>
-      <c r="AC85" t="inlineStr"/>
-      <c r="AD85" t="inlineStr"/>
-      <c r="AE85" t="inlineStr"/>
-      <c r="AF85" t="inlineStr"/>
-      <c r="AG85" t="inlineStr"/>
-      <c r="AH85" t="inlineStr"/>
-      <c r="AI85" t="n">
-        <v>28.22222222222222</v>
-      </c>
-      <c r="AJ85" t="n">
-        <v>182.2222222222222</v>
-      </c>
-      <c r="AK85" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="AL85" t="n">
-        <v>81.33333333333333</v>
-      </c>
-      <c r="AM85" t="n">
-        <v>30055555.55555556</v>
-      </c>
-      <c r="AN85" t="n">
-        <v>83.33333333333333</v>
-      </c>
-      <c r="AO85" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP85" t="n">
-        <v>182.0526315789474</v>
-      </c>
-      <c r="AQ85" t="n">
-        <v>1.421052631578947</v>
-      </c>
-      <c r="AR85" t="n">
-        <v>74.73684210526316</v>
-      </c>
-      <c r="AS85" t="n">
-        <v>11172368.42105263</v>
-      </c>
-      <c r="AT85" t="n">
-        <v>79.73684210526316</v>
-      </c>
-      <c r="AU85" t="n">
-        <v>25.96153846153846</v>
-      </c>
-      <c r="AV85" t="n">
-        <v>179.3461538461538</v>
-      </c>
-      <c r="AW85" t="n">
-        <v>1.846153846153846</v>
-      </c>
-      <c r="AX85" t="n">
-        <v>80.11538461538461</v>
-      </c>
-      <c r="AY85" t="n">
-        <v>29961538.46153846</v>
-      </c>
-      <c r="AZ85" t="n">
-        <v>83.26923076923077</v>
-      </c>
-      <c r="BA85" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB85" t="n">
-        <v>181.6666666666667</v>
-      </c>
-      <c r="BC85" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="BD85" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE85" t="n">
-        <v>233</v>
-      </c>
-      <c r="BF85" t="n">
-        <v>44500000</v>
-      </c>
-      <c r="BG85" t="n">
-        <v>236</v>
-      </c>
-      <c r="BH85" t="inlineStr"/>
-      <c r="BI85" t="inlineStr"/>
-      <c r="BJ85" t="inlineStr"/>
-      <c r="BK85" t="inlineStr"/>
-      <c r="BL85" t="inlineStr"/>
-      <c r="BM85" t="inlineStr"/>
-      <c r="BN85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr">
-        <is>
-          <t>IZqoAH3k</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="n">
-        <v>45523.64583333334</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de la fuente ramos o 
-  esp </t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio nuevo pepico amat
-  elda </t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>4038</v>
-      </c>
-      <c r="F86" t="n">
-        <v>4168</v>
-      </c>
-      <c r="G86" t="n">
-        <v>2</v>
-      </c>
-      <c r="H86" t="n">
-        <v>1</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>8WUSyF3F</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="n">
-        <v>46</v>
-      </c>
-      <c r="N86" t="n">
-        <v>54</v>
-      </c>
-      <c r="O86" t="n">
-        <v>15</v>
-      </c>
-      <c r="P86" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>4</v>
-      </c>
-      <c r="R86" t="n">
-        <v>5</v>
-      </c>
-      <c r="S86" t="n">
-        <v>11</v>
-      </c>
-      <c r="T86" t="n">
-        <v>17</v>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>hh4xt2Df</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>UBD9uzt0</t>
-        </is>
-      </c>
-      <c r="W86" t="n">
-        <v>148</v>
-      </c>
-      <c r="X86" t="n">
-        <v>1482</v>
-      </c>
-      <c r="Y86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>4jl02tPF</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr"/>
-      <c r="AD86" t="inlineStr"/>
-      <c r="AE86" t="inlineStr"/>
-      <c r="AF86" t="inlineStr"/>
-      <c r="AG86" t="inlineStr"/>
-      <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="inlineStr"/>
-      <c r="AJ86" t="inlineStr"/>
-      <c r="AK86" t="inlineStr"/>
-      <c r="AL86" t="inlineStr"/>
-      <c r="AM86" t="inlineStr"/>
-      <c r="AN86" t="inlineStr"/>
-      <c r="AO86" t="n">
-        <v>28.11111111111111</v>
-      </c>
-      <c r="AP86" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="AQ86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR86" t="n">
-        <v>66.27777777777777</v>
-      </c>
-      <c r="AS86" t="n">
-        <v>1244722.222222222</v>
-      </c>
-      <c r="AT86" t="n">
-        <v>69.27777777777777</v>
-      </c>
-      <c r="AU86" t="n">
-        <v>30.14285714285714</v>
-      </c>
-      <c r="AV86" t="n">
-        <v>184.5714285714286</v>
-      </c>
-      <c r="AW86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX86" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="AY86" t="n">
-        <v>1642857.142857143</v>
-      </c>
-      <c r="AZ86" t="n">
-        <v>72.85714285714286</v>
-      </c>
-      <c r="BA86" t="inlineStr"/>
-      <c r="BB86" t="inlineStr"/>
-      <c r="BC86" t="inlineStr"/>
-      <c r="BD86" t="inlineStr"/>
-      <c r="BE86" t="inlineStr"/>
-      <c r="BF86" t="inlineStr"/>
-      <c r="BG86" t="inlineStr"/>
-      <c r="BH86" t="inlineStr"/>
-      <c r="BI86" t="inlineStr"/>
-      <c r="BJ86" t="inlineStr"/>
-      <c r="BK86" t="inlineStr"/>
-      <c r="BL86" t="inlineStr"/>
-      <c r="BM86" t="inlineStr"/>
-      <c r="BN86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="inlineStr">
-        <is>
-          <t>ITdtTrn2</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="n">
-        <v>45523.58333333334</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fuertes p 
-  esp </t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>27618</v>
-      </c>
-      <c r="F87" t="n">
-        <v>22027</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="M87" t="n">
-        <v>45</v>
-      </c>
-      <c r="N87" t="n">
-        <v>55</v>
-      </c>
-      <c r="O87" t="n">
-        <v>12</v>
-      </c>
-      <c r="P87" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>3</v>
-      </c>
-      <c r="R87" t="n">
-        <v>2</v>
-      </c>
-      <c r="S87" t="n">
-        <v>15</v>
-      </c>
-      <c r="T87" t="n">
-        <v>8</v>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>UsfeP2jC</t>
-        </is>
-      </c>
-      <c r="W87" t="n">
-        <v>148</v>
-      </c>
-      <c r="X87" t="n">
-        <v>1481</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>69w4Rb2d</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="AC87" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="AD87" t="n">
-        <v>180.3</v>
-      </c>
-      <c r="AE87" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF87" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="AG87" t="n">
-        <v>2840000</v>
-      </c>
-      <c r="AH87" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="AI87" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="AJ87" t="n">
-        <v>183.5555555555555</v>
-      </c>
-      <c r="AK87" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL87" t="n">
-        <v>72.11111111111111</v>
-      </c>
-      <c r="AM87" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="AN87" t="n">
-        <v>76.44444444444444</v>
-      </c>
-      <c r="AO87" t="n">
-        <v>24.4375</v>
-      </c>
-      <c r="AP87" t="n">
-        <v>180.6875</v>
-      </c>
-      <c r="AQ87" t="n">
-        <v>1.0625</v>
-      </c>
-      <c r="AR87" t="n">
-        <v>69.75</v>
-      </c>
-      <c r="AS87" t="n">
-        <v>3079687.5</v>
-      </c>
-      <c r="AT87" t="n">
-        <v>76</v>
-      </c>
-      <c r="AU87" t="n">
-        <v>24.14285714285714</v>
-      </c>
-      <c r="AV87" t="n">
-        <v>180.2142857142857</v>
-      </c>
-      <c r="AW87" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX87" t="n">
-        <v>69.78571428571429</v>
-      </c>
-      <c r="AY87" t="n">
-        <v>3071428.571428571</v>
-      </c>
-      <c r="AZ87" t="n">
-        <v>75.57142857142857</v>
-      </c>
-      <c r="BA87" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="BB87" t="n">
-        <v>178</v>
-      </c>
-      <c r="BC87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD87" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE87" t="n">
-        <v>142</v>
-      </c>
-      <c r="BF87" t="n">
-        <v>4600000</v>
-      </c>
-      <c r="BG87" t="n">
-        <v>142</v>
-      </c>
-      <c r="BH87" t="n">
-        <v>26</v>
-      </c>
-      <c r="BI87" t="n">
-        <v>178</v>
-      </c>
-      <c r="BJ87" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL87" t="n">
-        <v>74</v>
-      </c>
-      <c r="BM87" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="BN87" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr">
-        <is>
-          <t>M3h3GWnS</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="n">
-        <v>45522.6875</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grado c  s 
-  esp </t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F88" t="n">
-        <v>23010</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="M88" t="n">
-        <v>33</v>
-      </c>
-      <c r="N88" t="n">
-        <v>67</v>
-      </c>
-      <c r="O88" t="n">
-        <v>12</v>
-      </c>
-      <c r="P88" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>5</v>
-      </c>
-      <c r="R88" t="n">
-        <v>4</v>
-      </c>
-      <c r="S88" t="n">
-        <v>11</v>
-      </c>
-      <c r="T88" t="n">
-        <v>6</v>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="W88" t="n">
-        <v>148</v>
-      </c>
-      <c r="X88" t="n">
-        <v>1481</v>
-      </c>
-      <c r="Y88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>YT0e2vMU</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="AC88" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>183.8</v>
-      </c>
-      <c r="AE88" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF88" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="AG88" t="n">
-        <v>11750000</v>
-      </c>
-      <c r="AH88" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="AI88" t="n">
-        <v>25.45454545454545</v>
-      </c>
-      <c r="AJ88" t="n">
-        <v>183</v>
-      </c>
-      <c r="AK88" t="n">
-        <v>3.454545454545455</v>
-      </c>
-      <c r="AL88" t="n">
-        <v>86.54545454545455</v>
-      </c>
-      <c r="AM88" t="n">
-        <v>90000000</v>
-      </c>
-      <c r="AN88" t="n">
-        <v>89.18181818181819</v>
-      </c>
-      <c r="AO88" t="n">
-        <v>26.28571428571428</v>
-      </c>
-      <c r="AP88" t="n">
-        <v>181.952380952381</v>
-      </c>
-      <c r="AQ88" t="n">
-        <v>1.095238095238095</v>
-      </c>
-      <c r="AR88" t="n">
-        <v>73.66666666666667</v>
-      </c>
-      <c r="AS88" t="n">
-        <v>6610000</v>
-      </c>
-      <c r="AT88" t="n">
-        <v>76.61904761904762</v>
-      </c>
-      <c r="AU88" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="AV88" t="n">
-        <v>177.6</v>
-      </c>
-      <c r="AW88" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX88" t="n">
-        <v>77.95</v>
-      </c>
-      <c r="AY88" t="n">
-        <v>34263750</v>
-      </c>
-      <c r="AZ88" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="BA88" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB88" t="n">
-        <v>172</v>
-      </c>
-      <c r="BC88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE88" t="n">
-        <v>69</v>
-      </c>
-      <c r="BF88" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="BG88" t="n">
-        <v>81</v>
-      </c>
-      <c r="BH88" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="BI88" t="n">
-        <v>181</v>
-      </c>
-      <c r="BJ88" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BK88" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL88" t="n">
-        <v>168</v>
-      </c>
-      <c r="BM88" t="n">
-        <v>108500000</v>
-      </c>
-      <c r="BN88" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr">
-        <is>
-          <t>hIsKeIld</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="n">
-        <v>45522.60416666666</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de aza m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el plantio
-  burgos </t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>12194</v>
-      </c>
-      <c r="F89" t="n">
-        <v>9642</v>
-      </c>
-      <c r="G89" t="n">
-        <v>3</v>
-      </c>
-      <c r="H89" t="n">
-        <v>1</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>vTxTEFi6</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>IJyXDZ6C</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="n">
-        <v>56</v>
-      </c>
-      <c r="N89" t="n">
-        <v>44</v>
-      </c>
-      <c r="O89" t="n">
-        <v>12</v>
-      </c>
-      <c r="P89" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>6</v>
-      </c>
-      <c r="R89" t="n">
-        <v>3</v>
-      </c>
-      <c r="S89" t="n">
-        <v>13</v>
-      </c>
-      <c r="T89" t="n">
-        <v>19</v>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>l6JQtDqc</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>M1vEw5An</t>
-        </is>
-      </c>
-      <c r="W89" t="n">
-        <v>148</v>
-      </c>
-      <c r="X89" t="n">
-        <v>1482</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z89" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA89" t="inlineStr"/>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>4jl02tPF</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr"/>
-      <c r="AD89" t="inlineStr"/>
-      <c r="AE89" t="inlineStr"/>
-      <c r="AF89" t="inlineStr"/>
-      <c r="AG89" t="inlineStr"/>
-      <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="inlineStr"/>
-      <c r="AJ89" t="inlineStr"/>
-      <c r="AK89" t="inlineStr"/>
-      <c r="AL89" t="inlineStr"/>
-      <c r="AM89" t="inlineStr"/>
-      <c r="AN89" t="inlineStr"/>
-      <c r="AO89" t="n">
-        <v>22.625</v>
-      </c>
-      <c r="AP89" t="n">
-        <v>183.625</v>
-      </c>
-      <c r="AQ89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR89" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="AS89" t="n">
-        <v>1884375</v>
-      </c>
-      <c r="AT89" t="n">
-        <v>73.75</v>
-      </c>
-      <c r="AU89" t="n">
-        <v>25.16666666666667</v>
-      </c>
-      <c r="AV89" t="n">
-        <v>181</v>
-      </c>
-      <c r="AW89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX89" t="n">
-        <v>65</v>
-      </c>
-      <c r="AY89" t="n">
-        <v>858333.3333333334</v>
-      </c>
-      <c r="AZ89" t="n">
-        <v>69.66666666666667</v>
-      </c>
-      <c r="BA89" t="inlineStr"/>
-      <c r="BB89" t="inlineStr"/>
-      <c r="BC89" t="inlineStr"/>
-      <c r="BD89" t="inlineStr"/>
-      <c r="BE89" t="inlineStr"/>
-      <c r="BF89" t="inlineStr"/>
-      <c r="BG89" t="inlineStr"/>
-      <c r="BH89" t="inlineStr"/>
-      <c r="BI89" t="inlineStr"/>
-      <c r="BJ89" t="inlineStr"/>
-      <c r="BK89" t="inlineStr"/>
-      <c r="BL89" t="inlineStr"/>
-      <c r="BM89" t="inlineStr"/>
-      <c r="BN89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="inlineStr">
-        <is>
-          <t>nigFFwtS</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="n">
-        <v>45522.60416666666</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">palencia caballero d 
-  esp </t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio manuel martinez valero
-  elche </t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>31388</v>
-      </c>
-      <c r="F90" t="n">
-        <v>15059</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>4jl02tPF</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>UytPaaEP</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="n">
-        <v>71</v>
-      </c>
-      <c r="N90" t="n">
-        <v>29</v>
-      </c>
-      <c r="O90" t="n">
-        <v>12</v>
-      </c>
-      <c r="P90" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>3</v>
-      </c>
-      <c r="R90" t="n">
-        <v>3</v>
-      </c>
-      <c r="S90" t="n">
-        <v>16</v>
-      </c>
-      <c r="T90" t="n">
-        <v>18</v>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>zT9gi7i9</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>lfrtHtBn</t>
-        </is>
-      </c>
-      <c r="W90" t="n">
-        <v>148</v>
-      </c>
-      <c r="X90" t="n">
-        <v>1482</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>za7D2lO5</t>
-        </is>
-      </c>
-      <c r="AC90" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD90" t="n">
-        <v>179.1111111111111</v>
-      </c>
-      <c r="AE90" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AF90" t="n">
-        <v>67.77777777777777</v>
-      </c>
-      <c r="AG90" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="AH90" t="n">
-        <v>73.77777777777777</v>
-      </c>
-      <c r="AI90" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ90" t="n">
-        <v>179.875</v>
-      </c>
-      <c r="AK90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL90" t="n">
-        <v>67.875</v>
-      </c>
-      <c r="AM90" t="n">
-        <v>1365625</v>
-      </c>
-      <c r="AN90" t="n">
-        <v>70.625</v>
-      </c>
-      <c r="AO90" t="n">
-        <v>26.1875</v>
-      </c>
-      <c r="AP90" t="n">
-        <v>179.1875</v>
-      </c>
-      <c r="AQ90" t="n">
-        <v>1.0625</v>
-      </c>
-      <c r="AR90" t="n">
-        <v>68.125</v>
-      </c>
-      <c r="AS90" t="n">
-        <v>1426562.5</v>
-      </c>
-      <c r="AT90" t="n">
-        <v>73.0625</v>
-      </c>
-      <c r="AU90" t="n">
-        <v>24</v>
-      </c>
-      <c r="AV90" t="n">
-        <v>179.6666666666667</v>
-      </c>
-      <c r="AW90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX90" t="n">
-        <v>65.66666666666667</v>
-      </c>
-      <c r="AY90" t="n">
-        <v>1277777.777777778</v>
-      </c>
-      <c r="AZ90" t="n">
-        <v>71.33333333333333</v>
-      </c>
-      <c r="BA90" t="inlineStr"/>
-      <c r="BB90" t="inlineStr"/>
-      <c r="BC90" t="inlineStr"/>
-      <c r="BD90" t="inlineStr"/>
-      <c r="BE90" t="inlineStr"/>
-      <c r="BF90" t="inlineStr"/>
-      <c r="BG90" t="inlineStr"/>
-      <c r="BH90" t="inlineStr"/>
-      <c r="BI90" t="inlineStr"/>
-      <c r="BJ90" t="inlineStr"/>
-      <c r="BK90" t="inlineStr"/>
-      <c r="BL90" t="inlineStr"/>
-      <c r="BM90" t="inlineStr"/>
-      <c r="BN90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="inlineStr">
-        <is>
-          <t>Eax2EqHs</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="n">
-        <v>45522.58333333334</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hernandez a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F91" t="n">
-        <v>31763</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" t="n">
-        <v>2</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="L91" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M91" t="n">
-        <v>66</v>
-      </c>
-      <c r="N91" t="n">
-        <v>34</v>
-      </c>
-      <c r="O91" t="n">
-        <v>11</v>
-      </c>
-      <c r="P91" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>5</v>
-      </c>
-      <c r="R91" t="n">
-        <v>5</v>
-      </c>
-      <c r="S91" t="n">
-        <v>14</v>
-      </c>
-      <c r="T91" t="n">
-        <v>21</v>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
-        </is>
-      </c>
-      <c r="W91" t="n">
-        <v>148</v>
-      </c>
-      <c r="X91" t="n">
-        <v>1481</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA91" t="inlineStr"/>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="AC91" t="n">
-        <v>25.88888888888889</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>182</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>1.888888888888889</v>
-      </c>
-      <c r="AF91" t="n">
-        <v>77.88888888888889</v>
-      </c>
-      <c r="AG91" t="n">
-        <v>23333333.33333333</v>
-      </c>
-      <c r="AH91" t="n">
-        <v>81.44444444444444</v>
-      </c>
-      <c r="AI91" t="n">
-        <v>28.125</v>
-      </c>
-      <c r="AJ91" t="n">
-        <v>178.125</v>
-      </c>
-      <c r="AK91" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AL91" t="n">
-        <v>75.125</v>
-      </c>
-      <c r="AM91" t="n">
-        <v>6887500</v>
-      </c>
-      <c r="AN91" t="n">
-        <v>76.75</v>
-      </c>
-      <c r="AO91" t="n">
-        <v>22.94736842105263</v>
-      </c>
-      <c r="AP91" t="n">
-        <v>177.9473684210526</v>
-      </c>
-      <c r="AQ91" t="n">
-        <v>1.315789473684211</v>
-      </c>
-      <c r="AR91" t="n">
-        <v>74.42105263157895</v>
-      </c>
-      <c r="AS91" t="n">
-        <v>16084210.52631579</v>
-      </c>
-      <c r="AT91" t="n">
-        <v>81.47368421052632</v>
-      </c>
-      <c r="AU91" t="n">
-        <v>27.875</v>
-      </c>
-      <c r="AV91" t="n">
-        <v>177.375</v>
-      </c>
-      <c r="AW91" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AX91" t="n">
-        <v>73.6875</v>
-      </c>
-      <c r="AY91" t="n">
-        <v>4837500</v>
-      </c>
-      <c r="AZ91" t="n">
-        <v>75.6875</v>
-      </c>
-      <c r="BA91" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB91" t="n">
-        <v>181.25</v>
-      </c>
-      <c r="BC91" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BD91" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE91" t="n">
-        <v>314</v>
-      </c>
-      <c r="BF91" t="n">
-        <v>89000000</v>
-      </c>
-      <c r="BG91" t="n">
-        <v>329</v>
-      </c>
-      <c r="BH91" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="BI91" t="n">
-        <v>181</v>
-      </c>
-      <c r="BJ91" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK91" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL91" t="n">
-        <v>137</v>
-      </c>
-      <c r="BM91" t="n">
-        <v>11550000</v>
-      </c>
-      <c r="BN91" t="n">
-        <v>151</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
